--- a/backend/templates/UC-18gsm-210W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-210W-BFQR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC4F90D-A6F4-4F76-9213-FCEA46EC1D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DF15C3-7F5C-4D09-B4D7-CADAA4084D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page1" sheetId="6" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1869,6 +1872,50 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1915,88 +1962,161 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2022,181 +2142,214 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2257,156 +2410,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3081,35 +3084,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3130,12 +3133,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="149"/>
-      <c r="C4" s="150"/>
-      <c r="D4" s="151"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="142"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3147,19 +3150,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="139"/>
-      <c r="K4" s="140"/>
+      <c r="J4" s="153"/>
+      <c r="K4" s="154"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="153"/>
-      <c r="C5" s="154"/>
-      <c r="D5" s="155"/>
+      <c r="B5" s="144"/>
+      <c r="C5" s="145"/>
+      <c r="D5" s="146"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3171,64 +3174,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="142"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="156"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="156" t="s">
+      <c r="A6" s="161" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="157"/>
-      <c r="C6" s="158"/>
+      <c r="B6" s="162"/>
+      <c r="C6" s="163"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="G6" s="134"/>
-      <c r="H6" s="146"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="136"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="160"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="149"/>
+      <c r="K6" s="150"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="159" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137" t="s">
+      <c r="A7" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="151"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="151" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="143" t="s">
+      <c r="G7" s="157" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="143" t="s">
+      <c r="H7" s="157" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="137" t="s">
+      <c r="I7" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="137"/>
-      <c r="K7" s="138"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="152"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="160"/>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="145" t="s">
+      <c r="A8" s="165"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="145"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="158"/>
+      <c r="H8" s="158"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3630,11 +3633,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="167" t="s">
+      <c r="A39" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="168"/>
-      <c r="C39" s="169"/>
+      <c r="B39" s="134"/>
+      <c r="C39" s="135"/>
       <c r="D39" s="35" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3669,11 +3672,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="164" t="s">
+      <c r="A40" s="169" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="165"/>
-      <c r="C40" s="166"/>
+      <c r="B40" s="170"/>
+      <c r="C40" s="171"/>
       <c r="D40" s="38">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3708,11 +3711,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="161" t="s">
+      <c r="A41" s="166" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="162"/>
-      <c r="C41" s="163"/>
+      <c r="B41" s="167"/>
+      <c r="C41" s="168"/>
       <c r="D41" s="41">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3753,8 +3756,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="170"/>
-      <c r="C42" s="170"/>
+      <c r="B42" s="136"/>
+      <c r="C42" s="136"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3771,8 +3774,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
+      <c r="B43" s="137"/>
+      <c r="C43" s="137"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3781,11 +3784,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="147" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
+      <c r="B44" s="147"/>
+      <c r="C44" s="147"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -3797,11 +3800,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="147" t="s">
         <v>135</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3843,15 +3846,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
@@ -3868,6 +3862,15 @@
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D9:D41">
@@ -3949,35 +3952,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3998,18 +4001,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="149">
+      <c r="B4" s="140">
         <f ca="1">Page2!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="196">
+      <c r="C4" s="195">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="193"/>
+      <c r="D4" s="196"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -4027,25 +4030,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="234">
+      <c r="J4" s="191">
         <f>Page2!K4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="235"/>
+      <c r="K4" s="192"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="153">
+      <c r="B5" s="144">
         <f ca="1">Page2!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="154">
+      <c r="C5" s="145">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="155"/>
+      <c r="D5" s="146"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4063,113 +4066,113 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="236">
+      <c r="J5" s="193">
         <f>Page2!K5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="237"/>
+      <c r="K5" s="194"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="201" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="187"/>
-      <c r="G6" s="200"/>
-      <c r="H6" s="187"/>
-      <c r="I6" s="198"/>
-      <c r="J6" s="199"/>
+      <c r="B6" s="202"/>
+      <c r="C6" s="203"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="190"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="190"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="188"/>
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="185" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="186"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="192" t="s">
+      <c r="A7" s="197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="186"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="200" t="s">
+      <c r="E7" s="198"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="189" t="s">
         <v>126</v>
       </c>
-      <c r="H7" s="186"/>
-      <c r="I7" s="200" t="s">
+      <c r="H7" s="198"/>
+      <c r="I7" s="189" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="187"/>
-      <c r="K7" s="209" t="s">
+      <c r="J7" s="190"/>
+      <c r="K7" s="182" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="172"/>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="172" t="s">
+      <c r="A8" s="199"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="174" t="s">
+      <c r="E8" s="211" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="175" t="s">
+      <c r="F8" s="212" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="177"/>
-      <c r="H8" s="197"/>
-      <c r="I8" s="177" t="s">
+      <c r="G8" s="214"/>
+      <c r="H8" s="200"/>
+      <c r="I8" s="214" t="s">
         <v>137</v>
       </c>
-      <c r="J8" s="175"/>
-      <c r="K8" s="210"/>
+      <c r="J8" s="212"/>
+      <c r="K8" s="183"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="172"/>
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="175"/>
-      <c r="G9" s="177"/>
-      <c r="H9" s="197"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="212"/>
+      <c r="G9" s="214"/>
+      <c r="H9" s="200"/>
       <c r="I9" s="58" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="59">
-        <v>250</v>
-      </c>
-      <c r="K9" s="210"/>
+        <v>210</v>
+      </c>
+      <c r="K9" s="183"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="172">
+      <c r="A10" s="199">
         <f>Page1!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" s="197">
+      <c r="B10" s="200">
         <f>Page1!B9</f>
         <v>0</v>
       </c>
-      <c r="C10" s="197">
+      <c r="C10" s="200">
         <f>Page1!C9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="173"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="201"/>
-      <c r="H10" s="202"/>
+      <c r="D10" s="225"/>
+      <c r="E10" s="158"/>
+      <c r="F10" s="213"/>
+      <c r="G10" s="219"/>
+      <c r="H10" s="220"/>
       <c r="I10" s="60" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="61">
-        <v>253</v>
-      </c>
-      <c r="K10" s="211"/>
+        <v>213</v>
+      </c>
+      <c r="K10" s="184"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="62">
@@ -4187,10 +4190,10 @@
       <c r="D11" s="65"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="221"/>
-      <c r="H11" s="221"/>
-      <c r="I11" s="203"/>
-      <c r="J11" s="204"/>
+      <c r="G11" s="176"/>
+      <c r="H11" s="176"/>
+      <c r="I11" s="221"/>
+      <c r="J11" s="222"/>
       <c r="K11" s="66"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4209,10 +4212,10 @@
       <c r="D12" s="70"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="214"/>
-      <c r="H12" s="214"/>
-      <c r="I12" s="205"/>
-      <c r="J12" s="206"/>
+      <c r="G12" s="177"/>
+      <c r="H12" s="177"/>
+      <c r="I12" s="174"/>
+      <c r="J12" s="175"/>
       <c r="K12" s="71"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4231,10 +4234,10 @@
       <c r="D13" s="70"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="214"/>
-      <c r="H13" s="214"/>
-      <c r="I13" s="205"/>
-      <c r="J13" s="206"/>
+      <c r="G13" s="177"/>
+      <c r="H13" s="177"/>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
       <c r="K13" s="71"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4253,10 +4256,10 @@
       <c r="D14" s="70"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="214"/>
-      <c r="H14" s="214"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="206"/>
+      <c r="G14" s="177"/>
+      <c r="H14" s="177"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="175"/>
       <c r="K14" s="71"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4275,10 +4278,10 @@
       <c r="D15" s="70"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="214"/>
-      <c r="H15" s="214"/>
-      <c r="I15" s="205"/>
-      <c r="J15" s="206"/>
+      <c r="G15" s="177"/>
+      <c r="H15" s="177"/>
+      <c r="I15" s="174"/>
+      <c r="J15" s="175"/>
       <c r="K15" s="71"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4297,10 +4300,10 @@
       <c r="D16" s="65"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="221"/>
-      <c r="H16" s="221"/>
-      <c r="I16" s="205"/>
-      <c r="J16" s="206"/>
+      <c r="G16" s="176"/>
+      <c r="H16" s="176"/>
+      <c r="I16" s="174"/>
+      <c r="J16" s="175"/>
       <c r="K16" s="66"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4319,10 +4322,10 @@
       <c r="D17" s="70"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="214"/>
-      <c r="H17" s="214"/>
-      <c r="I17" s="205"/>
-      <c r="J17" s="206"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="177"/>
+      <c r="I17" s="174"/>
+      <c r="J17" s="175"/>
       <c r="K17" s="71"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4341,10 +4344,10 @@
       <c r="D18" s="70"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="214"/>
-      <c r="H18" s="214"/>
-      <c r="I18" s="205"/>
-      <c r="J18" s="206"/>
+      <c r="G18" s="177"/>
+      <c r="H18" s="177"/>
+      <c r="I18" s="174"/>
+      <c r="J18" s="175"/>
       <c r="K18" s="71"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4363,10 +4366,10 @@
       <c r="D19" s="70"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="214"/>
-      <c r="H19" s="214"/>
-      <c r="I19" s="205"/>
-      <c r="J19" s="206"/>
+      <c r="G19" s="177"/>
+      <c r="H19" s="177"/>
+      <c r="I19" s="174"/>
+      <c r="J19" s="175"/>
       <c r="K19" s="71"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4385,10 +4388,10 @@
       <c r="D20" s="70"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="215"/>
-      <c r="H20" s="216"/>
-      <c r="I20" s="205"/>
-      <c r="J20" s="206"/>
+      <c r="G20" s="172"/>
+      <c r="H20" s="173"/>
+      <c r="I20" s="174"/>
+      <c r="J20" s="175"/>
       <c r="K20" s="71"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4407,10 +4410,10 @@
       <c r="D21" s="70"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="215"/>
-      <c r="H21" s="216"/>
-      <c r="I21" s="205"/>
-      <c r="J21" s="206"/>
+      <c r="G21" s="172"/>
+      <c r="H21" s="173"/>
+      <c r="I21" s="174"/>
+      <c r="J21" s="175"/>
       <c r="K21" s="71"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4429,10 +4432,10 @@
       <c r="D22" s="70"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="215"/>
-      <c r="H22" s="216"/>
-      <c r="I22" s="205"/>
-      <c r="J22" s="206"/>
+      <c r="G22" s="172"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="174"/>
+      <c r="J22" s="175"/>
       <c r="K22" s="71"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4451,10 +4454,10 @@
       <c r="D23" s="70"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="215"/>
-      <c r="H23" s="216"/>
-      <c r="I23" s="205"/>
-      <c r="J23" s="206"/>
+      <c r="G23" s="172"/>
+      <c r="H23" s="173"/>
+      <c r="I23" s="174"/>
+      <c r="J23" s="175"/>
       <c r="K23" s="71"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4473,10 +4476,10 @@
       <c r="D24" s="70"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="215"/>
-      <c r="H24" s="216"/>
-      <c r="I24" s="205"/>
-      <c r="J24" s="206"/>
+      <c r="G24" s="172"/>
+      <c r="H24" s="173"/>
+      <c r="I24" s="174"/>
+      <c r="J24" s="175"/>
       <c r="K24" s="71"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4495,10 +4498,10 @@
       <c r="D25" s="70"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="215"/>
-      <c r="H25" s="216"/>
-      <c r="I25" s="205"/>
-      <c r="J25" s="206"/>
+      <c r="G25" s="172"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="175"/>
       <c r="K25" s="71"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4517,10 +4520,10 @@
       <c r="D26" s="70"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="215"/>
-      <c r="H26" s="216"/>
-      <c r="I26" s="205"/>
-      <c r="J26" s="206"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="173"/>
+      <c r="I26" s="174"/>
+      <c r="J26" s="175"/>
       <c r="K26" s="71"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4539,10 +4542,10 @@
       <c r="D27" s="70"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="215"/>
-      <c r="H27" s="216"/>
-      <c r="I27" s="205"/>
-      <c r="J27" s="206"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="173"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="175"/>
       <c r="K27" s="71"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4561,10 +4564,10 @@
       <c r="D28" s="70"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="215"/>
-      <c r="H28" s="216"/>
-      <c r="I28" s="205"/>
-      <c r="J28" s="206"/>
+      <c r="G28" s="172"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="174"/>
+      <c r="J28" s="175"/>
       <c r="K28" s="71"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4583,10 +4586,10 @@
       <c r="D29" s="70"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="215"/>
-      <c r="H29" s="216"/>
-      <c r="I29" s="205"/>
-      <c r="J29" s="206"/>
+      <c r="G29" s="172"/>
+      <c r="H29" s="173"/>
+      <c r="I29" s="174"/>
+      <c r="J29" s="175"/>
       <c r="K29" s="71"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4605,10 +4608,10 @@
       <c r="D30" s="70"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="215"/>
-      <c r="H30" s="216"/>
-      <c r="I30" s="205"/>
-      <c r="J30" s="206"/>
+      <c r="G30" s="172"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="174"/>
+      <c r="J30" s="175"/>
       <c r="K30" s="71"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4627,10 +4630,10 @@
       <c r="D31" s="70"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="215"/>
-      <c r="H31" s="216"/>
-      <c r="I31" s="205"/>
-      <c r="J31" s="206"/>
+      <c r="G31" s="172"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="174"/>
+      <c r="J31" s="175"/>
       <c r="K31" s="71"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4649,10 +4652,10 @@
       <c r="D32" s="70"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="215"/>
-      <c r="H32" s="216"/>
-      <c r="I32" s="205"/>
-      <c r="J32" s="206"/>
+      <c r="G32" s="172"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="174"/>
+      <c r="J32" s="175"/>
       <c r="K32" s="71"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4671,10 +4674,10 @@
       <c r="D33" s="70"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="215"/>
-      <c r="H33" s="216"/>
-      <c r="I33" s="205"/>
-      <c r="J33" s="206"/>
+      <c r="G33" s="172"/>
+      <c r="H33" s="173"/>
+      <c r="I33" s="174"/>
+      <c r="J33" s="175"/>
       <c r="K33" s="71"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4693,10 +4696,10 @@
       <c r="D34" s="70"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="215"/>
-      <c r="H34" s="216"/>
-      <c r="I34" s="205"/>
-      <c r="J34" s="206"/>
+      <c r="G34" s="172"/>
+      <c r="H34" s="173"/>
+      <c r="I34" s="174"/>
+      <c r="J34" s="175"/>
       <c r="K34" s="71"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4715,10 +4718,10 @@
       <c r="D35" s="70"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="215"/>
-      <c r="H35" s="216"/>
-      <c r="I35" s="205"/>
-      <c r="J35" s="206"/>
+      <c r="G35" s="172"/>
+      <c r="H35" s="173"/>
+      <c r="I35" s="174"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="71"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4737,10 +4740,10 @@
       <c r="D36" s="70"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="215"/>
-      <c r="H36" s="216"/>
-      <c r="I36" s="205"/>
-      <c r="J36" s="206"/>
+      <c r="G36" s="172"/>
+      <c r="H36" s="173"/>
+      <c r="I36" s="174"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="71"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4759,10 +4762,10 @@
       <c r="D37" s="70"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="215"/>
-      <c r="H37" s="216"/>
-      <c r="I37" s="205"/>
-      <c r="J37" s="206"/>
+      <c r="G37" s="172"/>
+      <c r="H37" s="173"/>
+      <c r="I37" s="174"/>
+      <c r="J37" s="175"/>
       <c r="K37" s="71"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4781,10 +4784,10 @@
       <c r="D38" s="70"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="215"/>
-      <c r="H38" s="216"/>
-      <c r="I38" s="205"/>
-      <c r="J38" s="206"/>
+      <c r="G38" s="172"/>
+      <c r="H38" s="173"/>
+      <c r="I38" s="174"/>
+      <c r="J38" s="175"/>
       <c r="K38" s="71"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4803,10 +4806,10 @@
       <c r="D39" s="70"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="215"/>
-      <c r="H39" s="216"/>
-      <c r="I39" s="205"/>
-      <c r="J39" s="206"/>
+      <c r="G39" s="172"/>
+      <c r="H39" s="173"/>
+      <c r="I39" s="174"/>
+      <c r="J39" s="175"/>
       <c r="K39" s="71"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4825,18 +4828,18 @@
       <c r="D40" s="70"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="214"/>
-      <c r="H40" s="214"/>
-      <c r="I40" s="205"/>
-      <c r="J40" s="206"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="177"/>
+      <c r="I40" s="174"/>
+      <c r="J40" s="175"/>
       <c r="K40" s="71"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="194" t="s">
+      <c r="A41" s="209" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="195"/>
-      <c r="C41" s="195"/>
+      <c r="B41" s="210"/>
+      <c r="C41" s="210"/>
       <c r="D41" s="79" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4849,27 +4852,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="219" t="e">
+      <c r="G41" s="180" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="220"/>
-      <c r="I41" s="207" t="e">
+      <c r="H41" s="181"/>
+      <c r="I41" s="223" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="208"/>
+      <c r="J41" s="224"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="188" t="s">
+      <c r="A42" s="204" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="189"/>
-      <c r="C42" s="189"/>
+      <c r="B42" s="205"/>
+      <c r="C42" s="205"/>
       <c r="D42" s="80">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4882,27 +4885,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="217">
+      <c r="G42" s="178">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="218"/>
-      <c r="I42" s="212">
+      <c r="H42" s="179"/>
+      <c r="I42" s="185">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="213"/>
+      <c r="J42" s="186"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="190" t="s">
+      <c r="A43" s="206" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="191"/>
-      <c r="C43" s="191"/>
+      <c r="B43" s="207"/>
+      <c r="C43" s="207"/>
       <c r="D43" s="81">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4915,16 +4918,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="178">
+      <c r="G43" s="215">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="179"/>
-      <c r="I43" s="180">
+      <c r="H43" s="216"/>
+      <c r="I43" s="217">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="181"/>
+      <c r="J43" s="218"/>
       <c r="K43" s="83">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4934,8 +4937,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="170"/>
-      <c r="C44" s="170"/>
+      <c r="B44" s="136"/>
+      <c r="C44" s="136"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4952,8 +4955,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="171"/>
-      <c r="C45" s="171"/>
+      <c r="B45" s="137"/>
+      <c r="C45" s="137"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4962,11 +4965,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="147" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="147"/>
+      <c r="C46" s="147"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -4979,11 +4982,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="133" t="s">
+      <c r="A47" s="147" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="133"/>
-      <c r="C47" s="133"/>
+      <c r="B47" s="147"/>
+      <c r="C47" s="147"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -5038,28 +5041,62 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="I15:J15"/>
@@ -5076,62 +5113,28 @@
     <mergeCell ref="G18:H18"/>
     <mergeCell ref="G39:H39"/>
     <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
@@ -5187,35 +5190,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="138" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
+      <c r="B2" s="138"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5236,18 +5239,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="148" t="s">
+      <c r="A4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="149">
+      <c r="B4" s="140">
         <f ca="1">Page2!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="196">
+      <c r="C4" s="195">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="193"/>
+      <c r="D4" s="196"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5265,25 +5268,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="234">
+      <c r="J4" s="191">
         <f>Page2!K4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="235"/>
+      <c r="K4" s="192"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="153">
+      <c r="B5" s="144">
         <f ca="1">Page2!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="154">
+      <c r="C5" s="145">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="155"/>
+      <c r="D5" s="146"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5301,79 +5304,79 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="236">
+      <c r="J5" s="193">
         <f>Page2!K5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="237"/>
+      <c r="K5" s="194"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="230" t="s">
+      <c r="A6" s="229" t="s">
         <v>133</v>
       </c>
-      <c r="B6" s="231"/>
-      <c r="C6" s="232"/>
-      <c r="D6" s="233"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="146"/>
+      <c r="B6" s="230"/>
+      <c r="C6" s="231"/>
+      <c r="D6" s="232"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="160"/>
       <c r="H6" s="85"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="186"/>
-      <c r="K6" s="209"/>
+      <c r="I6" s="197"/>
+      <c r="J6" s="198"/>
+      <c r="K6" s="182"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="185" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="186"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="192" t="s">
+      <c r="A7" s="197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="208" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="222"/>
-      <c r="F7" s="222"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="227" t="s">
+      <c r="E7" s="233"/>
+      <c r="F7" s="233"/>
+      <c r="G7" s="196"/>
+      <c r="H7" s="226" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="172"/>
-      <c r="J7" s="197"/>
-      <c r="K7" s="210"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="183"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="172"/>
-      <c r="B8" s="197"/>
-      <c r="C8" s="197"/>
-      <c r="D8" s="225" t="s">
+      <c r="A8" s="199"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="236" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="174" t="s">
+      <c r="E8" s="211" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="174" t="s">
+      <c r="F8" s="211" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="174" t="s">
+      <c r="G8" s="211" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="228"/>
-      <c r="I8" s="172"/>
-      <c r="J8" s="197"/>
-      <c r="K8" s="210"/>
+      <c r="H8" s="227"/>
+      <c r="I8" s="199"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="183"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="172"/>
-      <c r="B9" s="197"/>
-      <c r="C9" s="197"/>
-      <c r="D9" s="226"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="172"/>
-      <c r="J9" s="197"/>
-      <c r="K9" s="210"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="237"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="228"/>
+      <c r="I9" s="199"/>
+      <c r="J9" s="200"/>
+      <c r="K9" s="183"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="62">
@@ -5393,9 +5396,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="87"/>
       <c r="H10" s="88"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="197"/>
-      <c r="K10" s="210"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="200"/>
+      <c r="K10" s="183"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67">
@@ -5415,9 +5418,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="90"/>
       <c r="H11" s="91"/>
-      <c r="I11" s="172"/>
-      <c r="J11" s="197"/>
-      <c r="K11" s="210"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="200"/>
+      <c r="K11" s="183"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="67">
@@ -5437,9 +5440,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="90"/>
       <c r="H12" s="91"/>
-      <c r="I12" s="172"/>
-      <c r="J12" s="197"/>
-      <c r="K12" s="210"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="200"/>
+      <c r="K12" s="183"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="67">
@@ -5459,9 +5462,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="87"/>
       <c r="H13" s="91"/>
-      <c r="I13" s="172"/>
-      <c r="J13" s="197"/>
-      <c r="K13" s="210"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="183"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="67">
@@ -5481,9 +5484,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="90"/>
       <c r="H14" s="91"/>
-      <c r="I14" s="172"/>
-      <c r="J14" s="197"/>
-      <c r="K14" s="210"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="200"/>
+      <c r="K14" s="183"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="67">
@@ -5503,9 +5506,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="90"/>
       <c r="H15" s="91"/>
-      <c r="I15" s="172"/>
-      <c r="J15" s="197"/>
-      <c r="K15" s="210"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="183"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67">
@@ -5525,9 +5528,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="90"/>
       <c r="H16" s="91"/>
-      <c r="I16" s="172"/>
-      <c r="J16" s="197"/>
-      <c r="K16" s="210"/>
+      <c r="I16" s="199"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="183"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67">
@@ -5547,9 +5550,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="90"/>
       <c r="H17" s="91"/>
-      <c r="I17" s="172"/>
-      <c r="J17" s="197"/>
-      <c r="K17" s="210"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="183"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="67">
@@ -5569,9 +5572,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="90"/>
       <c r="H18" s="91"/>
-      <c r="I18" s="172"/>
-      <c r="J18" s="197"/>
-      <c r="K18" s="210"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="183"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="67">
@@ -5591,9 +5594,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="90"/>
       <c r="H19" s="91"/>
-      <c r="I19" s="172"/>
-      <c r="J19" s="197"/>
-      <c r="K19" s="210"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="183"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75">
@@ -5613,9 +5616,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="90"/>
       <c r="H20" s="91"/>
-      <c r="I20" s="172"/>
-      <c r="J20" s="197"/>
-      <c r="K20" s="210"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="183"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="67">
@@ -5635,9 +5638,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="90"/>
       <c r="H21" s="91"/>
-      <c r="I21" s="172"/>
-      <c r="J21" s="197"/>
-      <c r="K21" s="210"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="183"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="67">
@@ -5657,9 +5660,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="90"/>
       <c r="H22" s="91"/>
-      <c r="I22" s="172"/>
-      <c r="J22" s="197"/>
-      <c r="K22" s="210"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="200"/>
+      <c r="K22" s="183"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="67">
@@ -5679,9 +5682,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="90"/>
       <c r="H23" s="91"/>
-      <c r="I23" s="172"/>
-      <c r="J23" s="197"/>
-      <c r="K23" s="210"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="183"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="67">
@@ -5701,9 +5704,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="90"/>
       <c r="H24" s="91"/>
-      <c r="I24" s="172"/>
-      <c r="J24" s="197"/>
-      <c r="K24" s="210"/>
+      <c r="I24" s="199"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="183"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="67">
@@ -5723,9 +5726,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="90"/>
       <c r="H25" s="91"/>
-      <c r="I25" s="172"/>
-      <c r="J25" s="197"/>
-      <c r="K25" s="210"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="183"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="67">
@@ -5745,9 +5748,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="90"/>
       <c r="H26" s="91"/>
-      <c r="I26" s="172"/>
-      <c r="J26" s="197"/>
-      <c r="K26" s="210"/>
+      <c r="I26" s="199"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="183"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="67">
@@ -5767,9 +5770,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="90"/>
       <c r="H27" s="91"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="197"/>
-      <c r="K27" s="210"/>
+      <c r="I27" s="199"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="183"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="67">
@@ -5789,9 +5792,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="90"/>
       <c r="H28" s="91"/>
-      <c r="I28" s="172"/>
-      <c r="J28" s="197"/>
-      <c r="K28" s="210"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="183"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="67">
@@ -5811,9 +5814,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="90"/>
       <c r="H29" s="91"/>
-      <c r="I29" s="172"/>
-      <c r="J29" s="197"/>
-      <c r="K29" s="210"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="183"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="75">
@@ -5833,9 +5836,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="90"/>
       <c r="H30" s="91"/>
-      <c r="I30" s="172"/>
-      <c r="J30" s="197"/>
-      <c r="K30" s="210"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="200"/>
+      <c r="K30" s="183"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="67">
@@ -5855,9 +5858,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="90"/>
       <c r="H31" s="91"/>
-      <c r="I31" s="172"/>
-      <c r="J31" s="197"/>
-      <c r="K31" s="210"/>
+      <c r="I31" s="199"/>
+      <c r="J31" s="200"/>
+      <c r="K31" s="183"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="67">
@@ -5877,9 +5880,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="90"/>
       <c r="H32" s="91"/>
-      <c r="I32" s="172"/>
-      <c r="J32" s="197"/>
-      <c r="K32" s="210"/>
+      <c r="I32" s="199"/>
+      <c r="J32" s="200"/>
+      <c r="K32" s="183"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="67">
@@ -5899,9 +5902,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="90"/>
       <c r="H33" s="91"/>
-      <c r="I33" s="172"/>
-      <c r="J33" s="197"/>
-      <c r="K33" s="210"/>
+      <c r="I33" s="199"/>
+      <c r="J33" s="200"/>
+      <c r="K33" s="183"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="67">
@@ -5921,9 +5924,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="90"/>
       <c r="H34" s="91"/>
-      <c r="I34" s="172"/>
-      <c r="J34" s="197"/>
-      <c r="K34" s="210"/>
+      <c r="I34" s="199"/>
+      <c r="J34" s="200"/>
+      <c r="K34" s="183"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="67">
@@ -5943,9 +5946,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="90"/>
       <c r="H35" s="91"/>
-      <c r="I35" s="172"/>
-      <c r="J35" s="197"/>
-      <c r="K35" s="210"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="183"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="67">
@@ -5965,9 +5968,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="90"/>
       <c r="H36" s="91"/>
-      <c r="I36" s="172"/>
-      <c r="J36" s="197"/>
-      <c r="K36" s="210"/>
+      <c r="I36" s="199"/>
+      <c r="J36" s="200"/>
+      <c r="K36" s="183"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="67">
@@ -5987,9 +5990,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="90"/>
       <c r="H37" s="91"/>
-      <c r="I37" s="172"/>
-      <c r="J37" s="197"/>
-      <c r="K37" s="210"/>
+      <c r="I37" s="199"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="183"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="67">
@@ -6009,9 +6012,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="90"/>
       <c r="H38" s="91"/>
-      <c r="I38" s="172"/>
-      <c r="J38" s="197"/>
-      <c r="K38" s="210"/>
+      <c r="I38" s="199"/>
+      <c r="J38" s="200"/>
+      <c r="K38" s="183"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="76">
@@ -6031,16 +6034,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="90"/>
       <c r="H39" s="91"/>
-      <c r="I39" s="172"/>
-      <c r="J39" s="197"/>
-      <c r="K39" s="210"/>
+      <c r="I39" s="199"/>
+      <c r="J39" s="200"/>
+      <c r="K39" s="183"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="223" t="s">
+      <c r="A40" s="234" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="224"/>
-      <c r="C40" s="224"/>
+      <c r="B40" s="235"/>
+      <c r="C40" s="235"/>
       <c r="D40" s="92" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6061,16 +6064,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="197"/>
-      <c r="J40" s="197"/>
-      <c r="K40" s="210"/>
+      <c r="I40" s="200"/>
+      <c r="J40" s="200"/>
+      <c r="K40" s="183"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="188" t="s">
+      <c r="A41" s="204" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="189"/>
-      <c r="C41" s="189"/>
+      <c r="B41" s="205"/>
+      <c r="C41" s="205"/>
       <c r="D41" s="94">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -6091,16 +6094,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="197"/>
-      <c r="J41" s="197"/>
-      <c r="K41" s="210"/>
+      <c r="I41" s="200"/>
+      <c r="J41" s="200"/>
+      <c r="K41" s="183"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="190" t="s">
+      <c r="A42" s="206" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="191"/>
-      <c r="C42" s="191"/>
+      <c r="B42" s="207"/>
+      <c r="C42" s="207"/>
       <c r="D42" s="96">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6121,16 +6124,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="211"/>
+      <c r="I42" s="220"/>
+      <c r="J42" s="220"/>
+      <c r="K42" s="184"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="170"/>
-      <c r="C43" s="170"/>
+      <c r="B43" s="136"/>
+      <c r="C43" s="136"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6147,8 +6150,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
+      <c r="B44" s="137"/>
+      <c r="C44" s="137"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6157,11 +6160,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="147" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -6174,11 +6177,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="147" t="s">
         <v>135</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="147"/>
+      <c r="C46" s="147"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6203,18 +6206,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="I6:K42"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="D7:G7"/>
@@ -6228,6 +6219,18 @@
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
+    <mergeCell ref="I6:K42"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
@@ -6274,15 +6277,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="301" t="s">
+      <c r="A1" s="238" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="302"/>
-      <c r="C1" s="302"/>
-      <c r="D1" s="302"/>
-      <c r="E1" s="302"/>
-      <c r="F1" s="302"/>
-      <c r="G1" s="303"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="240"/>
     </row>
     <row r="2" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="100"/>
@@ -6296,37 +6299,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="242" t="s">
+      <c r="A3" s="292" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="243"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
-      <c r="F3" s="243"/>
-      <c r="G3" s="244"/>
+      <c r="B3" s="293"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="293"/>
+      <c r="E3" s="293"/>
+      <c r="F3" s="293"/>
+      <c r="G3" s="294"/>
     </row>
     <row r="4" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="199" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="197"/>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="210"/>
+      <c r="B4" s="200"/>
+      <c r="C4" s="200"/>
+      <c r="D4" s="200"/>
+      <c r="E4" s="200"/>
+      <c r="F4" s="200"/>
+      <c r="G4" s="183"/>
     </row>
     <row r="5" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="304" t="s">
+      <c r="A5" s="241" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="305"/>
-      <c r="C5" s="305"/>
-      <c r="D5" s="305"/>
-      <c r="E5" s="305"/>
-      <c r="F5" s="305"/>
-      <c r="G5" s="306"/>
+      <c r="B5" s="242"/>
+      <c r="C5" s="242"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="243"/>
     </row>
     <row r="6" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="103" t="s">
@@ -6338,14 +6341,14 @@
       <c r="C6" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="260" t="s">
+      <c r="D6" s="244" t="s">
         <v>142</v>
       </c>
-      <c r="E6" s="262"/>
-      <c r="F6" s="281" t="s">
+      <c r="E6" s="245"/>
+      <c r="F6" s="246" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="285">
+      <c r="G6" s="247">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6358,13 +6361,13 @@
       <c r="C7" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="260">
+      <c r="D7" s="244">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="262"/>
-      <c r="F7" s="281"/>
-      <c r="G7" s="307"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="246"/>
+      <c r="G7" s="248"/>
     </row>
     <row r="8" spans="1:7" s="99" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="103" t="s">
@@ -6377,15 +6380,15 @@
       <c r="C8" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="281">
+      <c r="D8" s="246">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="281"/>
-      <c r="F8" s="282" t="s">
+      <c r="E8" s="246"/>
+      <c r="F8" s="258" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="285">
+      <c r="G8" s="247">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6398,15 +6401,15 @@
         <f>Page1!G44</f>
         <v>461359700</v>
       </c>
-      <c r="C9" s="282" t="s">
+      <c r="C9" s="258" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="288" t="s">
+      <c r="D9" s="263" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="289"/>
-      <c r="F9" s="283"/>
-      <c r="G9" s="286"/>
+      <c r="E9" s="264"/>
+      <c r="F9" s="259"/>
+      <c r="G9" s="261"/>
     </row>
     <row r="10" spans="1:7" s="99" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="110" t="s">
@@ -6416,34 +6419,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="284"/>
-      <c r="D10" s="290"/>
-      <c r="E10" s="291"/>
-      <c r="F10" s="284"/>
-      <c r="G10" s="287"/>
+      <c r="C10" s="260"/>
+      <c r="D10" s="265"/>
+      <c r="E10" s="266"/>
+      <c r="F10" s="260"/>
+      <c r="G10" s="262"/>
     </row>
     <row r="11" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="292" t="s">
+      <c r="A11" s="249" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="294" t="s">
+      <c r="B11" s="251" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="296" t="s">
+      <c r="C11" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="297"/>
-      <c r="E11" s="298"/>
-      <c r="F11" s="294" t="s">
+      <c r="D11" s="254"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="251" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="299" t="s">
+      <c r="G11" s="256" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="293"/>
-      <c r="B12" s="295"/>
+      <c r="A12" s="250"/>
+      <c r="B12" s="252"/>
       <c r="C12" s="112" t="s">
         <v>60</v>
       </c>
@@ -6453,8 +6456,8 @@
       <c r="E12" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="295"/>
-      <c r="G12" s="300"/>
+      <c r="F12" s="252"/>
+      <c r="G12" s="257"/>
     </row>
     <row r="13" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="113" t="s">
@@ -6524,7 +6527,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="277" t="s">
+      <c r="G15" s="267" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6548,7 +6551,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="228"/>
+      <c r="G16" s="227"/>
     </row>
     <row r="17" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="117" t="s">
@@ -6570,7 +6573,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="228"/>
+      <c r="G17" s="227"/>
     </row>
     <row r="18" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="117" t="s">
@@ -6592,7 +6595,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="228"/>
+      <c r="G18" s="227"/>
     </row>
     <row r="19" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="117" t="s">
@@ -6614,7 +6617,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="228"/>
+      <c r="G19" s="227"/>
     </row>
     <row r="20" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="117" t="s">
@@ -6636,7 +6639,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="228"/>
+      <c r="G20" s="227"/>
     </row>
     <row r="21" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="117" t="s">
@@ -6658,7 +6661,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="228"/>
+      <c r="G21" s="227"/>
     </row>
     <row r="22" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="117" t="s">
@@ -6680,7 +6683,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="138"/>
+      <c r="G22" s="152"/>
     </row>
     <row r="23" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="117" t="s">
@@ -6722,7 +6725,7 @@
       </c>
       <c r="E24" s="39">
         <f>Page2!J9</f>
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="F24" s="39" t="e">
         <f>Page2!I41</f>
@@ -6780,26 +6783,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="274" t="s">
+      <c r="A27" s="268" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="275"/>
-      <c r="C27" s="275"/>
-      <c r="D27" s="275"/>
-      <c r="E27" s="275"/>
-      <c r="F27" s="275"/>
-      <c r="G27" s="276"/>
+      <c r="B27" s="269"/>
+      <c r="C27" s="269"/>
+      <c r="D27" s="269"/>
+      <c r="E27" s="269"/>
+      <c r="F27" s="269"/>
+      <c r="G27" s="270"/>
     </row>
     <row r="28" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="258" t="s">
+      <c r="A28" s="271" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="259"/>
-      <c r="C28" s="278" t="s">
+      <c r="B28" s="272"/>
+      <c r="C28" s="273" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="279"/>
-      <c r="E28" s="280"/>
+      <c r="D28" s="274"/>
+      <c r="E28" s="275"/>
       <c r="F28" s="126" t="s">
         <v>92</v>
       </c>
@@ -6808,15 +6811,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="263" t="s">
+      <c r="A29" s="276" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="262"/>
-      <c r="C29" s="268" t="s">
+      <c r="B29" s="245"/>
+      <c r="C29" s="277" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="269"/>
-      <c r="E29" s="270"/>
+      <c r="D29" s="278"/>
+      <c r="E29" s="279"/>
       <c r="F29" s="80" t="s">
         <v>92</v>
       </c>
@@ -6825,15 +6828,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="263" t="s">
+      <c r="A30" s="276" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="262"/>
-      <c r="C30" s="268" t="s">
+      <c r="B30" s="245"/>
+      <c r="C30" s="277" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="269"/>
-      <c r="E30" s="270"/>
+      <c r="D30" s="278"/>
+      <c r="E30" s="279"/>
       <c r="F30" s="80" t="s">
         <v>92</v>
       </c>
@@ -6842,15 +6845,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="263" t="s">
+      <c r="A31" s="276" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="262"/>
-      <c r="C31" s="268" t="s">
+      <c r="B31" s="245"/>
+      <c r="C31" s="277" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="269"/>
-      <c r="E31" s="270"/>
+      <c r="D31" s="278"/>
+      <c r="E31" s="279"/>
       <c r="F31" s="80" t="s">
         <v>92</v>
       </c>
@@ -6859,15 +6862,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="263" t="s">
+      <c r="A32" s="276" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="262"/>
-      <c r="C32" s="268" t="s">
+      <c r="B32" s="245"/>
+      <c r="C32" s="277" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="269"/>
-      <c r="E32" s="270"/>
+      <c r="D32" s="278"/>
+      <c r="E32" s="279"/>
       <c r="F32" s="80" t="s">
         <v>92</v>
       </c>
@@ -6876,15 +6879,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="263" t="s">
+      <c r="A33" s="276" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="262"/>
-      <c r="C33" s="268" t="s">
+      <c r="B33" s="245"/>
+      <c r="C33" s="277" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="269"/>
-      <c r="E33" s="270"/>
+      <c r="D33" s="278"/>
+      <c r="E33" s="279"/>
       <c r="F33" s="80" t="s">
         <v>92</v>
       </c>
@@ -6893,15 +6896,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="99" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="152" t="s">
+      <c r="A34" s="143" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="153"/>
-      <c r="C34" s="271" t="s">
+      <c r="B34" s="144"/>
+      <c r="C34" s="280" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="272"/>
-      <c r="E34" s="273"/>
+      <c r="D34" s="281"/>
+      <c r="E34" s="282"/>
       <c r="F34" s="127" t="s">
         <v>92</v>
       </c>
@@ -6910,26 +6913,26 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="274" t="s">
+      <c r="A35" s="268" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="275"/>
-      <c r="C35" s="275"/>
-      <c r="D35" s="275"/>
-      <c r="E35" s="275"/>
-      <c r="F35" s="275"/>
-      <c r="G35" s="276"/>
+      <c r="B35" s="269"/>
+      <c r="C35" s="269"/>
+      <c r="D35" s="269"/>
+      <c r="E35" s="269"/>
+      <c r="F35" s="269"/>
+      <c r="G35" s="270"/>
     </row>
     <row r="36" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="148" t="s">
+      <c r="A36" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="149"/>
-      <c r="C36" s="266" t="s">
+      <c r="B36" s="140"/>
+      <c r="C36" s="286" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="267"/>
-      <c r="E36" s="149"/>
+      <c r="D36" s="287"/>
+      <c r="E36" s="140"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
       </c>
@@ -6938,15 +6941,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="258" t="s">
+      <c r="A37" s="271" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="259"/>
-      <c r="C37" s="260" t="s">
+      <c r="B37" s="272"/>
+      <c r="C37" s="244" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="261"/>
-      <c r="E37" s="262"/>
+      <c r="D37" s="283"/>
+      <c r="E37" s="245"/>
       <c r="F37" s="119" t="s">
         <v>92</v>
       </c>
@@ -6955,15 +6958,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="263" t="s">
+      <c r="A38" s="276" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="262"/>
-      <c r="C38" s="260" t="s">
+      <c r="B38" s="245"/>
+      <c r="C38" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="261"/>
-      <c r="E38" s="262"/>
+      <c r="D38" s="283"/>
+      <c r="E38" s="245"/>
       <c r="F38" s="119" t="s">
         <v>92</v>
       </c>
@@ -6972,15 +6975,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="152" t="s">
+      <c r="A39" s="143" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="153"/>
-      <c r="C39" s="264" t="s">
+      <c r="B39" s="144"/>
+      <c r="C39" s="284" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="265"/>
-      <c r="E39" s="153"/>
+      <c r="D39" s="285"/>
+      <c r="E39" s="144"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
@@ -6989,50 +6992,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="246" t="s">
+      <c r="A40" s="296" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="247"/>
-      <c r="C40" s="248" t="s">
+      <c r="B40" s="297"/>
+      <c r="C40" s="298" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="249"/>
-      <c r="E40" s="250"/>
-      <c r="F40" s="248" t="s">
+      <c r="D40" s="299"/>
+      <c r="E40" s="300"/>
+      <c r="F40" s="298" t="s">
         <v>139</v>
       </c>
-      <c r="G40" s="250"/>
+      <c r="G40" s="300"/>
     </row>
     <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="251"/>
-      <c r="B41" s="252"/>
-      <c r="C41" s="172"/>
-      <c r="D41" s="197"/>
-      <c r="E41" s="210"/>
-      <c r="F41" s="255"/>
-      <c r="G41" s="256"/>
+      <c r="A41" s="301"/>
+      <c r="B41" s="302"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="183"/>
+      <c r="F41" s="305"/>
+      <c r="G41" s="306"/>
     </row>
     <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="253"/>
-      <c r="B42" s="254"/>
-      <c r="C42" s="238" t="s">
+      <c r="A42" s="303"/>
+      <c r="B42" s="304"/>
+      <c r="C42" s="288" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="257"/>
-      <c r="E42" s="239"/>
-      <c r="F42" s="238" t="s">
+      <c r="D42" s="307"/>
+      <c r="E42" s="289"/>
+      <c r="F42" s="288" t="s">
         <v>140</v>
       </c>
-      <c r="G42" s="239"/>
+      <c r="G42" s="289"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="128"/>
       <c r="B43" s="128"/>
       <c r="C43" s="128"/>
       <c r="D43" s="128"/>
-      <c r="E43" s="245"/>
-      <c r="F43" s="245"/>
-      <c r="G43" s="245"/>
+      <c r="E43" s="295"/>
+      <c r="F43" s="295"/>
+      <c r="G43" s="295"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -7041,63 +7044,24 @@
       <c r="B44" s="129"/>
       <c r="C44" s="130"/>
       <c r="D44" s="128"/>
-      <c r="E44" s="240"/>
-      <c r="F44" s="240"/>
-      <c r="G44" s="240"/>
+      <c r="E44" s="290"/>
+      <c r="F44" s="290"/>
+      <c r="G44" s="290"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="241" t="s">
+      <c r="A46" s="291" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="241"/>
+      <c r="B46" s="291"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="241" t="s">
+      <c r="A47" s="291" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="241"/>
+      <c r="B47" s="291"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="A46:B46"/>
@@ -7114,6 +7078,45 @@
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="79" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-210W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-210W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DF15C3-7F5C-4D09-B4D7-CADAA4084D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7910EA4C-972A-4E33-A4A4-2BEF7EB76D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,9 +13,6 @@
     <sheet name="Page3" sheetId="9" r:id="rId3"/>
     <sheet name="COA Form" sheetId="10" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Page1!$A$1:$K$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Page2!$A$1:$K$47</definedName>
@@ -459,9 +456,6 @@
     <t>U-</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Opacity
 L-45.0 T-50.0 U-55.0</t>
   </si>
@@ -490,13 +484,13 @@
 L-(-16.00) T-(-11.00) U-(-6.00)</t>
   </si>
   <si>
+    <t>Reference:</t>
+  </si>
+  <si>
+    <t>Retention period: 5 years</t>
+  </si>
+  <si>
     <t>Testing Equipment Identification Number</t>
-  </si>
-  <si>
-    <t>Reference:</t>
-  </si>
-  <si>
-    <t>Retention period: 5 years</t>
   </si>
   <si>
     <t>Roll Cut Width</t>
@@ -520,6 +514,9 @@
   </si>
   <si>
     <t>#02</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1631,9 +1628,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1652,15 +1646,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1669,15 +1654,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1685,27 +1661,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="58" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1773,6 +1728,7 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1867,11 +1823,94 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="58" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1887,6 +1926,34 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1916,119 +1983,81 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2040,10 +2069,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2052,154 +2087,119 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -2234,6 +2234,15 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2327,6 +2336,12 @@
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2345,70 +2360,52 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2760,28 +2757,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Page1"/>
-      <sheetName val="Page2"/>
-      <sheetName val="Page3"/>
-      <sheetName val="COA Form"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3077,42 +3052,42 @@
   <cols>
     <col min="1" max="3" width="14" style="5" customWidth="1"/>
     <col min="4" max="11" width="21.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="132" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="132"/>
-    <col min="14" max="14" width="9.42578125" style="132" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="132"/>
+    <col min="12" max="12" width="10.5703125" style="85" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="85"/>
+    <col min="14" max="14" width="9.42578125" style="85" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="85"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3133,12 +3108,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="142"/>
+      <c r="B4" s="162"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="164"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3150,19 +3125,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="153"/>
-      <c r="K4" s="154"/>
+      <c r="J4" s="156"/>
+      <c r="K4" s="157"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="144"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="146"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="168"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3174,64 +3149,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="155"/>
-      <c r="K5" s="156"/>
+      <c r="J5" s="158"/>
+      <c r="K5" s="159"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="161" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="163"/>
+      <c r="A6" s="134" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="135"/>
+      <c r="C6" s="136"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="148"/>
-      <c r="H6" s="160"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="150"/>
+        <v>142</v>
+      </c>
+      <c r="G6" s="152"/>
+      <c r="H6" s="171"/>
+      <c r="I6" s="152"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="154"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="164" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151" t="s">
+      <c r="A7" s="137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="151" t="s">
+      <c r="E7" s="138" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="151" t="s">
+      <c r="F7" s="138" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="157" t="s">
+      <c r="G7" s="169" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="157" t="s">
+      <c r="H7" s="169" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="151" t="s">
+      <c r="I7" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="151"/>
-      <c r="K7" s="152"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="155"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="165"/>
-      <c r="B8" s="159"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="159" t="s">
+      <c r="A8" s="139"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="159"/>
-      <c r="G8" s="158"/>
-      <c r="H8" s="158"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="170"/>
+      <c r="H8" s="170"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3633,11 +3608,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="133" t="s">
+      <c r="A39" s="147" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="134"/>
-      <c r="C39" s="135"/>
+      <c r="B39" s="148"/>
+      <c r="C39" s="149"/>
       <c r="D39" s="35" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3672,11 +3647,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="169" t="s">
+      <c r="A40" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="170"/>
-      <c r="C40" s="171"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="146"/>
       <c r="D40" s="38">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3711,11 +3686,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="166" t="s">
+      <c r="A41" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="167"/>
-      <c r="C41" s="168"/>
+      <c r="B41" s="142"/>
+      <c r="C41" s="143"/>
       <c r="D41" s="41">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3756,8 +3731,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="136"/>
-      <c r="C42" s="136"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3774,8 +3749,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="137"/>
-      <c r="C43" s="137"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3784,15 +3759,15 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="147" t="s">
+      <c r="A44" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="147"/>
-      <c r="C44" s="147"/>
+      <c r="B44" s="133"/>
+      <c r="C44" s="133"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G44" s="46">
         <v>461359700</v>
@@ -3800,11 +3775,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="147" t="s">
-        <v>135</v>
-      </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="A45" s="133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3846,31 +3821,31 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
-    <mergeCell ref="A45:C45"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D9:D41">
@@ -3935,52 +3910,54 @@
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.98425196850393704" right="0.19685039370078741" top="0.11811023622047245" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="62" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr codeName="Sheet3"/>
+  <sheetPr codeName="Sheet3">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="14" style="5" customWidth="1"/>
     <col min="4" max="11" width="21.7109375" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="132"/>
+    <col min="12" max="16384" width="9.140625" style="85"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -4001,23 +3978,23 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="140">
-        <f ca="1">Page2!B4:D4</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="195">
+      <c r="B4" s="162">
+        <f>Page1!B4:D4</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="219">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="196"/>
+      <c r="D4" s="208"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="55">
-        <f ca="1">Page2!F4</f>
+      <c r="F4" s="119">
+        <f>Page1!F4</f>
         <v>0</v>
       </c>
       <c r="G4" s="9" t="s">
@@ -4030,30 +4007,30 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="191">
-        <f>Page2!K4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="192"/>
+      <c r="J4" s="220">
+        <f>Page1!J4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="221"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="144">
-        <f ca="1">Page2!B5:D5</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="145">
+      <c r="B5" s="166">
+        <f>Page1!B5:D5</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="167">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="168"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="12">
-        <f ca="1">Page2!F5</f>
+        <f>Page1!F5</f>
         <v>0</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -4066,781 +4043,772 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="193">
-        <f>Page2!K5</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="194"/>
+      <c r="J5" s="184">
+        <f>Page1!J5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="185"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="201" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="202"/>
-      <c r="C6" s="203"/>
-      <c r="D6" s="197"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="189"/>
-      <c r="H6" s="190"/>
-      <c r="I6" s="187"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="56"/>
+      <c r="A6" s="204" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="205"/>
+      <c r="C6" s="206"/>
+      <c r="D6" s="186"/>
+      <c r="E6" s="187"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="190"/>
+      <c r="H6" s="203"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="202"/>
+      <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="208" t="s">
+      <c r="A7" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="207" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="198"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="189" t="s">
-        <v>126</v>
-      </c>
-      <c r="H7" s="198"/>
-      <c r="I7" s="189" t="s">
+      <c r="E7" s="187"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="190" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="187"/>
+      <c r="I7" s="190" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" s="203"/>
+      <c r="K7" s="194" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="188"/>
+      <c r="B8" s="189"/>
+      <c r="C8" s="189"/>
+      <c r="D8" s="188" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="198" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="199" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="191"/>
+      <c r="H8" s="189"/>
+      <c r="I8" s="191" t="s">
         <v>136</v>
       </c>
-      <c r="J7" s="190"/>
-      <c r="K7" s="182" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="200"/>
-      <c r="D8" s="199" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="211" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="212" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="214"/>
-      <c r="H8" s="200"/>
-      <c r="I8" s="214" t="s">
-        <v>137</v>
-      </c>
-      <c r="J8" s="212"/>
-      <c r="K8" s="183"/>
+      <c r="J8" s="199"/>
+      <c r="K8" s="195"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="199"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="199"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="212"/>
-      <c r="G9" s="214"/>
-      <c r="H9" s="200"/>
-      <c r="I9" s="58" t="s">
+      <c r="A9" s="188"/>
+      <c r="B9" s="189"/>
+      <c r="C9" s="189"/>
+      <c r="D9" s="188"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="191"/>
+      <c r="H9" s="189"/>
+      <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="58">
         <v>210</v>
       </c>
-      <c r="K9" s="183"/>
+      <c r="K9" s="195"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="199">
+      <c r="A10" s="188"/>
+      <c r="B10" s="189"/>
+      <c r="C10" s="189"/>
+      <c r="D10" s="197"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="192"/>
+      <c r="H10" s="193"/>
+      <c r="I10" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="60">
+        <v>213</v>
+      </c>
+      <c r="K10" s="196"/>
+    </row>
+    <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="120">
         <f>Page1!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" s="200">
+      <c r="B11" s="121">
         <f>Page1!B9</f>
         <v>0</v>
       </c>
-      <c r="C10" s="200">
+      <c r="C11" s="122">
         <f>Page1!C9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="225"/>
-      <c r="E10" s="158"/>
-      <c r="F10" s="213"/>
-      <c r="G10" s="219"/>
-      <c r="H10" s="220"/>
-      <c r="I10" s="60" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" s="61">
-        <v>213</v>
-      </c>
-      <c r="K10" s="184"/>
-    </row>
-    <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62">
-        <f>Page1!A10</f>
-        <v>0</v>
-      </c>
-      <c r="B11" s="63">
-        <f>Page1!B10</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="64">
-        <f>Page1!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="D11" s="61"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="176"/>
-      <c r="H11" s="176"/>
-      <c r="I11" s="221"/>
-      <c r="J11" s="222"/>
-      <c r="K11" s="66"/>
+      <c r="G11" s="211"/>
+      <c r="H11" s="211"/>
+      <c r="I11" s="222"/>
+      <c r="J11" s="223"/>
+      <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67">
-        <f>Page1!A11</f>
-        <v>0</v>
-      </c>
-      <c r="B12" s="68">
-        <f>Page1!B11</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="69">
-        <f>Page1!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="70"/>
+      <c r="A12" s="123">
+        <f>Page1!A10</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="124">
+        <f>Page1!B10</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="125">
+        <f>Page1!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="63"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="177"/>
-      <c r="H12" s="177"/>
+      <c r="G12" s="212"/>
+      <c r="H12" s="212"/>
       <c r="I12" s="174"/>
       <c r="J12" s="175"/>
-      <c r="K12" s="71"/>
+      <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="67">
-        <f>Page1!A12</f>
-        <v>0</v>
-      </c>
-      <c r="B13" s="68">
-        <f>Page1!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="72">
-        <f>Page1!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="70"/>
+      <c r="A13" s="123">
+        <f>Page1!A11</f>
+        <v>0</v>
+      </c>
+      <c r="B13" s="124">
+        <f>Page1!B11</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="126">
+        <f>Page1!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="63"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="177"/>
-      <c r="H13" s="177"/>
+      <c r="G13" s="212"/>
+      <c r="H13" s="212"/>
       <c r="I13" s="174"/>
       <c r="J13" s="175"/>
-      <c r="K13" s="71"/>
+      <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67">
-        <f>Page1!A13</f>
-        <v>0</v>
-      </c>
-      <c r="B14" s="73">
-        <f>Page1!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="72">
-        <f>Page1!C13</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="70"/>
+      <c r="A14" s="123">
+        <f>Page1!A12</f>
+        <v>0</v>
+      </c>
+      <c r="B14" s="127">
+        <f>Page1!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="126">
+        <f>Page1!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="63"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="177"/>
+      <c r="G14" s="212"/>
+      <c r="H14" s="212"/>
       <c r="I14" s="174"/>
       <c r="J14" s="175"/>
-      <c r="K14" s="71"/>
+      <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67">
-        <f>Page1!A14</f>
-        <v>0</v>
-      </c>
-      <c r="B15" s="68">
-        <f>Page1!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="69">
-        <f>Page1!C14</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="70"/>
+      <c r="A15" s="123">
+        <f>Page1!A13</f>
+        <v>0</v>
+      </c>
+      <c r="B15" s="124">
+        <f>Page1!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="125">
+        <f>Page1!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="63"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="177"/>
-      <c r="H15" s="177"/>
+      <c r="G15" s="212"/>
+      <c r="H15" s="212"/>
       <c r="I15" s="174"/>
       <c r="J15" s="175"/>
-      <c r="K15" s="71"/>
+      <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="67">
-        <f>Page1!A15</f>
-        <v>0</v>
-      </c>
-      <c r="B16" s="68">
-        <f>Page1!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="69">
-        <f>Page1!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="65"/>
+      <c r="A16" s="123">
+        <f>Page1!A14</f>
+        <v>0</v>
+      </c>
+      <c r="B16" s="124">
+        <f>Page1!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="125">
+        <f>Page1!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="61"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="176"/>
-      <c r="H16" s="176"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
       <c r="I16" s="174"/>
       <c r="J16" s="175"/>
-      <c r="K16" s="66"/>
+      <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67">
-        <f>Page1!A16</f>
-        <v>0</v>
-      </c>
-      <c r="B17" s="68">
-        <f>Page1!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="69">
-        <f>Page1!C16</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="70"/>
+      <c r="A17" s="123">
+        <f>Page1!A15</f>
+        <v>0</v>
+      </c>
+      <c r="B17" s="124">
+        <f>Page1!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="125">
+        <f>Page1!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="63"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="177"/>
-      <c r="H17" s="177"/>
+      <c r="G17" s="212"/>
+      <c r="H17" s="212"/>
       <c r="I17" s="174"/>
       <c r="J17" s="175"/>
-      <c r="K17" s="71"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67">
-        <f>Page1!A17</f>
-        <v>0</v>
-      </c>
-      <c r="B18" s="68">
-        <f>Page1!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="69">
-        <f>Page1!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="70"/>
+      <c r="A18" s="123">
+        <f>Page1!A16</f>
+        <v>0</v>
+      </c>
+      <c r="B18" s="124">
+        <f>Page1!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="125">
+        <f>Page1!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="63"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="177"/>
-      <c r="H18" s="177"/>
+      <c r="G18" s="212"/>
+      <c r="H18" s="212"/>
       <c r="I18" s="174"/>
       <c r="J18" s="175"/>
-      <c r="K18" s="71"/>
+      <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67">
-        <f>Page1!A18</f>
-        <v>0</v>
-      </c>
-      <c r="B19" s="74">
-        <f>Page1!B18</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="69">
-        <f>Page1!C18</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="70"/>
+      <c r="A19" s="123">
+        <f>Page1!A17</f>
+        <v>0</v>
+      </c>
+      <c r="B19" s="128">
+        <f>Page1!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="125">
+        <f>Page1!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="63"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="177"/>
-      <c r="H19" s="177"/>
+      <c r="G19" s="212"/>
+      <c r="H19" s="212"/>
       <c r="I19" s="174"/>
       <c r="J19" s="175"/>
-      <c r="K19" s="71"/>
+      <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67">
-        <f>Page1!A19</f>
-        <v>0</v>
-      </c>
-      <c r="B20" s="68">
-        <f>Page1!B19</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="69">
-        <f>Page1!C19</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="70"/>
+      <c r="A20" s="123">
+        <f>Page1!A18</f>
+        <v>0</v>
+      </c>
+      <c r="B20" s="124">
+        <f>Page1!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="125">
+        <f>Page1!C18</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="63"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="172"/>
-      <c r="H20" s="173"/>
+      <c r="G20" s="209"/>
+      <c r="H20" s="210"/>
       <c r="I20" s="174"/>
       <c r="J20" s="175"/>
-      <c r="K20" s="71"/>
+      <c r="K20" s="64"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="75">
-        <f>Page1!A20</f>
-        <v>0</v>
-      </c>
-      <c r="B21" s="74">
-        <f>Page1!B20</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="72">
-        <f>Page1!C20</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="70"/>
+      <c r="A21" s="129">
+        <f>Page1!A19</f>
+        <v>0</v>
+      </c>
+      <c r="B21" s="128">
+        <f>Page1!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="126">
+        <f>Page1!C19</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="63"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="172"/>
-      <c r="H21" s="173"/>
+      <c r="G21" s="209"/>
+      <c r="H21" s="210"/>
       <c r="I21" s="174"/>
       <c r="J21" s="175"/>
-      <c r="K21" s="71"/>
+      <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67">
-        <f>Page1!A21</f>
-        <v>0</v>
-      </c>
-      <c r="B22" s="68">
-        <f>Page1!B21</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="69">
-        <f>Page1!C21</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="70"/>
+      <c r="A22" s="123">
+        <f>Page1!A20</f>
+        <v>0</v>
+      </c>
+      <c r="B22" s="124">
+        <f>Page1!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="125">
+        <f>Page1!C20</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="63"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="172"/>
-      <c r="H22" s="173"/>
+      <c r="G22" s="209"/>
+      <c r="H22" s="210"/>
       <c r="I22" s="174"/>
       <c r="J22" s="175"/>
-      <c r="K22" s="71"/>
+      <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67">
-        <f>Page1!A22</f>
-        <v>0</v>
-      </c>
-      <c r="B23" s="68">
-        <f>Page1!B22</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="72">
-        <f>Page1!C22</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="70"/>
+      <c r="A23" s="123">
+        <f>Page1!A21</f>
+        <v>0</v>
+      </c>
+      <c r="B23" s="124">
+        <f>Page1!B21</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="126">
+        <f>Page1!C21</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="63"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="172"/>
-      <c r="H23" s="173"/>
+      <c r="G23" s="209"/>
+      <c r="H23" s="210"/>
       <c r="I23" s="174"/>
       <c r="J23" s="175"/>
-      <c r="K23" s="71"/>
+      <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67">
-        <f>Page1!A23</f>
-        <v>0</v>
-      </c>
-      <c r="B24" s="73">
-        <f>Page1!B23</f>
-        <v>0</v>
-      </c>
-      <c r="C24" s="72">
-        <f>Page1!C23</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="70"/>
+      <c r="A24" s="123">
+        <f>Page1!A22</f>
+        <v>0</v>
+      </c>
+      <c r="B24" s="127">
+        <f>Page1!B22</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="126">
+        <f>Page1!C22</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="63"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="172"/>
-      <c r="H24" s="173"/>
+      <c r="G24" s="209"/>
+      <c r="H24" s="210"/>
       <c r="I24" s="174"/>
       <c r="J24" s="175"/>
-      <c r="K24" s="71"/>
+      <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="67">
-        <f>Page1!A24</f>
-        <v>0</v>
-      </c>
-      <c r="B25" s="68">
-        <f>Page1!B24</f>
-        <v>0</v>
-      </c>
-      <c r="C25" s="69">
-        <f>Page1!C24</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="70"/>
+      <c r="A25" s="123">
+        <f>Page1!A23</f>
+        <v>0</v>
+      </c>
+      <c r="B25" s="124">
+        <f>Page1!B23</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="125">
+        <f>Page1!C23</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="63"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="172"/>
-      <c r="H25" s="173"/>
+      <c r="G25" s="209"/>
+      <c r="H25" s="210"/>
       <c r="I25" s="174"/>
       <c r="J25" s="175"/>
-      <c r="K25" s="71"/>
+      <c r="K25" s="64"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67">
-        <f>Page1!A25</f>
-        <v>0</v>
-      </c>
-      <c r="B26" s="68">
-        <f>Page1!B25</f>
-        <v>0</v>
-      </c>
-      <c r="C26" s="69">
-        <f>Page1!C25</f>
-        <v>0</v>
-      </c>
-      <c r="D26" s="70"/>
+      <c r="A26" s="123">
+        <f>Page1!A24</f>
+        <v>0</v>
+      </c>
+      <c r="B26" s="124">
+        <f>Page1!B24</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="125">
+        <f>Page1!C24</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="63"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="172"/>
-      <c r="H26" s="173"/>
+      <c r="G26" s="209"/>
+      <c r="H26" s="210"/>
       <c r="I26" s="174"/>
       <c r="J26" s="175"/>
-      <c r="K26" s="71"/>
+      <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="67">
-        <f>Page1!A26</f>
-        <v>0</v>
-      </c>
-      <c r="B27" s="68">
-        <f>Page1!B26</f>
-        <v>0</v>
-      </c>
-      <c r="C27" s="69">
-        <f>Page1!C26</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="70"/>
+      <c r="A27" s="123">
+        <f>Page1!A25</f>
+        <v>0</v>
+      </c>
+      <c r="B27" s="124">
+        <f>Page1!B25</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="125">
+        <f>Page1!C25</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="63"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="172"/>
-      <c r="H27" s="173"/>
+      <c r="G27" s="209"/>
+      <c r="H27" s="210"/>
       <c r="I27" s="174"/>
       <c r="J27" s="175"/>
-      <c r="K27" s="71"/>
+      <c r="K27" s="64"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="67">
-        <f>Page1!A27</f>
-        <v>0</v>
-      </c>
-      <c r="B28" s="68">
-        <f>Page1!B27</f>
-        <v>0</v>
-      </c>
-      <c r="C28" s="69">
-        <f>Page1!C27</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="70"/>
+      <c r="A28" s="123">
+        <f>Page1!A26</f>
+        <v>0</v>
+      </c>
+      <c r="B28" s="124">
+        <f>Page1!B26</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="125">
+        <f>Page1!C26</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="63"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="172"/>
-      <c r="H28" s="173"/>
+      <c r="G28" s="209"/>
+      <c r="H28" s="210"/>
       <c r="I28" s="174"/>
       <c r="J28" s="175"/>
-      <c r="K28" s="71"/>
+      <c r="K28" s="64"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67">
-        <f>Page1!A28</f>
-        <v>0</v>
-      </c>
-      <c r="B29" s="74">
-        <f>Page1!B28</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="69">
-        <f>Page1!C28</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="70"/>
+      <c r="A29" s="123">
+        <f>Page1!A27</f>
+        <v>0</v>
+      </c>
+      <c r="B29" s="128">
+        <f>Page1!B27</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="125">
+        <f>Page1!C27</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="63"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="173"/>
+      <c r="G29" s="209"/>
+      <c r="H29" s="210"/>
       <c r="I29" s="174"/>
       <c r="J29" s="175"/>
-      <c r="K29" s="71"/>
+      <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="67">
-        <f>Page1!A29</f>
-        <v>0</v>
-      </c>
-      <c r="B30" s="68">
-        <f>Page1!B29</f>
-        <v>0</v>
-      </c>
-      <c r="C30" s="69">
-        <f>Page1!C29</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="70"/>
+      <c r="A30" s="123">
+        <f>Page1!A28</f>
+        <v>0</v>
+      </c>
+      <c r="B30" s="124">
+        <f>Page1!B28</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="125">
+        <f>Page1!C28</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="63"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="172"/>
-      <c r="H30" s="173"/>
+      <c r="G30" s="209"/>
+      <c r="H30" s="210"/>
       <c r="I30" s="174"/>
       <c r="J30" s="175"/>
-      <c r="K30" s="71"/>
+      <c r="K30" s="64"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="75">
-        <f>Page1!A30</f>
-        <v>0</v>
-      </c>
-      <c r="B31" s="74">
-        <f>Page1!B30</f>
-        <v>0</v>
-      </c>
-      <c r="C31" s="72">
-        <f>Page1!C30</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="70"/>
+      <c r="A31" s="129">
+        <f>Page1!A29</f>
+        <v>0</v>
+      </c>
+      <c r="B31" s="128">
+        <f>Page1!B29</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="126">
+        <f>Page1!C29</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="63"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="172"/>
-      <c r="H31" s="173"/>
+      <c r="G31" s="209"/>
+      <c r="H31" s="210"/>
       <c r="I31" s="174"/>
       <c r="J31" s="175"/>
-      <c r="K31" s="71"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="67">
-        <f>Page1!A31</f>
-        <v>0</v>
-      </c>
-      <c r="B32" s="68">
-        <f>Page1!B31</f>
-        <v>0</v>
-      </c>
-      <c r="C32" s="69">
-        <f>Page1!C31</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="70"/>
+      <c r="A32" s="123">
+        <f>Page1!A30</f>
+        <v>0</v>
+      </c>
+      <c r="B32" s="124">
+        <f>Page1!B30</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="125">
+        <f>Page1!C30</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="63"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="172"/>
-      <c r="H32" s="173"/>
+      <c r="G32" s="209"/>
+      <c r="H32" s="210"/>
       <c r="I32" s="174"/>
       <c r="J32" s="175"/>
-      <c r="K32" s="71"/>
+      <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="67">
-        <f>Page1!A32</f>
-        <v>0</v>
-      </c>
-      <c r="B33" s="68">
-        <f>Page1!B32</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="72">
-        <f>Page1!C32</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="70"/>
+      <c r="A33" s="123">
+        <f>Page1!A31</f>
+        <v>0</v>
+      </c>
+      <c r="B33" s="124">
+        <f>Page1!B31</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="126">
+        <f>Page1!C31</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="63"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="172"/>
-      <c r="H33" s="173"/>
+      <c r="G33" s="209"/>
+      <c r="H33" s="210"/>
       <c r="I33" s="174"/>
       <c r="J33" s="175"/>
-      <c r="K33" s="71"/>
+      <c r="K33" s="64"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67">
-        <f>Page1!A33</f>
-        <v>0</v>
-      </c>
-      <c r="B34" s="73">
-        <f>Page1!B33</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="72">
-        <f>Page1!C33</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="70"/>
+      <c r="A34" s="123">
+        <f>Page1!A32</f>
+        <v>0</v>
+      </c>
+      <c r="B34" s="127">
+        <f>Page1!B32</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="126">
+        <f>Page1!C32</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="63"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="172"/>
-      <c r="H34" s="173"/>
+      <c r="G34" s="209"/>
+      <c r="H34" s="210"/>
       <c r="I34" s="174"/>
       <c r="J34" s="175"/>
-      <c r="K34" s="71"/>
+      <c r="K34" s="64"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="67">
-        <f>Page1!A34</f>
-        <v>0</v>
-      </c>
-      <c r="B35" s="68">
-        <f>Page1!B34</f>
-        <v>0</v>
-      </c>
-      <c r="C35" s="69">
-        <f>Page1!C34</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="70"/>
+      <c r="A35" s="123">
+        <f>Page1!A33</f>
+        <v>0</v>
+      </c>
+      <c r="B35" s="124">
+        <f>Page1!B33</f>
+        <v>0</v>
+      </c>
+      <c r="C35" s="125">
+        <f>Page1!C33</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="63"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="172"/>
-      <c r="H35" s="173"/>
+      <c r="G35" s="209"/>
+      <c r="H35" s="210"/>
       <c r="I35" s="174"/>
       <c r="J35" s="175"/>
-      <c r="K35" s="71"/>
+      <c r="K35" s="64"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="67">
-        <f>Page1!A35</f>
-        <v>0</v>
-      </c>
-      <c r="B36" s="68">
-        <f>Page1!B35</f>
-        <v>0</v>
-      </c>
-      <c r="C36" s="69">
-        <f>Page1!C35</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="70"/>
+      <c r="A36" s="123">
+        <f>Page1!A34</f>
+        <v>0</v>
+      </c>
+      <c r="B36" s="124">
+        <f>Page1!B34</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="125">
+        <f>Page1!C34</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="63"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="172"/>
-      <c r="H36" s="173"/>
+      <c r="G36" s="209"/>
+      <c r="H36" s="210"/>
       <c r="I36" s="174"/>
       <c r="J36" s="175"/>
-      <c r="K36" s="71"/>
+      <c r="K36" s="64"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="67">
-        <f>[1]Page1!A35</f>
-        <v>0</v>
-      </c>
-      <c r="B37" s="68">
-        <f>[1]Page1!B35</f>
-        <v>0</v>
-      </c>
-      <c r="C37" s="69">
-        <f>[1]Page1!C35</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="70"/>
+      <c r="A37" s="123">
+        <f>Page1!A35</f>
+        <v>0</v>
+      </c>
+      <c r="B37" s="124">
+        <f>Page1!B35</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="125">
+        <f>Page1!C35</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="63"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="172"/>
-      <c r="H37" s="173"/>
+      <c r="G37" s="209"/>
+      <c r="H37" s="210"/>
       <c r="I37" s="174"/>
       <c r="J37" s="175"/>
-      <c r="K37" s="71"/>
+      <c r="K37" s="64"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="67">
-        <f>[1]Page1!A36</f>
-        <v>0</v>
-      </c>
-      <c r="B38" s="68">
-        <f>[1]Page1!B36</f>
-        <v>0</v>
-      </c>
-      <c r="C38" s="69">
-        <f>[1]Page1!C36</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="70"/>
+      <c r="A38" s="123">
+        <f>Page1!A36</f>
+        <v>0</v>
+      </c>
+      <c r="B38" s="124">
+        <f>Page1!B36</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="125">
+        <f>Page1!C36</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="63"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="172"/>
-      <c r="H38" s="173"/>
+      <c r="G38" s="209"/>
+      <c r="H38" s="210"/>
       <c r="I38" s="174"/>
       <c r="J38" s="175"/>
-      <c r="K38" s="71"/>
+      <c r="K38" s="64"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="67">
-        <f>[1]Page1!A37</f>
-        <v>0</v>
-      </c>
-      <c r="B39" s="68">
-        <f>[1]Page1!B37</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="69">
-        <f>[1]Page1!C37</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="70"/>
+      <c r="A39" s="123">
+        <f>Page1!A37</f>
+        <v>0</v>
+      </c>
+      <c r="B39" s="124">
+        <f>Page1!B37</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="125">
+        <f>Page1!C37</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="63"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="172"/>
-      <c r="H39" s="173"/>
+      <c r="G39" s="209"/>
+      <c r="H39" s="210"/>
       <c r="I39" s="174"/>
       <c r="J39" s="175"/>
-      <c r="K39" s="71"/>
+      <c r="K39" s="64"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="76">
-        <f>[1]Page1!A38</f>
-        <v>0</v>
-      </c>
-      <c r="B40" s="77">
-        <f>[1]Page1!B38</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="78">
-        <f>[1]Page1!C38</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="70"/>
+      <c r="A40" s="130">
+        <f>Page1!A38</f>
+        <v>0</v>
+      </c>
+      <c r="B40" s="131">
+        <f>Page1!B38</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="132">
+        <f>Page1!C38</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="63"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="177"/>
-      <c r="H40" s="177"/>
+      <c r="G40" s="212"/>
+      <c r="H40" s="212"/>
       <c r="I40" s="174"/>
       <c r="J40" s="175"/>
-      <c r="K40" s="71"/>
+      <c r="K40" s="64"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="209" t="s">
+      <c r="A41" s="215" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="210"/>
-      <c r="C41" s="210"/>
-      <c r="D41" s="79" t="e">
+      <c r="B41" s="216"/>
+      <c r="C41" s="216"/>
+      <c r="D41" s="65" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
       </c>
@@ -4852,28 +4820,28 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="180" t="e">
+      <c r="G41" s="213" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="181"/>
-      <c r="I41" s="223" t="e">
+      <c r="H41" s="214"/>
+      <c r="I41" s="176" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="224"/>
+      <c r="J41" s="177"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="204" t="s">
+      <c r="A42" s="217" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="205"/>
-      <c r="C42" s="205"/>
-      <c r="D42" s="80">
+      <c r="B42" s="218"/>
+      <c r="C42" s="218"/>
+      <c r="D42" s="66">
         <f>MIN(D11:D40)</f>
         <v>0</v>
       </c>
@@ -4885,50 +4853,50 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="178">
+      <c r="G42" s="224">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="179"/>
-      <c r="I42" s="185">
+      <c r="H42" s="225"/>
+      <c r="I42" s="172">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="186"/>
+      <c r="J42" s="173"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="206" t="s">
+      <c r="A43" s="182" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="207"/>
-      <c r="C43" s="207"/>
-      <c r="D43" s="81">
+      <c r="B43" s="183"/>
+      <c r="C43" s="183"/>
+      <c r="D43" s="67">
         <f>MAX(D11:D40)</f>
         <v>0</v>
       </c>
-      <c r="E43" s="82">
+      <c r="E43" s="68">
         <f>MAX(E11:E40)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="82">
+      <c r="F43" s="68">
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="215">
+      <c r="G43" s="178">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="216"/>
-      <c r="I43" s="217">
+      <c r="H43" s="179"/>
+      <c r="I43" s="180">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="218"/>
-      <c r="K43" s="83">
+      <c r="J43" s="181"/>
+      <c r="K43" s="69">
         <f>MAX(K11:K40)</f>
         <v>0</v>
       </c>
@@ -4937,8 +4905,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="136"/>
-      <c r="C44" s="136"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4955,8 +4923,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="137"/>
-      <c r="C45" s="137"/>
+      <c r="B45" s="151"/>
+      <c r="C45" s="151"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4965,15 +4933,15 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="147" t="s">
+      <c r="A46" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="147"/>
-      <c r="C46" s="147"/>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G46" s="46">
         <f>Page1!G44</f>
@@ -4982,11 +4950,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="147" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" s="147"/>
-      <c r="C47" s="147"/>
+      <c r="A47" s="133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="133"/>
+      <c r="C47" s="133"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -5010,99 +4978,56 @@
       <c r="K48" s="54"/>
     </row>
     <row r="51" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I51" s="84"/>
+      <c r="I51" s="70"/>
     </row>
     <row r="52" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I52" s="84"/>
+      <c r="I52" s="70"/>
     </row>
     <row r="53" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I53" s="84"/>
+      <c r="I53" s="70"/>
     </row>
     <row r="54" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I54" s="84"/>
+      <c r="I54" s="70"/>
     </row>
     <row r="55" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I55" s="84"/>
+      <c r="I55" s="70"/>
     </row>
     <row r="56" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I56" s="84"/>
+      <c r="I56" s="70"/>
     </row>
     <row r="57" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I57" s="84"/>
+      <c r="I57" s="70"/>
     </row>
     <row r="58" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I58" s="84"/>
+      <c r="I58" s="70"/>
     </row>
     <row r="59" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I59" s="84"/>
+      <c r="I59" s="70"/>
     </row>
     <row r="60" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I60" s="84"/>
+      <c r="I60" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I41:J41"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="I39:J39"/>
     <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G28:H28"/>
     <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="I18:J18"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="G22:H22"/>
@@ -5110,18 +5035,50 @@
     <mergeCell ref="G24:H24"/>
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
     <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I18:J18"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G36:H36"/>
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="G16:H16"/>
     <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="I21:J21"/>
@@ -5135,6 +5092,17 @@
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
@@ -5171,8 +5139,8 @@
       <formula>410</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="1.1811023622047245" right="0.39370078740157483" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5186,39 +5154,39 @@
   <cols>
     <col min="1" max="3" width="14" style="5" customWidth="1"/>
     <col min="4" max="11" width="21.7109375" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="132"/>
+    <col min="12" max="16384" width="9.140625" style="85"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="138"/>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="160"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="160"/>
+      <c r="J1" s="160"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="160" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5239,23 +5207,23 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="161" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="140">
-        <f ca="1">Page2!B4:D4</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="195">
+      <c r="B4" s="162">
+        <f>Page1!B4:D4</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="219">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="196"/>
+      <c r="D4" s="208"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="55">
-        <f ca="1">Page2!F4</f>
+      <c r="F4" s="119">
+        <f>Page1!F4</f>
         <v>0</v>
       </c>
       <c r="G4" s="9" t="s">
@@ -5268,30 +5236,30 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="191">
-        <f>Page2!K4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="192"/>
+      <c r="J4" s="220">
+        <f>Page1!J4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="221"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="144">
-        <f ca="1">Page2!B5:D5</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="145">
+      <c r="B5" s="166">
+        <f>Page1!B5:D5</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="167">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="146"/>
+      <c r="D5" s="168"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F5" s="12">
-        <f ca="1">Page2!F5</f>
+        <f>Page1!F5</f>
         <v>0</v>
       </c>
       <c r="G5" s="13" t="s">
@@ -5304,739 +5272,739 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="193">
-        <f>Page2!K5</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="194"/>
+      <c r="J5" s="184">
+        <f>Page1!J5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="185"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="229" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" s="230"/>
       <c r="C6" s="231"/>
       <c r="D6" s="232"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="160"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="198"/>
-      <c r="K6" s="182"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="171"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="186"/>
+      <c r="J6" s="187"/>
+      <c r="K6" s="194"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="208" t="s">
+      <c r="A7" s="186" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="187"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="207" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="233"/>
       <c r="F7" s="233"/>
-      <c r="G7" s="196"/>
+      <c r="G7" s="208"/>
       <c r="H7" s="226" t="s">
-        <v>127</v>
-      </c>
-      <c r="I7" s="199"/>
-      <c r="J7" s="200"/>
-      <c r="K7" s="183"/>
+        <v>126</v>
+      </c>
+      <c r="I7" s="188"/>
+      <c r="J7" s="189"/>
+      <c r="K7" s="195"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="200"/>
+      <c r="A8" s="188"/>
+      <c r="B8" s="189"/>
+      <c r="C8" s="189"/>
       <c r="D8" s="236" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="198" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="211" t="s">
+      <c r="F8" s="198" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="211" t="s">
-        <v>132</v>
-      </c>
-      <c r="G8" s="211" t="s">
-        <v>129</v>
+      <c r="G8" s="198" t="s">
+        <v>128</v>
       </c>
       <c r="H8" s="227"/>
-      <c r="I8" s="199"/>
-      <c r="J8" s="200"/>
-      <c r="K8" s="183"/>
+      <c r="I8" s="188"/>
+      <c r="J8" s="189"/>
+      <c r="K8" s="195"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
+      <c r="A9" s="188"/>
+      <c r="B9" s="189"/>
+      <c r="C9" s="189"/>
       <c r="D9" s="237"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="158"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="170"/>
+      <c r="G9" s="170"/>
       <c r="H9" s="228"/>
-      <c r="I9" s="199"/>
-      <c r="J9" s="200"/>
-      <c r="K9" s="183"/>
+      <c r="I9" s="188"/>
+      <c r="J9" s="189"/>
+      <c r="K9" s="195"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62">
+      <c r="A10" s="120">
         <f>Page1!A9</f>
         <v>0</v>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="121">
         <f>Page1!B9</f>
         <v>0</v>
       </c>
-      <c r="C10" s="64">
+      <c r="C10" s="122">
         <f>Page1!C9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="86"/>
+      <c r="D10" s="72"/>
       <c r="E10" s="23"/>
       <c r="F10" s="23"/>
-      <c r="G10" s="87"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="199"/>
-      <c r="J10" s="200"/>
-      <c r="K10" s="183"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="188"/>
+      <c r="J10" s="189"/>
+      <c r="K10" s="195"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67">
+      <c r="A11" s="123">
         <f>Page1!A10</f>
         <v>0</v>
       </c>
-      <c r="B11" s="68">
+      <c r="B11" s="124">
         <f>Page1!B10</f>
         <v>0</v>
       </c>
-      <c r="C11" s="69">
+      <c r="C11" s="125">
         <f>Page1!C10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="89"/>
+      <c r="D11" s="75"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="200"/>
-      <c r="K11" s="183"/>
+      <c r="G11" s="76"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="188"/>
+      <c r="J11" s="189"/>
+      <c r="K11" s="195"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="67">
+      <c r="A12" s="123">
         <f>Page1!A11</f>
         <v>0</v>
       </c>
-      <c r="B12" s="68">
+      <c r="B12" s="124">
         <f>Page1!B11</f>
         <v>0</v>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="126">
         <f>Page1!C11</f>
         <v>0</v>
       </c>
-      <c r="D12" s="89"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="199"/>
-      <c r="J12" s="200"/>
-      <c r="K12" s="183"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="188"/>
+      <c r="J12" s="189"/>
+      <c r="K12" s="195"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="67">
+      <c r="A13" s="123">
         <f>Page1!A12</f>
         <v>0</v>
       </c>
-      <c r="B13" s="73">
+      <c r="B13" s="127">
         <f>Page1!B12</f>
         <v>0</v>
       </c>
-      <c r="C13" s="72">
+      <c r="C13" s="126">
         <f>Page1!C12</f>
         <v>0</v>
       </c>
-      <c r="D13" s="86"/>
+      <c r="D13" s="72"/>
       <c r="E13" s="23"/>
       <c r="F13" s="23"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="199"/>
-      <c r="J13" s="200"/>
-      <c r="K13" s="183"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="188"/>
+      <c r="J13" s="189"/>
+      <c r="K13" s="195"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67">
+      <c r="A14" s="123">
         <f>Page1!A13</f>
         <v>0</v>
       </c>
-      <c r="B14" s="68">
+      <c r="B14" s="124">
         <f>Page1!B13</f>
         <v>0</v>
       </c>
-      <c r="C14" s="69">
+      <c r="C14" s="125">
         <f>Page1!C13</f>
         <v>0</v>
       </c>
-      <c r="D14" s="89"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="26"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="199"/>
-      <c r="J14" s="200"/>
-      <c r="K14" s="183"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="188"/>
+      <c r="J14" s="189"/>
+      <c r="K14" s="195"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67">
+      <c r="A15" s="123">
         <f>Page1!A14</f>
         <v>0</v>
       </c>
-      <c r="B15" s="68">
+      <c r="B15" s="124">
         <f>Page1!B14</f>
         <v>0</v>
       </c>
-      <c r="C15" s="69">
+      <c r="C15" s="125">
         <f>Page1!C14</f>
         <v>0</v>
       </c>
-      <c r="D15" s="89"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="26"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="199"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="183"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="188"/>
+      <c r="J15" s="189"/>
+      <c r="K15" s="195"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="67">
+      <c r="A16" s="123">
         <f>Page1!A15</f>
         <v>0</v>
       </c>
-      <c r="B16" s="68">
+      <c r="B16" s="124">
         <f>Page1!B15</f>
         <v>0</v>
       </c>
-      <c r="C16" s="69">
+      <c r="C16" s="125">
         <f>Page1!C15</f>
         <v>0</v>
       </c>
-      <c r="D16" s="89"/>
+      <c r="D16" s="75"/>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
-      <c r="G16" s="90"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="199"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="183"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="188"/>
+      <c r="J16" s="189"/>
+      <c r="K16" s="195"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67">
+      <c r="A17" s="123">
         <f>Page1!A16</f>
         <v>0</v>
       </c>
-      <c r="B17" s="68">
+      <c r="B17" s="124">
         <f>Page1!B16</f>
         <v>0</v>
       </c>
-      <c r="C17" s="69">
+      <c r="C17" s="125">
         <f>Page1!C16</f>
         <v>0</v>
       </c>
-      <c r="D17" s="89"/>
+      <c r="D17" s="75"/>
       <c r="E17" s="26"/>
       <c r="F17" s="26"/>
-      <c r="G17" s="90"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="199"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="183"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="188"/>
+      <c r="J17" s="189"/>
+      <c r="K17" s="195"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67">
+      <c r="A18" s="123">
         <f>Page1!A17</f>
         <v>0</v>
       </c>
-      <c r="B18" s="74">
+      <c r="B18" s="128">
         <f>Page1!B17</f>
         <v>0</v>
       </c>
-      <c r="C18" s="69">
+      <c r="C18" s="125">
         <f>Page1!C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="89"/>
+      <c r="D18" s="75"/>
       <c r="E18" s="26"/>
       <c r="F18" s="26"/>
-      <c r="G18" s="90"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="199"/>
-      <c r="J18" s="200"/>
-      <c r="K18" s="183"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="188"/>
+      <c r="J18" s="189"/>
+      <c r="K18" s="195"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67">
+      <c r="A19" s="123">
         <f>Page1!A18</f>
         <v>0</v>
       </c>
-      <c r="B19" s="68">
+      <c r="B19" s="124">
         <f>Page1!B18</f>
         <v>0</v>
       </c>
-      <c r="C19" s="69">
+      <c r="C19" s="125">
         <f>Page1!C18</f>
         <v>0</v>
       </c>
-      <c r="D19" s="89"/>
+      <c r="D19" s="75"/>
       <c r="E19" s="26"/>
       <c r="F19" s="26"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="91"/>
-      <c r="I19" s="199"/>
-      <c r="J19" s="200"/>
-      <c r="K19" s="183"/>
+      <c r="G19" s="76"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="188"/>
+      <c r="J19" s="189"/>
+      <c r="K19" s="195"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="75">
+      <c r="A20" s="129">
         <f>Page1!A19</f>
         <v>0</v>
       </c>
-      <c r="B20" s="74">
+      <c r="B20" s="128">
         <f>Page1!B19</f>
         <v>0</v>
       </c>
-      <c r="C20" s="72">
+      <c r="C20" s="126">
         <f>Page1!C19</f>
         <v>0</v>
       </c>
-      <c r="D20" s="89"/>
+      <c r="D20" s="75"/>
       <c r="E20" s="26"/>
       <c r="F20" s="26"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="199"/>
-      <c r="J20" s="200"/>
-      <c r="K20" s="183"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="188"/>
+      <c r="J20" s="189"/>
+      <c r="K20" s="195"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="67">
+      <c r="A21" s="123">
         <f>Page1!A20</f>
         <v>0</v>
       </c>
-      <c r="B21" s="68">
+      <c r="B21" s="124">
         <f>Page1!B20</f>
         <v>0</v>
       </c>
-      <c r="C21" s="69">
+      <c r="C21" s="125">
         <f>Page1!C20</f>
         <v>0</v>
       </c>
-      <c r="D21" s="89"/>
+      <c r="D21" s="75"/>
       <c r="E21" s="26"/>
       <c r="F21" s="26"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="199"/>
-      <c r="J21" s="200"/>
-      <c r="K21" s="183"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="188"/>
+      <c r="J21" s="189"/>
+      <c r="K21" s="195"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="67">
+      <c r="A22" s="123">
         <f>Page1!A21</f>
         <v>0</v>
       </c>
-      <c r="B22" s="68">
+      <c r="B22" s="124">
         <f>Page1!B21</f>
         <v>0</v>
       </c>
-      <c r="C22" s="72">
+      <c r="C22" s="126">
         <f>Page1!C21</f>
         <v>0</v>
       </c>
-      <c r="D22" s="89"/>
+      <c r="D22" s="75"/>
       <c r="E22" s="26"/>
       <c r="F22" s="26"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="199"/>
-      <c r="J22" s="200"/>
-      <c r="K22" s="183"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="188"/>
+      <c r="J22" s="189"/>
+      <c r="K22" s="195"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="67">
+      <c r="A23" s="123">
         <f>Page1!A22</f>
         <v>0</v>
       </c>
-      <c r="B23" s="73">
+      <c r="B23" s="127">
         <f>Page1!B22</f>
         <v>0</v>
       </c>
-      <c r="C23" s="72">
+      <c r="C23" s="126">
         <f>Page1!C22</f>
         <v>0</v>
       </c>
-      <c r="D23" s="89"/>
+      <c r="D23" s="75"/>
       <c r="E23" s="26"/>
       <c r="F23" s="26"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="199"/>
-      <c r="J23" s="200"/>
-      <c r="K23" s="183"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="188"/>
+      <c r="J23" s="189"/>
+      <c r="K23" s="195"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="67">
+      <c r="A24" s="123">
         <f>Page1!A23</f>
         <v>0</v>
       </c>
-      <c r="B24" s="68">
+      <c r="B24" s="124">
         <f>Page1!B23</f>
         <v>0</v>
       </c>
-      <c r="C24" s="69">
+      <c r="C24" s="125">
         <f>Page1!C23</f>
         <v>0</v>
       </c>
-      <c r="D24" s="89"/>
+      <c r="D24" s="75"/>
       <c r="E24" s="26"/>
       <c r="F24" s="26"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="199"/>
-      <c r="J24" s="200"/>
-      <c r="K24" s="183"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="188"/>
+      <c r="J24" s="189"/>
+      <c r="K24" s="195"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="67">
+      <c r="A25" s="123">
         <f>Page1!A24</f>
         <v>0</v>
       </c>
-      <c r="B25" s="68">
+      <c r="B25" s="124">
         <f>Page1!B24</f>
         <v>0</v>
       </c>
-      <c r="C25" s="69">
+      <c r="C25" s="125">
         <f>Page1!C24</f>
         <v>0</v>
       </c>
-      <c r="D25" s="89"/>
+      <c r="D25" s="75"/>
       <c r="E25" s="26"/>
       <c r="F25" s="26"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="91"/>
-      <c r="I25" s="199"/>
-      <c r="J25" s="200"/>
-      <c r="K25" s="183"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="188"/>
+      <c r="J25" s="189"/>
+      <c r="K25" s="195"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="67">
+      <c r="A26" s="123">
         <f>Page1!A25</f>
         <v>0</v>
       </c>
-      <c r="B26" s="68">
+      <c r="B26" s="124">
         <f>Page1!B25</f>
         <v>0</v>
       </c>
-      <c r="C26" s="69">
+      <c r="C26" s="125">
         <f>Page1!C25</f>
         <v>0</v>
       </c>
-      <c r="D26" s="89"/>
+      <c r="D26" s="75"/>
       <c r="E26" s="26"/>
       <c r="F26" s="26"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="199"/>
-      <c r="J26" s="200"/>
-      <c r="K26" s="183"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="188"/>
+      <c r="J26" s="189"/>
+      <c r="K26" s="195"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="67">
+      <c r="A27" s="123">
         <f>Page1!A26</f>
         <v>0</v>
       </c>
-      <c r="B27" s="68">
+      <c r="B27" s="124">
         <f>Page1!B26</f>
         <v>0</v>
       </c>
-      <c r="C27" s="69">
+      <c r="C27" s="125">
         <f>Page1!C26</f>
         <v>0</v>
       </c>
-      <c r="D27" s="89"/>
+      <c r="D27" s="75"/>
       <c r="E27" s="26"/>
       <c r="F27" s="26"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="199"/>
-      <c r="J27" s="200"/>
-      <c r="K27" s="183"/>
+      <c r="G27" s="76"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="188"/>
+      <c r="J27" s="189"/>
+      <c r="K27" s="195"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="67">
+      <c r="A28" s="123">
         <f>Page1!A27</f>
         <v>0</v>
       </c>
-      <c r="B28" s="74">
+      <c r="B28" s="128">
         <f>Page1!B27</f>
         <v>0</v>
       </c>
-      <c r="C28" s="69">
+      <c r="C28" s="125">
         <f>Page1!C27</f>
         <v>0</v>
       </c>
-      <c r="D28" s="89"/>
+      <c r="D28" s="75"/>
       <c r="E28" s="26"/>
       <c r="F28" s="26"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="199"/>
-      <c r="J28" s="200"/>
-      <c r="K28" s="183"/>
+      <c r="G28" s="76"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="188"/>
+      <c r="J28" s="189"/>
+      <c r="K28" s="195"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="67">
+      <c r="A29" s="123">
         <f>Page1!A28</f>
         <v>0</v>
       </c>
-      <c r="B29" s="68">
+      <c r="B29" s="124">
         <f>Page1!B28</f>
         <v>0</v>
       </c>
-      <c r="C29" s="69">
+      <c r="C29" s="125">
         <f>Page1!C28</f>
         <v>0</v>
       </c>
-      <c r="D29" s="89"/>
+      <c r="D29" s="75"/>
       <c r="E29" s="26"/>
       <c r="F29" s="26"/>
-      <c r="G29" s="90"/>
-      <c r="H29" s="91"/>
-      <c r="I29" s="199"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="183"/>
+      <c r="G29" s="76"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="188"/>
+      <c r="J29" s="189"/>
+      <c r="K29" s="195"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="75">
+      <c r="A30" s="129">
         <f>Page1!A29</f>
         <v>0</v>
       </c>
-      <c r="B30" s="74">
+      <c r="B30" s="128">
         <f>Page1!B29</f>
         <v>0</v>
       </c>
-      <c r="C30" s="72">
+      <c r="C30" s="126">
         <f>Page1!C29</f>
         <v>0</v>
       </c>
-      <c r="D30" s="89"/>
+      <c r="D30" s="75"/>
       <c r="E30" s="26"/>
       <c r="F30" s="26"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="91"/>
-      <c r="I30" s="199"/>
-      <c r="J30" s="200"/>
-      <c r="K30" s="183"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="188"/>
+      <c r="J30" s="189"/>
+      <c r="K30" s="195"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="67">
+      <c r="A31" s="123">
         <f>Page1!A30</f>
         <v>0</v>
       </c>
-      <c r="B31" s="68">
+      <c r="B31" s="124">
         <f>Page1!B30</f>
         <v>0</v>
       </c>
-      <c r="C31" s="69">
+      <c r="C31" s="125">
         <f>Page1!C30</f>
         <v>0</v>
       </c>
-      <c r="D31" s="89"/>
+      <c r="D31" s="75"/>
       <c r="E31" s="26"/>
       <c r="F31" s="26"/>
-      <c r="G31" s="90"/>
-      <c r="H31" s="91"/>
-      <c r="I31" s="199"/>
-      <c r="J31" s="200"/>
-      <c r="K31" s="183"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="188"/>
+      <c r="J31" s="189"/>
+      <c r="K31" s="195"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="67">
+      <c r="A32" s="123">
         <f>Page1!A31</f>
         <v>0</v>
       </c>
-      <c r="B32" s="68">
+      <c r="B32" s="124">
         <f>Page1!B31</f>
         <v>0</v>
       </c>
-      <c r="C32" s="72">
+      <c r="C32" s="126">
         <f>Page1!C31</f>
         <v>0</v>
       </c>
-      <c r="D32" s="89"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="26"/>
       <c r="F32" s="26"/>
-      <c r="G32" s="90"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="199"/>
-      <c r="J32" s="200"/>
-      <c r="K32" s="183"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="188"/>
+      <c r="J32" s="189"/>
+      <c r="K32" s="195"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="67">
+      <c r="A33" s="123">
         <f>Page1!A32</f>
         <v>0</v>
       </c>
-      <c r="B33" s="73">
+      <c r="B33" s="127">
         <f>Page1!B32</f>
         <v>0</v>
       </c>
-      <c r="C33" s="72">
+      <c r="C33" s="126">
         <f>Page1!C32</f>
         <v>0</v>
       </c>
-      <c r="D33" s="89"/>
+      <c r="D33" s="75"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
-      <c r="G33" s="90"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="199"/>
-      <c r="J33" s="200"/>
-      <c r="K33" s="183"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="188"/>
+      <c r="J33" s="189"/>
+      <c r="K33" s="195"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="67">
+      <c r="A34" s="123">
         <f>Page1!A33</f>
         <v>0</v>
       </c>
-      <c r="B34" s="68">
+      <c r="B34" s="124">
         <f>Page1!B33</f>
         <v>0</v>
       </c>
-      <c r="C34" s="69">
+      <c r="C34" s="125">
         <f>Page1!C33</f>
         <v>0</v>
       </c>
-      <c r="D34" s="89"/>
+      <c r="D34" s="75"/>
       <c r="E34" s="26"/>
       <c r="F34" s="26"/>
-      <c r="G34" s="90"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="199"/>
-      <c r="J34" s="200"/>
-      <c r="K34" s="183"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="188"/>
+      <c r="J34" s="189"/>
+      <c r="K34" s="195"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="67">
+      <c r="A35" s="123">
         <f>Page1!A34</f>
         <v>0</v>
       </c>
-      <c r="B35" s="68">
+      <c r="B35" s="124">
         <f>Page1!B34</f>
         <v>0</v>
       </c>
-      <c r="C35" s="69">
+      <c r="C35" s="125">
         <f>Page1!C34</f>
         <v>0</v>
       </c>
-      <c r="D35" s="89"/>
+      <c r="D35" s="75"/>
       <c r="E35" s="26"/>
       <c r="F35" s="26"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="91"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="183"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="188"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="195"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="67">
+      <c r="A36" s="123">
         <f>Page1!A35</f>
         <v>0</v>
       </c>
-      <c r="B36" s="68">
+      <c r="B36" s="124">
         <f>Page1!B35</f>
         <v>0</v>
       </c>
-      <c r="C36" s="69">
+      <c r="C36" s="125">
         <f>Page1!C35</f>
         <v>0</v>
       </c>
-      <c r="D36" s="89"/>
+      <c r="D36" s="75"/>
       <c r="E36" s="26"/>
       <c r="F36" s="26"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="91"/>
-      <c r="I36" s="199"/>
-      <c r="J36" s="200"/>
-      <c r="K36" s="183"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="188"/>
+      <c r="J36" s="189"/>
+      <c r="K36" s="195"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="67">
+      <c r="A37" s="123">
         <f>Page1!A36</f>
         <v>0</v>
       </c>
-      <c r="B37" s="68">
+      <c r="B37" s="124">
         <f>Page1!B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="69">
+      <c r="C37" s="125">
         <f>Page1!C36</f>
         <v>0</v>
       </c>
-      <c r="D37" s="89"/>
+      <c r="D37" s="75"/>
       <c r="E37" s="26"/>
       <c r="F37" s="26"/>
-      <c r="G37" s="90"/>
-      <c r="H37" s="91"/>
-      <c r="I37" s="199"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="183"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="188"/>
+      <c r="J37" s="189"/>
+      <c r="K37" s="195"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="67">
+      <c r="A38" s="123">
         <f>Page1!A37</f>
         <v>0</v>
       </c>
-      <c r="B38" s="68">
+      <c r="B38" s="124">
         <f>Page1!B37</f>
         <v>0</v>
       </c>
-      <c r="C38" s="69">
+      <c r="C38" s="125">
         <f>Page1!C37</f>
         <v>0</v>
       </c>
-      <c r="D38" s="89"/>
+      <c r="D38" s="75"/>
       <c r="E38" s="26"/>
       <c r="F38" s="26"/>
-      <c r="G38" s="90"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="199"/>
-      <c r="J38" s="200"/>
-      <c r="K38" s="183"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="188"/>
+      <c r="J38" s="189"/>
+      <c r="K38" s="195"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="76">
+      <c r="A39" s="130">
         <f>Page1!A38</f>
         <v>0</v>
       </c>
-      <c r="B39" s="77">
+      <c r="B39" s="131">
         <f>Page1!B38</f>
         <v>0</v>
       </c>
-      <c r="C39" s="78">
+      <c r="C39" s="132">
         <f>Page1!C38</f>
         <v>0</v>
       </c>
-      <c r="D39" s="89"/>
+      <c r="D39" s="75"/>
       <c r="E39" s="26"/>
       <c r="F39" s="26"/>
-      <c r="G39" s="90"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="199"/>
-      <c r="J39" s="200"/>
-      <c r="K39" s="183"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="188"/>
+      <c r="J39" s="189"/>
+      <c r="K39" s="195"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="234" t="s">
@@ -6044,7 +6012,7 @@
       </c>
       <c r="B40" s="235"/>
       <c r="C40" s="235"/>
-      <c r="D40" s="92" t="e">
+      <c r="D40" s="78" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
       </c>
@@ -6060,21 +6028,21 @@
         <f>AVERAGE(G10:G39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H40" s="93" t="e">
+      <c r="H40" s="79" t="e">
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="200"/>
-      <c r="J40" s="200"/>
-      <c r="K40" s="183"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="189"/>
+      <c r="K40" s="195"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="204" t="s">
+      <c r="A41" s="217" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="205"/>
-      <c r="C41" s="205"/>
-      <c r="D41" s="94">
+      <c r="B41" s="218"/>
+      <c r="C41" s="218"/>
+      <c r="D41" s="80">
         <f>MIN(D10:D39)</f>
         <v>0</v>
       </c>
@@ -6090,50 +6058,50 @@
         <f>MIN(G10:G39)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="95">
+      <c r="H41" s="81">
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="200"/>
-      <c r="J41" s="200"/>
-      <c r="K41" s="183"/>
+      <c r="I41" s="189"/>
+      <c r="J41" s="189"/>
+      <c r="K41" s="195"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="206" t="s">
+      <c r="A42" s="182" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="207"/>
-      <c r="C42" s="207"/>
-      <c r="D42" s="96">
+      <c r="B42" s="183"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="82">
         <f>MAX(D10:D39)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="97">
+      <c r="E42" s="83">
         <f>MAX(E10:E39)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="97">
+      <c r="F42" s="83">
         <f>MAX(F10:F39)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="97">
+      <c r="G42" s="83">
         <f>MAX(G10:G39)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="98">
+      <c r="H42" s="84">
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="220"/>
-      <c r="J42" s="220"/>
-      <c r="K42" s="184"/>
+      <c r="I42" s="193"/>
+      <c r="J42" s="193"/>
+      <c r="K42" s="196"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="136"/>
-      <c r="C43" s="136"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6150,8 +6118,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="137"/>
-      <c r="C44" s="137"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6160,15 +6128,15 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="147" t="s">
+      <c r="A45" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
+      <c r="B45" s="133"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G45" s="46">
         <f>Page1!G44</f>
@@ -6177,11 +6145,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="147" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="147"/>
-      <c r="C46" s="147"/>
+      <c r="A46" s="133" t="s">
+        <v>133</v>
+      </c>
+      <c r="B46" s="133"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6206,7 +6174,20 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A46:C46"/>
+    <mergeCell ref="I6:K42"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:G6"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="D7:G7"/>
     <mergeCell ref="A40:C40"/>
@@ -6218,19 +6199,6 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="I6:K42"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
@@ -6256,8 +6224,8 @@
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="1.4960629921259843" right="0.11811023622047245" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6269,213 +6237,213 @@
   <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="21.42578125" style="99" customWidth="1"/>
-    <col min="3" max="5" width="12.85546875" style="99" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" style="99" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="99" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="131"/>
+    <col min="1" max="2" width="21.42578125" style="86" customWidth="1"/>
+    <col min="3" max="5" width="12.85546875" style="86" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="86" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="86" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="117"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="238" t="s">
+    <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="239" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="240"/>
-    </row>
-    <row r="2" spans="1:7" s="99" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="100"/>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="102" t="s">
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
+      <c r="E1" s="240"/>
+      <c r="F1" s="240"/>
+      <c r="G1" s="241"/>
+    </row>
+    <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="87"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="292" t="s">
+    <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="250" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="251"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="251"/>
+      <c r="G3" s="252"/>
+    </row>
+    <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="188" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="189"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="189"/>
+      <c r="G4" s="195"/>
+    </row>
+    <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="242" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="244"/>
+    </row>
+    <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="245" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="293"/>
-      <c r="C3" s="293"/>
-      <c r="D3" s="293"/>
-      <c r="E3" s="293"/>
-      <c r="F3" s="293"/>
-      <c r="G3" s="294"/>
-    </row>
-    <row r="4" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="199" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="183"/>
-    </row>
-    <row r="5" spans="1:7" s="99" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="241" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="242"/>
-      <c r="C5" s="242"/>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="243"/>
-    </row>
-    <row r="6" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="103" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="104" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="105" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="244" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" s="245"/>
-      <c r="F6" s="246" t="s">
+      <c r="E6" s="246"/>
+      <c r="F6" s="247" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="247">
+      <c r="G6" s="248">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="103" t="s">
+    <row r="7" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="107"/>
-      <c r="C7" s="105" t="s">
+      <c r="B7" s="94"/>
+      <c r="C7" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="244">
+      <c r="D7" s="245">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="245"/>
-      <c r="F7" s="246"/>
-      <c r="G7" s="248"/>
-    </row>
-    <row r="8" spans="1:7" s="99" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="103" t="s">
+      <c r="E7" s="246"/>
+      <c r="F7" s="247"/>
+      <c r="G7" s="249"/>
+    </row>
+    <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="90" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="106">
+      <c r="B8" s="93">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="246">
+      <c r="D8" s="247">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="246"/>
-      <c r="F8" s="258" t="s">
+      <c r="E8" s="247"/>
+      <c r="F8" s="262" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="247">
+      <c r="G8" s="248">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="109" t="s">
+    <row r="9" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="108">
+      <c r="B9" s="95">
         <f>Page1!G44</f>
         <v>461359700</v>
       </c>
-      <c r="C9" s="258" t="s">
+      <c r="C9" s="262" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="263" t="s">
+      <c r="D9" s="267" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="264"/>
-      <c r="F9" s="259"/>
-      <c r="G9" s="261"/>
-    </row>
-    <row r="10" spans="1:7" s="99" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="110" t="s">
+      <c r="E9" s="268"/>
+      <c r="F9" s="263"/>
+      <c r="G9" s="265"/>
+    </row>
+    <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="111">
+      <c r="B10" s="98">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="260"/>
-      <c r="D10" s="265"/>
-      <c r="E10" s="266"/>
-      <c r="F10" s="260"/>
-      <c r="G10" s="262"/>
-    </row>
-    <row r="11" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="249" t="s">
+      <c r="C10" s="264"/>
+      <c r="D10" s="269"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="264"/>
+      <c r="G10" s="266"/>
+    </row>
+    <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="253" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="251" t="s">
+      <c r="B11" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="253" t="s">
+      <c r="C11" s="257" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="254"/>
-      <c r="E11" s="255"/>
-      <c r="F11" s="251" t="s">
+      <c r="D11" s="258"/>
+      <c r="E11" s="259"/>
+      <c r="F11" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="256" t="s">
+      <c r="G11" s="260" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="250"/>
-      <c r="B12" s="252"/>
-      <c r="C12" s="112" t="s">
+    <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="254"/>
+      <c r="B12" s="256"/>
+      <c r="C12" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="112" t="s">
+      <c r="D12" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="112" t="s">
+      <c r="E12" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="252"/>
-      <c r="G12" s="257"/>
-    </row>
-    <row r="13" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="113" t="s">
+      <c r="F12" s="256"/>
+      <c r="G12" s="261"/>
+    </row>
+    <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="115">
+      <c r="C13" s="102">
         <v>17</v>
       </c>
-      <c r="D13" s="115">
+      <c r="D13" s="102">
         <v>18</v>
       </c>
-      <c r="E13" s="115">
+      <c r="E13" s="102">
         <v>20</v>
       </c>
-      <c r="F13" s="116" t="e">
+      <c r="F13" s="103" t="e">
         <f>Page1!D39</f>
         <v>#DIV/0!</v>
       </c>
@@ -6483,68 +6451,68 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="117" t="s">
+    <row r="14" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="119">
+      <c r="C14" s="106">
         <v>18</v>
       </c>
-      <c r="D14" s="119">
+      <c r="D14" s="106">
         <v>23</v>
       </c>
-      <c r="E14" s="119">
+      <c r="E14" s="106">
         <v>28</v>
       </c>
-      <c r="F14" s="120" t="e">
+      <c r="F14" s="107" t="e">
         <f>Page1!E39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G14" s="121" t="s">
+      <c r="G14" s="108" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="117" t="s">
+    <row r="15" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="118" t="s">
+      <c r="B15" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="119">
+      <c r="C15" s="106">
         <v>300</v>
       </c>
-      <c r="D15" s="119" t="s">
+      <c r="D15" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="119" t="s">
+      <c r="E15" s="106" t="s">
         <v>39</v>
       </c>
       <c r="F15" s="39" t="e">
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="267" t="s">
+      <c r="G15" s="271" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="117" t="s">
+    <row r="16" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="119">
+      <c r="C16" s="106">
         <v>300</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="119" t="s">
+      <c r="E16" s="106" t="s">
         <v>39</v>
       </c>
       <c r="F16" s="39" t="e">
@@ -6553,20 +6521,20 @@
       </c>
       <c r="G16" s="227"/>
     </row>
-    <row r="17" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="117" t="s">
+    <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="104" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="118" t="s">
+      <c r="B17" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="119">
+      <c r="C17" s="106">
         <v>900</v>
       </c>
-      <c r="D17" s="119" t="s">
+      <c r="D17" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="119">
+      <c r="E17" s="106">
         <v>1200</v>
       </c>
       <c r="F17" s="39" t="e">
@@ -6575,20 +6543,20 @@
       </c>
       <c r="G17" s="227"/>
     </row>
-    <row r="18" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="117" t="s">
+    <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="104" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="119">
+      <c r="C18" s="106">
         <v>700</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="119">
+      <c r="E18" s="106">
         <v>1000</v>
       </c>
       <c r="F18" s="39" t="e">
@@ -6597,20 +6565,20 @@
       </c>
       <c r="G18" s="227"/>
     </row>
-    <row r="19" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="117" t="s">
+    <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="119">
+      <c r="C19" s="106">
         <v>350</v>
       </c>
-      <c r="D19" s="119" t="s">
+      <c r="D19" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="119" t="s">
+      <c r="E19" s="106" t="s">
         <v>39</v>
       </c>
       <c r="F19" s="39" t="e">
@@ -6619,20 +6587,20 @@
       </c>
       <c r="G19" s="227"/>
     </row>
-    <row r="20" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="117" t="s">
+    <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="118" t="s">
+      <c r="B20" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="119">
+      <c r="C20" s="106">
         <v>400</v>
       </c>
-      <c r="D20" s="119" t="s">
+      <c r="D20" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="119" t="s">
+      <c r="E20" s="106" t="s">
         <v>39</v>
       </c>
       <c r="F20" s="39" t="e">
@@ -6641,11 +6609,11 @@
       </c>
       <c r="G20" s="227"/>
     </row>
-    <row r="21" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="117" t="s">
+    <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="118" t="s">
+      <c r="B21" s="105" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="38">
@@ -6663,11 +6631,11 @@
       </c>
       <c r="G21" s="227"/>
     </row>
-    <row r="22" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="117" t="s">
+    <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="105" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="38">
@@ -6683,13 +6651,13 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="152"/>
-    </row>
-    <row r="23" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="117" t="s">
+      <c r="G22" s="155"/>
+    </row>
+    <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="105" t="s">
         <v>81</v>
       </c>
       <c r="C23" s="39">
@@ -6705,18 +6673,18 @@
         <f>Page1!F39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G23" s="121" t="s">
+      <c r="G23" s="108" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="117" t="s">
+    <row r="24" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="B24" s="118" t="s">
+      <c r="B24" s="105" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="119" t="s">
+      <c r="C24" s="106" t="s">
         <v>39</v>
       </c>
       <c r="D24" s="39">
@@ -6724,215 +6692,215 @@
         <v>0</v>
       </c>
       <c r="E24" s="39">
-        <f>Page2!J9</f>
-        <v>210</v>
+        <f>Page2!J10</f>
+        <v>213</v>
       </c>
       <c r="F24" s="39" t="e">
         <f>Page2!I41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G24" s="121" t="s">
+      <c r="G24" s="108" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="117" t="s">
+    <row r="25" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="118" t="s">
+      <c r="B25" s="105" t="s">
         <v>87</v>
       </c>
       <c r="C25" s="39">
         <v>6000</v>
       </c>
-      <c r="D25" s="119" t="s">
+      <c r="D25" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="119" t="s">
+      <c r="E25" s="106" t="s">
         <v>39</v>
       </c>
       <c r="F25" s="39">
         <v>6000</v>
       </c>
-      <c r="G25" s="121" t="s">
+      <c r="G25" s="108" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="123" t="s">
+    <row r="26" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="110" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="124" t="s">
+      <c r="B26" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="57">
+      <c r="C26" s="56">
         <v>410</v>
       </c>
-      <c r="D26" s="57">
+      <c r="D26" s="56">
         <v>430</v>
       </c>
-      <c r="E26" s="125">
+      <c r="E26" s="112">
         <v>450</v>
       </c>
-      <c r="F26" s="125" t="e">
+      <c r="F26" s="112" t="e">
         <f>Page2!K41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G26" s="122" t="s">
+      <c r="G26" s="109" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="268" t="s">
+    <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="272" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="269"/>
-      <c r="C27" s="269"/>
-      <c r="D27" s="269"/>
-      <c r="E27" s="269"/>
-      <c r="F27" s="269"/>
-      <c r="G27" s="270"/>
-    </row>
-    <row r="28" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="271" t="s">
+      <c r="B27" s="273"/>
+      <c r="C27" s="273"/>
+      <c r="D27" s="273"/>
+      <c r="E27" s="273"/>
+      <c r="F27" s="273"/>
+      <c r="G27" s="274"/>
+    </row>
+    <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="275" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="272"/>
-      <c r="C28" s="273" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="274"/>
-      <c r="E28" s="275"/>
-      <c r="F28" s="126" t="s">
+      <c r="B28" s="276"/>
+      <c r="C28" s="277" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="278"/>
+      <c r="E28" s="279"/>
+      <c r="F28" s="113" t="s">
         <v>92</v>
       </c>
       <c r="G28" s="18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="276" t="s">
+    <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="280" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="245"/>
-      <c r="C29" s="277" t="s">
+      <c r="B29" s="246"/>
+      <c r="C29" s="281" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="278"/>
-      <c r="E29" s="279"/>
-      <c r="F29" s="80" t="s">
+      <c r="D29" s="282"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="G29" s="121" t="s">
+      <c r="G29" s="108" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="276" t="s">
+    <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="280" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="245"/>
-      <c r="C30" s="277" t="s">
+      <c r="B30" s="246"/>
+      <c r="C30" s="281" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="278"/>
-      <c r="E30" s="279"/>
-      <c r="F30" s="80" t="s">
+      <c r="D30" s="282"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="66" t="s">
         <v>92</v>
       </c>
       <c r="G30" s="18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="276" t="s">
+    <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="280" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="245"/>
-      <c r="C31" s="277" t="s">
+      <c r="B31" s="246"/>
+      <c r="C31" s="281" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="278"/>
-      <c r="E31" s="279"/>
-      <c r="F31" s="80" t="s">
+      <c r="D31" s="282"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="G31" s="121" t="s">
+      <c r="G31" s="108" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="276" t="s">
+    <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="280" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="245"/>
-      <c r="C32" s="277" t="s">
+      <c r="B32" s="246"/>
+      <c r="C32" s="281" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="278"/>
-      <c r="E32" s="279"/>
-      <c r="F32" s="80" t="s">
+      <c r="D32" s="282"/>
+      <c r="E32" s="283"/>
+      <c r="F32" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="G32" s="121" t="s">
+      <c r="G32" s="108" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="276" t="s">
+    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="280" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="245"/>
-      <c r="C33" s="277" t="s">
+      <c r="B33" s="246"/>
+      <c r="C33" s="281" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="278"/>
-      <c r="E33" s="279"/>
-      <c r="F33" s="80" t="s">
+      <c r="D33" s="282"/>
+      <c r="E33" s="283"/>
+      <c r="F33" s="66" t="s">
         <v>92</v>
       </c>
       <c r="G33" s="19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="99" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="143" t="s">
+    <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="165" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="144"/>
-      <c r="C34" s="280" t="s">
+      <c r="B34" s="166"/>
+      <c r="C34" s="286" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="281"/>
-      <c r="E34" s="282"/>
-      <c r="F34" s="127" t="s">
+      <c r="D34" s="287"/>
+      <c r="E34" s="288"/>
+      <c r="F34" s="114" t="s">
         <v>92</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="268" t="s">
+    <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="272" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="269"/>
-      <c r="C35" s="269"/>
-      <c r="D35" s="269"/>
-      <c r="E35" s="269"/>
-      <c r="F35" s="269"/>
-      <c r="G35" s="270"/>
-    </row>
-    <row r="36" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="139" t="s">
+      <c r="B35" s="273"/>
+      <c r="C35" s="273"/>
+      <c r="D35" s="273"/>
+      <c r="E35" s="273"/>
+      <c r="F35" s="273"/>
+      <c r="G35" s="274"/>
+    </row>
+    <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="161" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="140"/>
-      <c r="C36" s="286" t="s">
+      <c r="B36" s="162"/>
+      <c r="C36" s="284" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="287"/>
-      <c r="E36" s="140"/>
+      <c r="D36" s="285"/>
+      <c r="E36" s="162"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
       </c>
@@ -6940,134 +6908,130 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="271" t="s">
+    <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="275" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="272"/>
-      <c r="C37" s="244" t="s">
+      <c r="B37" s="276"/>
+      <c r="C37" s="245" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="283"/>
-      <c r="E37" s="245"/>
-      <c r="F37" s="119" t="s">
+      <c r="D37" s="289"/>
+      <c r="E37" s="246"/>
+      <c r="F37" s="106" t="s">
         <v>92</v>
       </c>
-      <c r="G37" s="121" t="s">
+      <c r="G37" s="108" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="276" t="s">
+    <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="280" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="245"/>
-      <c r="C38" s="244" t="s">
+      <c r="B38" s="246"/>
+      <c r="C38" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="283"/>
-      <c r="E38" s="245"/>
-      <c r="F38" s="119" t="s">
+      <c r="D38" s="289"/>
+      <c r="E38" s="246"/>
+      <c r="F38" s="106" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="121" t="s">
+      <c r="G38" s="108" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="143" t="s">
+    <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="165" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="144"/>
-      <c r="C39" s="284" t="s">
+      <c r="B39" s="166"/>
+      <c r="C39" s="290" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="285"/>
-      <c r="E39" s="144"/>
+      <c r="D39" s="291"/>
+      <c r="E39" s="166"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G39" s="122" t="s">
+      <c r="G39" s="109" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="296" t="s">
+    <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="294" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="297"/>
-      <c r="C40" s="298" t="s">
+      <c r="B40" s="295"/>
+      <c r="C40" s="296" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="297"/>
+      <c r="E40" s="298"/>
+      <c r="F40" s="296" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="299"/>
-      <c r="E40" s="300"/>
-      <c r="F40" s="298" t="s">
+      <c r="G40" s="298"/>
+    </row>
+    <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="299"/>
+      <c r="B41" s="300"/>
+      <c r="C41" s="188"/>
+      <c r="D41" s="189"/>
+      <c r="E41" s="195"/>
+      <c r="F41" s="303"/>
+      <c r="G41" s="304"/>
+    </row>
+    <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="301"/>
+      <c r="B42" s="302"/>
+      <c r="C42" s="305" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="306"/>
+      <c r="E42" s="307"/>
+      <c r="F42" s="305" t="s">
         <v>139</v>
       </c>
-      <c r="G40" s="300"/>
-    </row>
-    <row r="41" spans="1:7" s="99" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="301"/>
-      <c r="B41" s="302"/>
-      <c r="C41" s="199"/>
-      <c r="D41" s="200"/>
-      <c r="E41" s="183"/>
-      <c r="F41" s="305"/>
-      <c r="G41" s="306"/>
-    </row>
-    <row r="42" spans="1:7" s="99" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="303"/>
-      <c r="B42" s="304"/>
-      <c r="C42" s="288" t="s">
-        <v>22</v>
-      </c>
-      <c r="D42" s="307"/>
-      <c r="E42" s="289"/>
-      <c r="F42" s="288" t="s">
-        <v>140</v>
-      </c>
-      <c r="G42" s="289"/>
+      <c r="G42" s="307"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="128"/>
-      <c r="B43" s="128"/>
-      <c r="C43" s="128"/>
-      <c r="D43" s="128"/>
-      <c r="E43" s="295"/>
-      <c r="F43" s="295"/>
-      <c r="G43" s="295"/>
+      <c r="A43" s="115"/>
+      <c r="B43" s="115"/>
+      <c r="C43" s="115"/>
+      <c r="D43" s="115"/>
+      <c r="E43" s="292"/>
+      <c r="F43" s="292"/>
+      <c r="G43" s="292"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="129"/>
-      <c r="C44" s="130"/>
-      <c r="D44" s="128"/>
-      <c r="E44" s="290"/>
-      <c r="F44" s="290"/>
-      <c r="G44" s="290"/>
+      <c r="B44" s="116"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="115"/>
+      <c r="E44" s="293"/>
+      <c r="F44" s="293"/>
+      <c r="G44" s="293"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="291" t="s">
+      <c r="A46" s="238" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="291"/>
+      <c r="B46" s="238"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="291" t="s">
+      <c r="A47" s="238" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="291"/>
+      <c r="B47" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="E43:G43"/>
     <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="E43:G43"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="F40:G40"/>
@@ -7075,6 +7039,7 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="F41:G41"/>
     <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="A38:B38"/>
@@ -7094,22 +7059,18 @@
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="G15:G22"/>
     <mergeCell ref="A27:G27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="C29:E29"/>
-    <mergeCell ref="D8:E8"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="G8:G10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:E10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
@@ -7117,9 +7078,16 @@
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="D8:E8"/>
   </mergeCells>
-  <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="79" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/templates/UC-18gsm-210W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-210W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7910EA4C-972A-4E33-A4A4-2BEF7EB76D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC999A6-C07F-43C6-867A-BC228902F6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1446,7 +1446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1869,6 +1869,81 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1884,13 +1959,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1926,90 +1995,144 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2030,136 +2153,16 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2198,6 +2201,153 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2219,18 +2369,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2269,261 +2410,1511 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
+  <dxfs count="166">
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike/>
+        <u val="none"/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3059,35 +4450,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3108,12 +4499,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="161" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="163"/>
-      <c r="D4" s="164"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="147"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -3125,19 +4516,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="156"/>
-      <c r="K4" s="157"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="140"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="165" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="166"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="168"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="150"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -3149,64 +4540,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="158"/>
-      <c r="K5" s="159"/>
+      <c r="J5" s="141"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="157" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="135"/>
-      <c r="C6" s="136"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="159"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="G6" s="152"/>
-      <c r="H6" s="171"/>
-      <c r="I6" s="152"/>
-      <c r="J6" s="153"/>
-      <c r="K6" s="154"/>
+      <c r="G6" s="134"/>
+      <c r="H6" s="155"/>
+      <c r="I6" s="134"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="136"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="137" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="138"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="138" t="s">
+      <c r="A7" s="160" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="138" t="s">
+      <c r="E7" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="138" t="s">
+      <c r="F7" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="169" t="s">
+      <c r="G7" s="152" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="169" t="s">
+      <c r="H7" s="152" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="138" t="s">
+      <c r="I7" s="137" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="138"/>
-      <c r="K7" s="155"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="138"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140" t="s">
+      <c r="A8" s="161"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="140"/>
-      <c r="G8" s="170"/>
-      <c r="H8" s="170"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -3608,11 +4999,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="147" t="s">
+      <c r="A39" s="168" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="148"/>
-      <c r="C39" s="149"/>
+      <c r="B39" s="169"/>
+      <c r="C39" s="170"/>
       <c r="D39" s="35" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -3647,11 +5038,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="144" t="s">
+      <c r="A40" s="165" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="145"/>
-      <c r="C40" s="146"/>
+      <c r="B40" s="166"/>
+      <c r="C40" s="167"/>
       <c r="D40" s="38">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -3686,11 +5077,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="141" t="s">
+      <c r="A41" s="162" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="142"/>
-      <c r="C41" s="143"/>
+      <c r="B41" s="163"/>
+      <c r="C41" s="164"/>
       <c r="D41" s="41">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -3731,8 +5122,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="150"/>
-      <c r="C42" s="150"/>
+      <c r="B42" s="171"/>
+      <c r="C42" s="171"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -3749,8 +5140,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="151"/>
-      <c r="C43" s="151"/>
+      <c r="B43" s="172"/>
+      <c r="C43" s="172"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -3759,11 +5150,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="133" t="s">
+      <c r="A44" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="133"/>
-      <c r="C44" s="133"/>
+      <c r="B44" s="156"/>
+      <c r="C44" s="156"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -3775,11 +5166,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="156" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="156"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -3821,6 +5212,15 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -3837,76 +5237,51 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D9:D41">
-    <cfRule type="cellIs" dxfId="24" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="93" priority="13" operator="notBetween">
+      <formula>17</formula>
       <formula>20</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="14" operator="lessThan">
-      <formula>17</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E41">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="11" operator="notBetween">
+      <formula>18</formula>
       <formula>28</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="12" operator="lessThan">
-      <formula>18</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F41">
-    <cfRule type="cellIs" dxfId="20" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="9" operator="notBetween">
+      <formula>360</formula>
       <formula>400</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="lessThan">
-      <formula>360</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G41">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="7" operator="notBetween">
+      <formula>0.3</formula>
       <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="lessThan">
-      <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H38">
-    <cfRule type="cellIs" dxfId="16" priority="1" stopIfTrue="1" operator="notBetween">
-      <formula>0.6</formula>
-      <formula>1.4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10">
-    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="89" priority="1" stopIfTrue="1" operator="notBetween">
       <formula>0.6</formula>
       <formula>1.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I41">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="5" operator="notBetween">
+      <formula>900</formula>
       <formula>1200</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="lessThan">
-      <formula>900</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J41">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="87" priority="4" operator="lessThan">
       <formula>350</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K41">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="3" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3929,35 +5304,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -3978,18 +5353,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="161" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="162">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="219">
+      <c r="C4" s="177">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="208"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -4007,25 +5382,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220">
+      <c r="J4" s="179">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="221"/>
+      <c r="K4" s="180"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="165" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="166">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="167">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="168"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4043,104 +5418,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="184">
+      <c r="J5" s="195">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="185"/>
+      <c r="K5" s="196"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="204" t="s">
+      <c r="A6" s="213" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="206"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="187"/>
-      <c r="F6" s="203"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="203"/>
-      <c r="I6" s="201"/>
-      <c r="J6" s="202"/>
+      <c r="B6" s="214"/>
+      <c r="C6" s="215"/>
+      <c r="D6" s="197"/>
+      <c r="E6" s="198"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="185"/>
+      <c r="H6" s="186"/>
+      <c r="I6" s="211"/>
+      <c r="J6" s="212"/>
       <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="186" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="187"/>
-      <c r="C7" s="187"/>
-      <c r="D7" s="207" t="s">
+      <c r="A7" s="197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="216" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="187"/>
-      <c r="F7" s="208"/>
-      <c r="G7" s="190" t="s">
+      <c r="E7" s="198"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="185" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="187"/>
-      <c r="I7" s="190" t="s">
+      <c r="H7" s="198"/>
+      <c r="I7" s="185" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="203"/>
-      <c r="K7" s="194" t="s">
+      <c r="J7" s="186"/>
+      <c r="K7" s="204" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
-      <c r="B8" s="189"/>
-      <c r="C8" s="189"/>
-      <c r="D8" s="188" t="s">
+      <c r="A8" s="199"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="199" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="198" t="s">
+      <c r="E8" s="208" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="199" t="s">
+      <c r="F8" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="191"/>
-      <c r="H8" s="189"/>
-      <c r="I8" s="191" t="s">
+      <c r="G8" s="201"/>
+      <c r="H8" s="200"/>
+      <c r="I8" s="201" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="199"/>
-      <c r="K8" s="195"/>
+      <c r="J8" s="209"/>
+      <c r="K8" s="205"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="188"/>
-      <c r="B9" s="189"/>
-      <c r="C9" s="189"/>
-      <c r="D9" s="188"/>
-      <c r="E9" s="169"/>
-      <c r="F9" s="199"/>
-      <c r="G9" s="191"/>
-      <c r="H9" s="189"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="199"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="209"/>
+      <c r="G9" s="201"/>
+      <c r="H9" s="200"/>
       <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="58">
         <v>210</v>
       </c>
-      <c r="K9" s="195"/>
+      <c r="K9" s="205"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="188"/>
-      <c r="B10" s="189"/>
-      <c r="C10" s="189"/>
-      <c r="D10" s="197"/>
-      <c r="E10" s="170"/>
-      <c r="F10" s="200"/>
-      <c r="G10" s="192"/>
-      <c r="H10" s="193"/>
+      <c r="A10" s="199"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="200"/>
+      <c r="D10" s="207"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="210"/>
+      <c r="G10" s="202"/>
+      <c r="H10" s="203"/>
       <c r="I10" s="59" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="60">
         <v>213</v>
       </c>
-      <c r="K10" s="196"/>
+      <c r="K10" s="206"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
@@ -4158,10 +5533,10 @@
       <c r="D11" s="61"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="211"/>
-      <c r="H11" s="211"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="223"/>
+      <c r="G11" s="194"/>
+      <c r="H11" s="194"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="182"/>
       <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4180,10 +5555,10 @@
       <c r="D12" s="63"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="212"/>
-      <c r="I12" s="174"/>
-      <c r="J12" s="175"/>
+      <c r="G12" s="193"/>
+      <c r="H12" s="193"/>
+      <c r="I12" s="183"/>
+      <c r="J12" s="184"/>
       <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4202,10 +5577,10 @@
       <c r="D13" s="63"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="212"/>
-      <c r="I13" s="174"/>
-      <c r="J13" s="175"/>
+      <c r="G13" s="193"/>
+      <c r="H13" s="193"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="184"/>
       <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4224,10 +5599,10 @@
       <c r="D14" s="63"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="212"/>
-      <c r="I14" s="174"/>
-      <c r="J14" s="175"/>
+      <c r="G14" s="193"/>
+      <c r="H14" s="193"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="184"/>
       <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4246,10 +5621,10 @@
       <c r="D15" s="63"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="212"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="175"/>
+      <c r="G15" s="193"/>
+      <c r="H15" s="193"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="184"/>
       <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4268,10 +5643,10 @@
       <c r="D16" s="61"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="211"/>
-      <c r="H16" s="211"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="175"/>
+      <c r="G16" s="194"/>
+      <c r="H16" s="194"/>
+      <c r="I16" s="183"/>
+      <c r="J16" s="184"/>
       <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4290,10 +5665,10 @@
       <c r="D17" s="63"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="212"/>
-      <c r="I17" s="174"/>
-      <c r="J17" s="175"/>
+      <c r="G17" s="193"/>
+      <c r="H17" s="193"/>
+      <c r="I17" s="183"/>
+      <c r="J17" s="184"/>
       <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4312,10 +5687,10 @@
       <c r="D18" s="63"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="212"/>
-      <c r="I18" s="174"/>
-      <c r="J18" s="175"/>
+      <c r="G18" s="193"/>
+      <c r="H18" s="193"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="184"/>
       <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4334,10 +5709,10 @@
       <c r="D19" s="63"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="212"/>
-      <c r="H19" s="212"/>
-      <c r="I19" s="174"/>
-      <c r="J19" s="175"/>
+      <c r="G19" s="193"/>
+      <c r="H19" s="193"/>
+      <c r="I19" s="183"/>
+      <c r="J19" s="184"/>
       <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4356,10 +5731,10 @@
       <c r="D20" s="63"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="209"/>
-      <c r="H20" s="210"/>
-      <c r="I20" s="174"/>
-      <c r="J20" s="175"/>
+      <c r="G20" s="189"/>
+      <c r="H20" s="190"/>
+      <c r="I20" s="183"/>
+      <c r="J20" s="184"/>
       <c r="K20" s="64"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,10 +5753,10 @@
       <c r="D21" s="63"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="209"/>
-      <c r="H21" s="210"/>
-      <c r="I21" s="174"/>
-      <c r="J21" s="175"/>
+      <c r="G21" s="189"/>
+      <c r="H21" s="190"/>
+      <c r="I21" s="183"/>
+      <c r="J21" s="184"/>
       <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4400,10 +5775,10 @@
       <c r="D22" s="63"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="209"/>
-      <c r="H22" s="210"/>
-      <c r="I22" s="174"/>
-      <c r="J22" s="175"/>
+      <c r="G22" s="189"/>
+      <c r="H22" s="190"/>
+      <c r="I22" s="183"/>
+      <c r="J22" s="184"/>
       <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4422,10 +5797,10 @@
       <c r="D23" s="63"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="209"/>
-      <c r="H23" s="210"/>
-      <c r="I23" s="174"/>
-      <c r="J23" s="175"/>
+      <c r="G23" s="189"/>
+      <c r="H23" s="190"/>
+      <c r="I23" s="183"/>
+      <c r="J23" s="184"/>
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4444,10 +5819,10 @@
       <c r="D24" s="63"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="209"/>
-      <c r="H24" s="210"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="175"/>
+      <c r="G24" s="189"/>
+      <c r="H24" s="190"/>
+      <c r="I24" s="183"/>
+      <c r="J24" s="184"/>
       <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,10 +5841,10 @@
       <c r="D25" s="63"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="209"/>
-      <c r="H25" s="210"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="175"/>
+      <c r="G25" s="189"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="183"/>
+      <c r="J25" s="184"/>
       <c r="K25" s="64"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4488,10 +5863,10 @@
       <c r="D26" s="63"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="209"/>
-      <c r="H26" s="210"/>
-      <c r="I26" s="174"/>
-      <c r="J26" s="175"/>
+      <c r="G26" s="189"/>
+      <c r="H26" s="190"/>
+      <c r="I26" s="183"/>
+      <c r="J26" s="184"/>
       <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4510,10 +5885,10 @@
       <c r="D27" s="63"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="209"/>
-      <c r="H27" s="210"/>
-      <c r="I27" s="174"/>
-      <c r="J27" s="175"/>
+      <c r="G27" s="189"/>
+      <c r="H27" s="190"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="184"/>
       <c r="K27" s="64"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4532,10 +5907,10 @@
       <c r="D28" s="63"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="209"/>
-      <c r="H28" s="210"/>
-      <c r="I28" s="174"/>
-      <c r="J28" s="175"/>
+      <c r="G28" s="189"/>
+      <c r="H28" s="190"/>
+      <c r="I28" s="183"/>
+      <c r="J28" s="184"/>
       <c r="K28" s="64"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4554,10 +5929,10 @@
       <c r="D29" s="63"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="209"/>
-      <c r="H29" s="210"/>
-      <c r="I29" s="174"/>
-      <c r="J29" s="175"/>
+      <c r="G29" s="189"/>
+      <c r="H29" s="190"/>
+      <c r="I29" s="183"/>
+      <c r="J29" s="184"/>
       <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4576,10 +5951,10 @@
       <c r="D30" s="63"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="209"/>
-      <c r="H30" s="210"/>
-      <c r="I30" s="174"/>
-      <c r="J30" s="175"/>
+      <c r="G30" s="189"/>
+      <c r="H30" s="190"/>
+      <c r="I30" s="183"/>
+      <c r="J30" s="184"/>
       <c r="K30" s="64"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4598,10 +5973,10 @@
       <c r="D31" s="63"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="209"/>
-      <c r="H31" s="210"/>
-      <c r="I31" s="174"/>
-      <c r="J31" s="175"/>
+      <c r="G31" s="189"/>
+      <c r="H31" s="190"/>
+      <c r="I31" s="183"/>
+      <c r="J31" s="184"/>
       <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4620,10 +5995,10 @@
       <c r="D32" s="63"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="209"/>
-      <c r="H32" s="210"/>
-      <c r="I32" s="174"/>
-      <c r="J32" s="175"/>
+      <c r="G32" s="189"/>
+      <c r="H32" s="190"/>
+      <c r="I32" s="183"/>
+      <c r="J32" s="184"/>
       <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4642,10 +6017,10 @@
       <c r="D33" s="63"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="209"/>
-      <c r="H33" s="210"/>
-      <c r="I33" s="174"/>
-      <c r="J33" s="175"/>
+      <c r="G33" s="189"/>
+      <c r="H33" s="190"/>
+      <c r="I33" s="183"/>
+      <c r="J33" s="184"/>
       <c r="K33" s="64"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4664,10 +6039,10 @@
       <c r="D34" s="63"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="209"/>
-      <c r="H34" s="210"/>
-      <c r="I34" s="174"/>
-      <c r="J34" s="175"/>
+      <c r="G34" s="189"/>
+      <c r="H34" s="190"/>
+      <c r="I34" s="183"/>
+      <c r="J34" s="184"/>
       <c r="K34" s="64"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4686,10 +6061,10 @@
       <c r="D35" s="63"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="209"/>
-      <c r="H35" s="210"/>
-      <c r="I35" s="174"/>
-      <c r="J35" s="175"/>
+      <c r="G35" s="189"/>
+      <c r="H35" s="190"/>
+      <c r="I35" s="183"/>
+      <c r="J35" s="184"/>
       <c r="K35" s="64"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4708,10 +6083,10 @@
       <c r="D36" s="63"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="209"/>
-      <c r="H36" s="210"/>
-      <c r="I36" s="174"/>
-      <c r="J36" s="175"/>
+      <c r="G36" s="189"/>
+      <c r="H36" s="190"/>
+      <c r="I36" s="183"/>
+      <c r="J36" s="184"/>
       <c r="K36" s="64"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4730,10 +6105,10 @@
       <c r="D37" s="63"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="209"/>
-      <c r="H37" s="210"/>
-      <c r="I37" s="174"/>
-      <c r="J37" s="175"/>
+      <c r="G37" s="189"/>
+      <c r="H37" s="190"/>
+      <c r="I37" s="183"/>
+      <c r="J37" s="184"/>
       <c r="K37" s="64"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4752,10 +6127,10 @@
       <c r="D38" s="63"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="209"/>
-      <c r="H38" s="210"/>
-      <c r="I38" s="174"/>
-      <c r="J38" s="175"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="183"/>
+      <c r="J38" s="184"/>
       <c r="K38" s="64"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4774,10 +6149,10 @@
       <c r="D39" s="63"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="209"/>
-      <c r="H39" s="210"/>
-      <c r="I39" s="174"/>
-      <c r="J39" s="175"/>
+      <c r="G39" s="189"/>
+      <c r="H39" s="190"/>
+      <c r="I39" s="183"/>
+      <c r="J39" s="184"/>
       <c r="K39" s="64"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4796,18 +6171,18 @@
       <c r="D40" s="63"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="212"/>
-      <c r="I40" s="174"/>
-      <c r="J40" s="175"/>
+      <c r="G40" s="193"/>
+      <c r="H40" s="193"/>
+      <c r="I40" s="183"/>
+      <c r="J40" s="184"/>
       <c r="K40" s="64"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="215" t="s">
+      <c r="A41" s="173" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="216"/>
-      <c r="C41" s="216"/>
+      <c r="B41" s="174"/>
+      <c r="C41" s="174"/>
       <c r="D41" s="65" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -4820,27 +6195,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="213" t="e">
+      <c r="G41" s="191" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="214"/>
-      <c r="I41" s="176" t="e">
+      <c r="H41" s="192"/>
+      <c r="I41" s="225" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="177"/>
+      <c r="J41" s="226"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="217" t="s">
+      <c r="A42" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="218"/>
-      <c r="C42" s="218"/>
+      <c r="B42" s="176"/>
+      <c r="C42" s="176"/>
       <c r="D42" s="66">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -4853,27 +6228,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="224">
+      <c r="G42" s="187">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="225"/>
-      <c r="I42" s="172">
+      <c r="H42" s="188"/>
+      <c r="I42" s="223">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="173"/>
+      <c r="J42" s="224"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="182" t="s">
+      <c r="A43" s="221" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="183"/>
-      <c r="C43" s="183"/>
+      <c r="B43" s="222"/>
+      <c r="C43" s="222"/>
       <c r="D43" s="67">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -4886,16 +6261,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="178">
+      <c r="G43" s="217">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="179"/>
-      <c r="I43" s="180">
+      <c r="H43" s="218"/>
+      <c r="I43" s="219">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="181"/>
+      <c r="J43" s="220"/>
       <c r="K43" s="69">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -4905,8 +6280,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="150"/>
-      <c r="C44" s="150"/>
+      <c r="B44" s="171"/>
+      <c r="C44" s="171"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -4923,8 +6298,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="151"/>
-      <c r="C45" s="151"/>
+      <c r="B45" s="172"/>
+      <c r="C45" s="172"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -4933,11 +6308,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="156"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -4950,11 +6325,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="133" t="s">
+      <c r="A47" s="156" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="133"/>
-      <c r="C47" s="133"/>
+      <c r="B47" s="156"/>
+      <c r="C47" s="156"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -5009,6 +6384,84 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A5:B5"/>
@@ -5025,118 +6478,40 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
-    <cfRule type="cellIs" dxfId="11" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="8" operator="notBetween">
+      <formula>700</formula>
       <formula>1000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" operator="lessThan">
-      <formula>700</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E43">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="34" priority="7" operator="lessThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F43">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="33" priority="6" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H19 G20:G39 G40:H43">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThan">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
-      <formula>50</formula>
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="notBetween">
+      <formula>45</formula>
+      <formula>55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K43">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="notBetween">
+      <formula>410</formula>
       <formula>450</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
-      <formula>410</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:J43">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="notBetween">
+      <formula>210</formula>
+      <formula>213</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -5158,35 +6533,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="160"/>
-      <c r="J1" s="160"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="160" t="s">
+      <c r="A2" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="160"/>
-      <c r="C2" s="160"/>
-      <c r="D2" s="160"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="160"/>
-      <c r="G2" s="160"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
+      <c r="B2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5207,18 +6582,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="161" t="s">
+      <c r="A4" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="162">
+      <c r="B4" s="145">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="219">
+      <c r="C4" s="177">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="208"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5236,25 +6611,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="220">
+      <c r="J4" s="179">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="221"/>
+      <c r="K4" s="180"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="165" t="s">
+      <c r="A5" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="166">
+      <c r="B5" s="149">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="167">
+      <c r="C5" s="150">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="168"/>
+      <c r="D5" s="151"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5272,79 +6647,79 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="184">
+      <c r="J5" s="195">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="185"/>
+      <c r="K5" s="196"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="229" t="s">
+      <c r="A6" s="230" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="232"/>
-      <c r="E6" s="153"/>
-      <c r="F6" s="153"/>
-      <c r="G6" s="171"/>
+      <c r="B6" s="231"/>
+      <c r="C6" s="232"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="155"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="186"/>
-      <c r="J6" s="187"/>
-      <c r="K6" s="194"/>
+      <c r="I6" s="197"/>
+      <c r="J6" s="198"/>
+      <c r="K6" s="204"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="186" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="187"/>
-      <c r="C7" s="187"/>
-      <c r="D7" s="207" t="s">
+      <c r="A7" s="197" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="198"/>
+      <c r="C7" s="198"/>
+      <c r="D7" s="216" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="208"/>
-      <c r="H7" s="226" t="s">
+      <c r="E7" s="234"/>
+      <c r="F7" s="234"/>
+      <c r="G7" s="178"/>
+      <c r="H7" s="227" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="188"/>
-      <c r="J7" s="189"/>
-      <c r="K7" s="195"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="200"/>
+      <c r="K7" s="205"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="188"/>
-      <c r="B8" s="189"/>
-      <c r="C8" s="189"/>
-      <c r="D8" s="236" t="s">
+      <c r="A8" s="199"/>
+      <c r="B8" s="200"/>
+      <c r="C8" s="200"/>
+      <c r="D8" s="237" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="198" t="s">
+      <c r="E8" s="208" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="198" t="s">
+      <c r="F8" s="208" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="198" t="s">
+      <c r="G8" s="208" t="s">
         <v>128</v>
       </c>
-      <c r="H8" s="227"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="189"/>
-      <c r="K8" s="195"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="199"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="205"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="188"/>
-      <c r="B9" s="189"/>
-      <c r="C9" s="189"/>
-      <c r="D9" s="237"/>
-      <c r="E9" s="170"/>
-      <c r="F9" s="170"/>
-      <c r="G9" s="170"/>
-      <c r="H9" s="228"/>
-      <c r="I9" s="188"/>
-      <c r="J9" s="189"/>
-      <c r="K9" s="195"/>
+      <c r="A9" s="199"/>
+      <c r="B9" s="200"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="238"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="199"/>
+      <c r="J9" s="200"/>
+      <c r="K9" s="205"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
@@ -5364,9 +6739,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="73"/>
       <c r="H10" s="74"/>
-      <c r="I10" s="188"/>
-      <c r="J10" s="189"/>
-      <c r="K10" s="195"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="200"/>
+      <c r="K10" s="205"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="123">
@@ -5386,9 +6761,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="76"/>
       <c r="H11" s="77"/>
-      <c r="I11" s="188"/>
-      <c r="J11" s="189"/>
-      <c r="K11" s="195"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="200"/>
+      <c r="K11" s="205"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="123">
@@ -5408,9 +6783,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="76"/>
       <c r="H12" s="77"/>
-      <c r="I12" s="188"/>
-      <c r="J12" s="189"/>
-      <c r="K12" s="195"/>
+      <c r="I12" s="199"/>
+      <c r="J12" s="200"/>
+      <c r="K12" s="205"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="123">
@@ -5430,9 +6805,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="73"/>
       <c r="H13" s="77"/>
-      <c r="I13" s="188"/>
-      <c r="J13" s="189"/>
-      <c r="K13" s="195"/>
+      <c r="I13" s="199"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="205"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="123">
@@ -5452,9 +6827,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="76"/>
       <c r="H14" s="77"/>
-      <c r="I14" s="188"/>
-      <c r="J14" s="189"/>
-      <c r="K14" s="195"/>
+      <c r="I14" s="199"/>
+      <c r="J14" s="200"/>
+      <c r="K14" s="205"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="123">
@@ -5474,9 +6849,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="76"/>
       <c r="H15" s="77"/>
-      <c r="I15" s="188"/>
-      <c r="J15" s="189"/>
-      <c r="K15" s="195"/>
+      <c r="I15" s="199"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="205"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="123">
@@ -5496,9 +6871,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="76"/>
       <c r="H16" s="77"/>
-      <c r="I16" s="188"/>
-      <c r="J16" s="189"/>
-      <c r="K16" s="195"/>
+      <c r="I16" s="199"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="205"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="123">
@@ -5518,9 +6893,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="76"/>
       <c r="H17" s="77"/>
-      <c r="I17" s="188"/>
-      <c r="J17" s="189"/>
-      <c r="K17" s="195"/>
+      <c r="I17" s="199"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="205"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="123">
@@ -5540,9 +6915,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="76"/>
       <c r="H18" s="77"/>
-      <c r="I18" s="188"/>
-      <c r="J18" s="189"/>
-      <c r="K18" s="195"/>
+      <c r="I18" s="199"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="205"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="123">
@@ -5562,9 +6937,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="76"/>
       <c r="H19" s="77"/>
-      <c r="I19" s="188"/>
-      <c r="J19" s="189"/>
-      <c r="K19" s="195"/>
+      <c r="I19" s="199"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="205"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
@@ -5584,9 +6959,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="76"/>
       <c r="H20" s="77"/>
-      <c r="I20" s="188"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="195"/>
+      <c r="I20" s="199"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="205"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="123">
@@ -5606,9 +6981,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="76"/>
       <c r="H21" s="77"/>
-      <c r="I21" s="188"/>
-      <c r="J21" s="189"/>
-      <c r="K21" s="195"/>
+      <c r="I21" s="199"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="205"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="123">
@@ -5628,9 +7003,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="76"/>
       <c r="H22" s="77"/>
-      <c r="I22" s="188"/>
-      <c r="J22" s="189"/>
-      <c r="K22" s="195"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="200"/>
+      <c r="K22" s="205"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="123">
@@ -5650,9 +7025,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="76"/>
       <c r="H23" s="77"/>
-      <c r="I23" s="188"/>
-      <c r="J23" s="189"/>
-      <c r="K23" s="195"/>
+      <c r="I23" s="199"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="205"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="123">
@@ -5672,9 +7047,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="76"/>
       <c r="H24" s="77"/>
-      <c r="I24" s="188"/>
-      <c r="J24" s="189"/>
-      <c r="K24" s="195"/>
+      <c r="I24" s="199"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="205"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123">
@@ -5694,9 +7069,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="76"/>
       <c r="H25" s="77"/>
-      <c r="I25" s="188"/>
-      <c r="J25" s="189"/>
-      <c r="K25" s="195"/>
+      <c r="I25" s="199"/>
+      <c r="J25" s="200"/>
+      <c r="K25" s="205"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="123">
@@ -5716,9 +7091,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="76"/>
       <c r="H26" s="77"/>
-      <c r="I26" s="188"/>
-      <c r="J26" s="189"/>
-      <c r="K26" s="195"/>
+      <c r="I26" s="199"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="205"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="123">
@@ -5738,9 +7113,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="76"/>
       <c r="H27" s="77"/>
-      <c r="I27" s="188"/>
-      <c r="J27" s="189"/>
-      <c r="K27" s="195"/>
+      <c r="I27" s="199"/>
+      <c r="J27" s="200"/>
+      <c r="K27" s="205"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="123">
@@ -5760,9 +7135,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="76"/>
       <c r="H28" s="77"/>
-      <c r="I28" s="188"/>
-      <c r="J28" s="189"/>
-      <c r="K28" s="195"/>
+      <c r="I28" s="199"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="205"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="123">
@@ -5782,9 +7157,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="76"/>
       <c r="H29" s="77"/>
-      <c r="I29" s="188"/>
-      <c r="J29" s="189"/>
-      <c r="K29" s="195"/>
+      <c r="I29" s="199"/>
+      <c r="J29" s="200"/>
+      <c r="K29" s="205"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
@@ -5804,9 +7179,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="76"/>
       <c r="H30" s="77"/>
-      <c r="I30" s="188"/>
-      <c r="J30" s="189"/>
-      <c r="K30" s="195"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="200"/>
+      <c r="K30" s="205"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="123">
@@ -5826,9 +7201,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="76"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="188"/>
-      <c r="J31" s="189"/>
-      <c r="K31" s="195"/>
+      <c r="I31" s="199"/>
+      <c r="J31" s="200"/>
+      <c r="K31" s="205"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="123">
@@ -5848,9 +7223,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="76"/>
       <c r="H32" s="77"/>
-      <c r="I32" s="188"/>
-      <c r="J32" s="189"/>
-      <c r="K32" s="195"/>
+      <c r="I32" s="199"/>
+      <c r="J32" s="200"/>
+      <c r="K32" s="205"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="123">
@@ -5870,9 +7245,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="76"/>
       <c r="H33" s="77"/>
-      <c r="I33" s="188"/>
-      <c r="J33" s="189"/>
-      <c r="K33" s="195"/>
+      <c r="I33" s="199"/>
+      <c r="J33" s="200"/>
+      <c r="K33" s="205"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="123">
@@ -5892,9 +7267,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="76"/>
       <c r="H34" s="77"/>
-      <c r="I34" s="188"/>
-      <c r="J34" s="189"/>
-      <c r="K34" s="195"/>
+      <c r="I34" s="199"/>
+      <c r="J34" s="200"/>
+      <c r="K34" s="205"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="123">
@@ -5914,9 +7289,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="76"/>
       <c r="H35" s="77"/>
-      <c r="I35" s="188"/>
-      <c r="J35" s="189"/>
-      <c r="K35" s="195"/>
+      <c r="I35" s="199"/>
+      <c r="J35" s="200"/>
+      <c r="K35" s="205"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="123">
@@ -5936,9 +7311,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="76"/>
       <c r="H36" s="77"/>
-      <c r="I36" s="188"/>
-      <c r="J36" s="189"/>
-      <c r="K36" s="195"/>
+      <c r="I36" s="199"/>
+      <c r="J36" s="200"/>
+      <c r="K36" s="205"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="123">
@@ -5958,9 +7333,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="76"/>
       <c r="H37" s="77"/>
-      <c r="I37" s="188"/>
-      <c r="J37" s="189"/>
-      <c r="K37" s="195"/>
+      <c r="I37" s="199"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="205"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="123">
@@ -5980,9 +7355,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="76"/>
       <c r="H38" s="77"/>
-      <c r="I38" s="188"/>
-      <c r="J38" s="189"/>
-      <c r="K38" s="195"/>
+      <c r="I38" s="199"/>
+      <c r="J38" s="200"/>
+      <c r="K38" s="205"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="130">
@@ -6002,16 +7377,16 @@
       <c r="F39" s="26"/>
       <c r="G39" s="76"/>
       <c r="H39" s="77"/>
-      <c r="I39" s="188"/>
-      <c r="J39" s="189"/>
-      <c r="K39" s="195"/>
+      <c r="I39" s="199"/>
+      <c r="J39" s="200"/>
+      <c r="K39" s="205"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="234" t="s">
+      <c r="A40" s="235" t="s">
         <v>26</v>
       </c>
-      <c r="B40" s="235"/>
-      <c r="C40" s="235"/>
+      <c r="B40" s="236"/>
+      <c r="C40" s="236"/>
       <c r="D40" s="78" t="e">
         <f>AVERAGE(D10:D39)</f>
         <v>#DIV/0!</v>
@@ -6032,16 +7407,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="189"/>
-      <c r="J40" s="189"/>
-      <c r="K40" s="195"/>
+      <c r="I40" s="200"/>
+      <c r="J40" s="200"/>
+      <c r="K40" s="205"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="217" t="s">
+      <c r="A41" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="218"/>
-      <c r="C41" s="218"/>
+      <c r="B41" s="176"/>
+      <c r="C41" s="176"/>
       <c r="D41" s="80">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -6062,16 +7437,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="189"/>
-      <c r="J41" s="189"/>
-      <c r="K41" s="195"/>
+      <c r="I41" s="200"/>
+      <c r="J41" s="200"/>
+      <c r="K41" s="205"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="182" t="s">
+      <c r="A42" s="221" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="183"/>
-      <c r="C42" s="183"/>
+      <c r="B42" s="222"/>
+      <c r="C42" s="222"/>
       <c r="D42" s="82">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -6092,16 +7467,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="193"/>
-      <c r="J42" s="193"/>
-      <c r="K42" s="196"/>
+      <c r="I42" s="203"/>
+      <c r="J42" s="203"/>
+      <c r="K42" s="206"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
+      <c r="B43" s="171"/>
+      <c r="C43" s="171"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -6118,8 +7493,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="151"/>
-      <c r="C44" s="151"/>
+      <c r="B44" s="172"/>
+      <c r="C44" s="172"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -6128,11 +7503,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="133" t="s">
+      <c r="A45" s="156" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="133"/>
-      <c r="C45" s="133"/>
+      <c r="B45" s="156"/>
+      <c r="C45" s="156"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -6145,11 +7520,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="156" t="s">
         <v>133</v>
       </c>
-      <c r="B46" s="133"/>
-      <c r="C46" s="133"/>
+      <c r="B46" s="156"/>
+      <c r="C46" s="156"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -6174,15 +7549,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="I6:K42"/>
     <mergeCell ref="H7:H9"/>
@@ -6199,27 +7565,36 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
-      <formula>52</formula>
-      <formula>64</formula>
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="notBetween">
+      <formula>55</formula>
+      <formula>65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E42">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="notBetween">
-      <formula>49</formula>
-      <formula>59</formula>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="notBetween">
+      <formula>45</formula>
+      <formula>55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F42">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
-      <formula>-12.5</formula>
-      <formula>-4.5</formula>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="notBetween">
+      <formula>-16</formula>
+      <formula>-6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:H42">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="notBetween">
       <formula>0</formula>
       <formula>4</formula>
     </cfRule>
@@ -6245,15 +7620,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="289" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
-      <c r="E1" s="240"/>
-      <c r="F1" s="240"/>
-      <c r="G1" s="241"/>
+      <c r="B1" s="290"/>
+      <c r="C1" s="290"/>
+      <c r="D1" s="290"/>
+      <c r="E1" s="290"/>
+      <c r="F1" s="290"/>
+      <c r="G1" s="291"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -6267,37 +7642,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="250" t="s">
+      <c r="A3" s="297" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="251"/>
-      <c r="C3" s="251"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="252"/>
+      <c r="B3" s="298"/>
+      <c r="C3" s="298"/>
+      <c r="D3" s="298"/>
+      <c r="E3" s="298"/>
+      <c r="F3" s="298"/>
+      <c r="G3" s="299"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="188" t="s">
+      <c r="A4" s="199" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="189"/>
-      <c r="C4" s="189"/>
-      <c r="D4" s="189"/>
-      <c r="E4" s="189"/>
-      <c r="F4" s="189"/>
-      <c r="G4" s="195"/>
+      <c r="B4" s="200"/>
+      <c r="C4" s="200"/>
+      <c r="D4" s="200"/>
+      <c r="E4" s="200"/>
+      <c r="F4" s="200"/>
+      <c r="G4" s="205"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="242" t="s">
+      <c r="A5" s="292" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="243"/>
-      <c r="C5" s="243"/>
-      <c r="D5" s="243"/>
-      <c r="E5" s="243"/>
-      <c r="F5" s="243"/>
-      <c r="G5" s="244"/>
+      <c r="B5" s="293"/>
+      <c r="C5" s="293"/>
+      <c r="D5" s="293"/>
+      <c r="E5" s="293"/>
+      <c r="F5" s="293"/>
+      <c r="G5" s="294"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -6309,14 +7684,14 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="245" t="s">
+      <c r="D6" s="257" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="246"/>
-      <c r="F6" s="247" t="s">
+      <c r="E6" s="259"/>
+      <c r="F6" s="295" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="248">
+      <c r="G6" s="280">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -6329,13 +7704,13 @@
       <c r="C7" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="245">
+      <c r="D7" s="257">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="246"/>
-      <c r="F7" s="247"/>
-      <c r="G7" s="249"/>
+      <c r="E7" s="259"/>
+      <c r="F7" s="295"/>
+      <c r="G7" s="296"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -6348,15 +7723,15 @@
       <c r="C8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="247">
+      <c r="D8" s="295">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="247"/>
-      <c r="F8" s="262" t="s">
+      <c r="E8" s="295"/>
+      <c r="F8" s="277" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="248">
+      <c r="G8" s="280">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -6369,15 +7744,15 @@
         <f>Page1!G44</f>
         <v>461359700</v>
       </c>
-      <c r="C9" s="262" t="s">
+      <c r="C9" s="277" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="267" t="s">
+      <c r="D9" s="283" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="268"/>
-      <c r="F9" s="263"/>
-      <c r="G9" s="265"/>
+      <c r="E9" s="284"/>
+      <c r="F9" s="278"/>
+      <c r="G9" s="281"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -6387,34 +7762,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="264"/>
-      <c r="D10" s="269"/>
-      <c r="E10" s="270"/>
-      <c r="F10" s="264"/>
-      <c r="G10" s="266"/>
+      <c r="C10" s="279"/>
+      <c r="D10" s="285"/>
+      <c r="E10" s="286"/>
+      <c r="F10" s="279"/>
+      <c r="G10" s="282"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="253" t="s">
+      <c r="A11" s="300" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="255" t="s">
+      <c r="B11" s="302" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="257" t="s">
+      <c r="C11" s="304" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="258"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="255" t="s">
+      <c r="D11" s="305"/>
+      <c r="E11" s="306"/>
+      <c r="F11" s="302" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="260" t="s">
+      <c r="G11" s="307" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="254"/>
-      <c r="B12" s="256"/>
+      <c r="A12" s="301"/>
+      <c r="B12" s="303"/>
       <c r="C12" s="99" t="s">
         <v>60</v>
       </c>
@@ -6424,8 +7799,8 @@
       <c r="E12" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="256"/>
-      <c r="G12" s="261"/>
+      <c r="F12" s="303"/>
+      <c r="G12" s="308"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -6495,7 +7870,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="271" t="s">
+      <c r="G15" s="287" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6519,7 +7894,7 @@
         <f>Page2!F41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G16" s="227"/>
+      <c r="G16" s="228"/>
     </row>
     <row r="17" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="104" t="s">
@@ -6541,7 +7916,7 @@
         <f>Page1!I39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G17" s="227"/>
+      <c r="G17" s="228"/>
     </row>
     <row r="18" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="104" t="s">
@@ -6563,7 +7938,7 @@
         <f>Page2!D41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="227"/>
+      <c r="G18" s="228"/>
     </row>
     <row r="19" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="104" t="s">
@@ -6585,7 +7960,7 @@
         <f>Page1!J39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G19" s="227"/>
+      <c r="G19" s="228"/>
     </row>
     <row r="20" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
@@ -6607,7 +7982,7 @@
         <f>Page2!E41</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="227"/>
+      <c r="G20" s="228"/>
     </row>
     <row r="21" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="104" t="s">
@@ -6629,7 +8004,7 @@
         <f>Page1!G39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="227"/>
+      <c r="G21" s="228"/>
     </row>
     <row r="22" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="104" t="s">
@@ -6651,7 +8026,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="155"/>
+      <c r="G22" s="138"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -6688,8 +8063,8 @@
         <v>39</v>
       </c>
       <c r="D24" s="39">
-        <f>Page2!J8</f>
-        <v>0</v>
+        <f>Page2!J9</f>
+        <v>210</v>
       </c>
       <c r="E24" s="39">
         <f>Page2!J10</f>
@@ -6751,26 +8126,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="272" t="s">
+      <c r="A27" s="271" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="273"/>
-      <c r="C27" s="273"/>
-      <c r="D27" s="273"/>
-      <c r="E27" s="273"/>
-      <c r="F27" s="273"/>
-      <c r="G27" s="274"/>
+      <c r="B27" s="272"/>
+      <c r="C27" s="272"/>
+      <c r="D27" s="272"/>
+      <c r="E27" s="272"/>
+      <c r="F27" s="272"/>
+      <c r="G27" s="273"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="275" t="s">
+      <c r="A28" s="255" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="276"/>
-      <c r="C28" s="277" t="s">
+      <c r="B28" s="256"/>
+      <c r="C28" s="274" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="278"/>
-      <c r="E28" s="279"/>
+      <c r="D28" s="275"/>
+      <c r="E28" s="276"/>
       <c r="F28" s="113" t="s">
         <v>92</v>
       </c>
@@ -6779,15 +8154,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="280" t="s">
+      <c r="A29" s="260" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="246"/>
-      <c r="C29" s="281" t="s">
+      <c r="B29" s="259"/>
+      <c r="C29" s="265" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="282"/>
-      <c r="E29" s="283"/>
+      <c r="D29" s="266"/>
+      <c r="E29" s="267"/>
       <c r="F29" s="66" t="s">
         <v>92</v>
       </c>
@@ -6796,15 +8171,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="280" t="s">
+      <c r="A30" s="260" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="246"/>
-      <c r="C30" s="281" t="s">
+      <c r="B30" s="259"/>
+      <c r="C30" s="265" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="282"/>
-      <c r="E30" s="283"/>
+      <c r="D30" s="266"/>
+      <c r="E30" s="267"/>
       <c r="F30" s="66" t="s">
         <v>92</v>
       </c>
@@ -6813,15 +8188,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="280" t="s">
+      <c r="A31" s="260" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="246"/>
-      <c r="C31" s="281" t="s">
+      <c r="B31" s="259"/>
+      <c r="C31" s="265" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="282"/>
-      <c r="E31" s="283"/>
+      <c r="D31" s="266"/>
+      <c r="E31" s="267"/>
       <c r="F31" s="66" t="s">
         <v>92</v>
       </c>
@@ -6830,15 +8205,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="280" t="s">
+      <c r="A32" s="260" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="246"/>
-      <c r="C32" s="281" t="s">
+      <c r="B32" s="259"/>
+      <c r="C32" s="265" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="282"/>
-      <c r="E32" s="283"/>
+      <c r="D32" s="266"/>
+      <c r="E32" s="267"/>
       <c r="F32" s="66" t="s">
         <v>92</v>
       </c>
@@ -6846,61 +8221,61 @@
         <v>93</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="280" t="s">
+    <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="260" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="246"/>
-      <c r="C33" s="281" t="s">
+      <c r="B33" s="259"/>
+      <c r="C33" s="265" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="282"/>
-      <c r="E33" s="283"/>
+      <c r="D33" s="266"/>
+      <c r="E33" s="267"/>
       <c r="F33" s="66" t="s">
         <v>92</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="108" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="165" t="s">
+      <c r="A34" s="148" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="166"/>
-      <c r="C34" s="286" t="s">
+      <c r="B34" s="149"/>
+      <c r="C34" s="268" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="287"/>
-      <c r="E34" s="288"/>
+      <c r="D34" s="269"/>
+      <c r="E34" s="270"/>
       <c r="F34" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="133" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="272" t="s">
+      <c r="A35" s="271" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="273"/>
-      <c r="C35" s="273"/>
-      <c r="D35" s="273"/>
-      <c r="E35" s="273"/>
-      <c r="F35" s="273"/>
-      <c r="G35" s="274"/>
+      <c r="B35" s="272"/>
+      <c r="C35" s="272"/>
+      <c r="D35" s="272"/>
+      <c r="E35" s="272"/>
+      <c r="F35" s="272"/>
+      <c r="G35" s="273"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="161" t="s">
+      <c r="A36" s="144" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="162"/>
-      <c r="C36" s="284" t="s">
+      <c r="B36" s="145"/>
+      <c r="C36" s="263" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="285"/>
-      <c r="E36" s="162"/>
+      <c r="D36" s="264"/>
+      <c r="E36" s="145"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
       </c>
@@ -6909,15 +8284,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="275" t="s">
+      <c r="A37" s="255" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="276"/>
-      <c r="C37" s="245" t="s">
+      <c r="B37" s="256"/>
+      <c r="C37" s="257" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="289"/>
-      <c r="E37" s="246"/>
+      <c r="D37" s="258"/>
+      <c r="E37" s="259"/>
       <c r="F37" s="106" t="s">
         <v>92</v>
       </c>
@@ -6926,15 +8301,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="280" t="s">
+      <c r="A38" s="260" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="246"/>
-      <c r="C38" s="245" t="s">
+      <c r="B38" s="259"/>
+      <c r="C38" s="257" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="289"/>
-      <c r="E38" s="246"/>
+      <c r="D38" s="258"/>
+      <c r="E38" s="259"/>
       <c r="F38" s="106" t="s">
         <v>92</v>
       </c>
@@ -6943,15 +8318,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="165" t="s">
+      <c r="A39" s="148" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="166"/>
-      <c r="C39" s="290" t="s">
+      <c r="B39" s="149"/>
+      <c r="C39" s="261" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="291"/>
-      <c r="E39" s="166"/>
+      <c r="D39" s="262"/>
+      <c r="E39" s="149"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
@@ -6960,50 +8335,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="294" t="s">
+      <c r="A40" s="241" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="295"/>
-      <c r="C40" s="296" t="s">
+      <c r="B40" s="242"/>
+      <c r="C40" s="243" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="297"/>
-      <c r="E40" s="298"/>
-      <c r="F40" s="296" t="s">
+      <c r="D40" s="244"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="243" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="298"/>
+      <c r="G40" s="245"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="299"/>
-      <c r="B41" s="300"/>
-      <c r="C41" s="188"/>
-      <c r="D41" s="189"/>
-      <c r="E41" s="195"/>
-      <c r="F41" s="303"/>
-      <c r="G41" s="304"/>
+      <c r="A41" s="246"/>
+      <c r="B41" s="247"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="205"/>
+      <c r="F41" s="250"/>
+      <c r="G41" s="251"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="301"/>
-      <c r="B42" s="302"/>
-      <c r="C42" s="305" t="s">
+      <c r="A42" s="248"/>
+      <c r="B42" s="249"/>
+      <c r="C42" s="252" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="306"/>
-      <c r="E42" s="307"/>
-      <c r="F42" s="305" t="s">
+      <c r="D42" s="253"/>
+      <c r="E42" s="254"/>
+      <c r="F42" s="252" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="307"/>
+      <c r="G42" s="254"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="292"/>
-      <c r="F43" s="292"/>
-      <c r="G43" s="292"/>
+      <c r="E43" s="239"/>
+      <c r="F43" s="239"/>
+      <c r="G43" s="239"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -7012,63 +8387,24 @@
       <c r="B44" s="116"/>
       <c r="C44" s="118"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="293"/>
-      <c r="F44" s="293"/>
-      <c r="G44" s="293"/>
+      <c r="E44" s="240"/>
+      <c r="F44" s="240"/>
+      <c r="G44" s="240"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="238" t="s">
+      <c r="A46" s="288" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="238"/>
+      <c r="B46" s="288"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="238" t="s">
+      <c r="A47" s="288" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="238"/>
+      <c r="B47" s="288"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="G15:G22"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:G1"/>
@@ -7085,6 +8421,45 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="G15:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-210W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-210W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC999A6-C07F-43C6-867A-BC228902F6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00DB193-E85B-44C3-AA1A-52AC6DB8DE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="142">
   <si>
     <t>Sample No.</t>
   </si>
@@ -511,9 +511,6 @@
   </si>
   <si>
     <t>Swanson Plastics(India) Pvt. Ltd</t>
-  </si>
-  <si>
-    <t>#02</t>
   </si>
   <si>
     <t>NA</t>
@@ -1872,6 +1869,63 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1881,9 +1935,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1938,153 +1989,66 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2123,6 +2087,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2135,71 +2102,263 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2248,300 +2407,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="166">
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <strike/>
@@ -2582,518 +2453,6 @@
         <strike/>
         <color rgb="FFFF0000"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3214,833 +2573,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike/>
-        <u val="none"/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -4450,35 +2982,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -4499,12 +3031,12 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="147"/>
+      <c r="B4" s="163"/>
+      <c r="C4" s="164"/>
+      <c r="D4" s="165"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -4516,19 +3048,19 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="139"/>
-      <c r="K4" s="140"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="158"/>
       <c r="M4" s="45" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149"/>
-      <c r="C5" s="150"/>
-      <c r="D5" s="151"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -4540,64 +3072,64 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="141"/>
-      <c r="K5" s="142"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="160"/>
     </row>
     <row r="6" spans="1:13" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="135" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="158"/>
-      <c r="C6" s="159"/>
+      <c r="B6" s="136"/>
+      <c r="C6" s="137"/>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="134"/>
-      <c r="H6" s="155"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="136"/>
+        <v>141</v>
+      </c>
+      <c r="G6" s="153"/>
+      <c r="H6" s="172"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="155"/>
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="160" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="137"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="137" t="s">
+      <c r="A7" s="138" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="137" t="s">
+      <c r="E7" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="137" t="s">
+      <c r="F7" s="139" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="152" t="s">
+      <c r="G7" s="170" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="152" t="s">
+      <c r="H7" s="170" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="137" t="s">
+      <c r="I7" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="137"/>
-      <c r="K7" s="138"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="156"/>
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="161"/>
-      <c r="B8" s="154"/>
-      <c r="C8" s="154"/>
-      <c r="D8" s="154"/>
-      <c r="E8" s="154" t="s">
+      <c r="A8" s="140"/>
+      <c r="B8" s="141"/>
+      <c r="C8" s="141"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="154"/>
-      <c r="G8" s="153"/>
-      <c r="H8" s="153"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
       <c r="I8" s="1" t="s">
         <v>10</v>
       </c>
@@ -4999,11 +3531,11 @@
       <c r="K38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="168" t="s">
+      <c r="A39" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="169"/>
-      <c r="C39" s="170"/>
+      <c r="B39" s="149"/>
+      <c r="C39" s="150"/>
       <c r="D39" s="35" t="e">
         <f t="shared" ref="D39:K39" si="0">AVERAGE(D9:D38)</f>
         <v>#DIV/0!</v>
@@ -5038,11 +3570,11 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="165" t="s">
+      <c r="A40" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="166"/>
-      <c r="C40" s="167"/>
+      <c r="B40" s="146"/>
+      <c r="C40" s="147"/>
       <c r="D40" s="38">
         <f t="shared" ref="D40:K40" si="1">MIN(D9:D38)</f>
         <v>0</v>
@@ -5077,11 +3609,11 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="162" t="s">
+      <c r="A41" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="163"/>
-      <c r="C41" s="164"/>
+      <c r="B41" s="143"/>
+      <c r="C41" s="144"/>
       <c r="D41" s="41">
         <f t="shared" ref="D41:K41" si="2">MAX(D9:D38)</f>
         <v>0</v>
@@ -5122,8 +3654,8 @@
       <c r="A42" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="171"/>
-      <c r="C42" s="171"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
       <c r="D42" s="44" t="s">
         <v>22</v>
       </c>
@@ -5140,8 +3672,8 @@
     </row>
     <row r="43" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
-      <c r="B43" s="172"/>
-      <c r="C43" s="172"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
       <c r="D43" s="44"/>
       <c r="F43" s="46"/>
       <c r="G43" s="47"/>
@@ -5150,11 +3682,11 @@
       <c r="J43" s="51"/>
     </row>
     <row r="44" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="156" t="s">
+      <c r="A44" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="156"/>
-      <c r="C44" s="156"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="134"/>
       <c r="D44" s="44"/>
       <c r="E44" s="44"/>
       <c r="F44" s="47" t="s">
@@ -5166,11 +3698,11 @@
       <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:14" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="156"/>
-      <c r="C45" s="156"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="44"/>
@@ -5212,15 +3744,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="25">
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="B43:C43"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="I7:K7"/>
     <mergeCell ref="J4:K4"/>
@@ -5237,51 +3760,60 @@
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="D7:D8"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D9:D41">
-    <cfRule type="cellIs" dxfId="93" priority="13" operator="notBetween">
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="notBetween">
       <formula>17</formula>
       <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9:E41">
-    <cfRule type="cellIs" dxfId="92" priority="11" operator="notBetween">
+    <cfRule type="cellIs" dxfId="16" priority="11" operator="notBetween">
       <formula>18</formula>
       <formula>28</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:F41">
-    <cfRule type="cellIs" dxfId="91" priority="9" operator="notBetween">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="notBetween">
       <formula>360</formula>
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G41">
-    <cfRule type="cellIs" dxfId="90" priority="7" operator="notBetween">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="notBetween">
       <formula>0.3</formula>
       <formula>0.6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H38">
-    <cfRule type="cellIs" dxfId="89" priority="1" stopIfTrue="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="13" priority="1" stopIfTrue="1" operator="notBetween">
       <formula>0.6</formula>
       <formula>1.4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I41">
-    <cfRule type="cellIs" dxfId="88" priority="5" operator="notBetween">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="notBetween">
       <formula>900</formula>
       <formula>1200</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J41">
-    <cfRule type="cellIs" dxfId="87" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="lessThan">
       <formula>350</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K41">
-    <cfRule type="cellIs" dxfId="86" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5304,35 +3836,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -5353,18 +3885,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145">
+      <c r="B4" s="163">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="177">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="178"/>
+      <c r="D4" s="209"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -5382,25 +3914,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="179">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="180"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149">
+      <c r="B5" s="167">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="168">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="151"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -5418,104 +3950,104 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="195">
+      <c r="J5" s="185">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="196"/>
+      <c r="K5" s="186"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="213" t="s">
+      <c r="A6" s="205" t="s">
         <v>134</v>
       </c>
-      <c r="B6" s="214"/>
-      <c r="C6" s="215"/>
-      <c r="D6" s="197"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="185"/>
-      <c r="H6" s="186"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="212"/>
+      <c r="B6" s="206"/>
+      <c r="C6" s="207"/>
+      <c r="D6" s="187"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="204"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="204"/>
+      <c r="I6" s="202"/>
+      <c r="J6" s="203"/>
       <c r="K6" s="55"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="216" t="s">
+      <c r="A7" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="198"/>
-      <c r="F7" s="178"/>
-      <c r="G7" s="185" t="s">
+      <c r="E7" s="188"/>
+      <c r="F7" s="209"/>
+      <c r="G7" s="191" t="s">
         <v>125</v>
       </c>
-      <c r="H7" s="198"/>
-      <c r="I7" s="185" t="s">
+      <c r="H7" s="188"/>
+      <c r="I7" s="191" t="s">
         <v>135</v>
       </c>
-      <c r="J7" s="186"/>
-      <c r="K7" s="204" t="s">
+      <c r="J7" s="204"/>
+      <c r="K7" s="195" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="200"/>
-      <c r="D8" s="199" t="s">
+      <c r="A8" s="189"/>
+      <c r="B8" s="190"/>
+      <c r="C8" s="190"/>
+      <c r="D8" s="189" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="208" t="s">
+      <c r="E8" s="199" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="209" t="s">
+      <c r="F8" s="200" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="201"/>
-      <c r="H8" s="200"/>
-      <c r="I8" s="201" t="s">
+      <c r="G8" s="192"/>
+      <c r="H8" s="190"/>
+      <c r="I8" s="192" t="s">
         <v>136</v>
       </c>
-      <c r="J8" s="209"/>
-      <c r="K8" s="205"/>
+      <c r="J8" s="200"/>
+      <c r="K8" s="196"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="199"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="199"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="201"/>
-      <c r="H9" s="200"/>
+      <c r="A9" s="189"/>
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
+      <c r="D9" s="189"/>
+      <c r="E9" s="170"/>
+      <c r="F9" s="200"/>
+      <c r="G9" s="192"/>
+      <c r="H9" s="190"/>
       <c r="I9" s="57" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="58">
         <v>210</v>
       </c>
-      <c r="K9" s="205"/>
+      <c r="K9" s="196"/>
     </row>
     <row r="10" spans="1:11" s="5" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="199"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="200"/>
-      <c r="D10" s="207"/>
-      <c r="E10" s="153"/>
-      <c r="F10" s="210"/>
-      <c r="G10" s="202"/>
-      <c r="H10" s="203"/>
+      <c r="A10" s="189"/>
+      <c r="B10" s="190"/>
+      <c r="C10" s="190"/>
+      <c r="D10" s="198"/>
+      <c r="E10" s="171"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="193"/>
+      <c r="H10" s="194"/>
       <c r="I10" s="59" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="60">
         <v>213</v>
       </c>
-      <c r="K10" s="206"/>
+      <c r="K10" s="197"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
@@ -5533,10 +4065,10 @@
       <c r="D11" s="61"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
-      <c r="G11" s="194"/>
-      <c r="H11" s="194"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="182"/>
+      <c r="G11" s="212"/>
+      <c r="H11" s="212"/>
+      <c r="I11" s="223"/>
+      <c r="J11" s="224"/>
       <c r="K11" s="62"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5555,10 +4087,10 @@
       <c r="D12" s="63"/>
       <c r="E12" s="25"/>
       <c r="F12" s="25"/>
-      <c r="G12" s="193"/>
-      <c r="H12" s="193"/>
-      <c r="I12" s="183"/>
-      <c r="J12" s="184"/>
+      <c r="G12" s="213"/>
+      <c r="H12" s="213"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="176"/>
       <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5577,10 +4109,10 @@
       <c r="D13" s="63"/>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
-      <c r="G13" s="193"/>
-      <c r="H13" s="193"/>
-      <c r="I13" s="183"/>
-      <c r="J13" s="184"/>
+      <c r="G13" s="213"/>
+      <c r="H13" s="213"/>
+      <c r="I13" s="175"/>
+      <c r="J13" s="176"/>
       <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5599,10 +4131,10 @@
       <c r="D14" s="63"/>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
-      <c r="G14" s="193"/>
-      <c r="H14" s="193"/>
-      <c r="I14" s="183"/>
-      <c r="J14" s="184"/>
+      <c r="G14" s="213"/>
+      <c r="H14" s="213"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="176"/>
       <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5621,10 +4153,10 @@
       <c r="D15" s="63"/>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
-      <c r="G15" s="193"/>
-      <c r="H15" s="193"/>
-      <c r="I15" s="183"/>
-      <c r="J15" s="184"/>
+      <c r="G15" s="213"/>
+      <c r="H15" s="213"/>
+      <c r="I15" s="175"/>
+      <c r="J15" s="176"/>
       <c r="K15" s="64"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5643,10 +4175,10 @@
       <c r="D16" s="61"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
-      <c r="G16" s="194"/>
-      <c r="H16" s="194"/>
-      <c r="I16" s="183"/>
-      <c r="J16" s="184"/>
+      <c r="G16" s="212"/>
+      <c r="H16" s="212"/>
+      <c r="I16" s="175"/>
+      <c r="J16" s="176"/>
       <c r="K16" s="62"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5665,10 +4197,10 @@
       <c r="D17" s="63"/>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
-      <c r="G17" s="193"/>
-      <c r="H17" s="193"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="184"/>
+      <c r="G17" s="213"/>
+      <c r="H17" s="213"/>
+      <c r="I17" s="175"/>
+      <c r="J17" s="176"/>
       <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5687,10 +4219,10 @@
       <c r="D18" s="63"/>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
-      <c r="G18" s="193"/>
-      <c r="H18" s="193"/>
-      <c r="I18" s="183"/>
-      <c r="J18" s="184"/>
+      <c r="G18" s="213"/>
+      <c r="H18" s="213"/>
+      <c r="I18" s="175"/>
+      <c r="J18" s="176"/>
       <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5709,10 +4241,10 @@
       <c r="D19" s="63"/>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
-      <c r="G19" s="193"/>
-      <c r="H19" s="193"/>
-      <c r="I19" s="183"/>
-      <c r="J19" s="184"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="175"/>
+      <c r="J19" s="176"/>
       <c r="K19" s="64"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5731,10 +4263,10 @@
       <c r="D20" s="63"/>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="190"/>
-      <c r="I20" s="183"/>
-      <c r="J20" s="184"/>
+      <c r="G20" s="210"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="175"/>
+      <c r="J20" s="176"/>
       <c r="K20" s="64"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5753,10 +4285,10 @@
       <c r="D21" s="63"/>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="190"/>
-      <c r="I21" s="183"/>
-      <c r="J21" s="184"/>
+      <c r="G21" s="210"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="175"/>
+      <c r="J21" s="176"/>
       <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5775,10 +4307,10 @@
       <c r="D22" s="63"/>
       <c r="E22" s="25"/>
       <c r="F22" s="25"/>
-      <c r="G22" s="189"/>
-      <c r="H22" s="190"/>
-      <c r="I22" s="183"/>
-      <c r="J22" s="184"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="211"/>
+      <c r="I22" s="175"/>
+      <c r="J22" s="176"/>
       <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5797,10 +4329,10 @@
       <c r="D23" s="63"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
-      <c r="G23" s="189"/>
-      <c r="H23" s="190"/>
-      <c r="I23" s="183"/>
-      <c r="J23" s="184"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="211"/>
+      <c r="I23" s="175"/>
+      <c r="J23" s="176"/>
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5819,10 +4351,10 @@
       <c r="D24" s="63"/>
       <c r="E24" s="25"/>
       <c r="F24" s="25"/>
-      <c r="G24" s="189"/>
-      <c r="H24" s="190"/>
-      <c r="I24" s="183"/>
-      <c r="J24" s="184"/>
+      <c r="G24" s="210"/>
+      <c r="H24" s="211"/>
+      <c r="I24" s="175"/>
+      <c r="J24" s="176"/>
       <c r="K24" s="64"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5841,10 +4373,10 @@
       <c r="D25" s="63"/>
       <c r="E25" s="25"/>
       <c r="F25" s="25"/>
-      <c r="G25" s="189"/>
-      <c r="H25" s="190"/>
-      <c r="I25" s="183"/>
-      <c r="J25" s="184"/>
+      <c r="G25" s="210"/>
+      <c r="H25" s="211"/>
+      <c r="I25" s="175"/>
+      <c r="J25" s="176"/>
       <c r="K25" s="64"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5863,10 +4395,10 @@
       <c r="D26" s="63"/>
       <c r="E26" s="25"/>
       <c r="F26" s="25"/>
-      <c r="G26" s="189"/>
-      <c r="H26" s="190"/>
-      <c r="I26" s="183"/>
-      <c r="J26" s="184"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="175"/>
+      <c r="J26" s="176"/>
       <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5885,10 +4417,10 @@
       <c r="D27" s="63"/>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="190"/>
-      <c r="I27" s="183"/>
-      <c r="J27" s="184"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="211"/>
+      <c r="I27" s="175"/>
+      <c r="J27" s="176"/>
       <c r="K27" s="64"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5907,10 +4439,10 @@
       <c r="D28" s="63"/>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
-      <c r="G28" s="189"/>
-      <c r="H28" s="190"/>
-      <c r="I28" s="183"/>
-      <c r="J28" s="184"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="211"/>
+      <c r="I28" s="175"/>
+      <c r="J28" s="176"/>
       <c r="K28" s="64"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5929,10 +4461,10 @@
       <c r="D29" s="63"/>
       <c r="E29" s="25"/>
       <c r="F29" s="25"/>
-      <c r="G29" s="189"/>
-      <c r="H29" s="190"/>
-      <c r="I29" s="183"/>
-      <c r="J29" s="184"/>
+      <c r="G29" s="210"/>
+      <c r="H29" s="211"/>
+      <c r="I29" s="175"/>
+      <c r="J29" s="176"/>
       <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5951,10 +4483,10 @@
       <c r="D30" s="63"/>
       <c r="E30" s="25"/>
       <c r="F30" s="25"/>
-      <c r="G30" s="189"/>
-      <c r="H30" s="190"/>
-      <c r="I30" s="183"/>
-      <c r="J30" s="184"/>
+      <c r="G30" s="210"/>
+      <c r="H30" s="211"/>
+      <c r="I30" s="175"/>
+      <c r="J30" s="176"/>
       <c r="K30" s="64"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5973,10 +4505,10 @@
       <c r="D31" s="63"/>
       <c r="E31" s="25"/>
       <c r="F31" s="25"/>
-      <c r="G31" s="189"/>
-      <c r="H31" s="190"/>
-      <c r="I31" s="183"/>
-      <c r="J31" s="184"/>
+      <c r="G31" s="210"/>
+      <c r="H31" s="211"/>
+      <c r="I31" s="175"/>
+      <c r="J31" s="176"/>
       <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5995,10 +4527,10 @@
       <c r="D32" s="63"/>
       <c r="E32" s="25"/>
       <c r="F32" s="25"/>
-      <c r="G32" s="189"/>
-      <c r="H32" s="190"/>
-      <c r="I32" s="183"/>
-      <c r="J32" s="184"/>
+      <c r="G32" s="210"/>
+      <c r="H32" s="211"/>
+      <c r="I32" s="175"/>
+      <c r="J32" s="176"/>
       <c r="K32" s="64"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6017,10 +4549,10 @@
       <c r="D33" s="63"/>
       <c r="E33" s="25"/>
       <c r="F33" s="25"/>
-      <c r="G33" s="189"/>
-      <c r="H33" s="190"/>
-      <c r="I33" s="183"/>
-      <c r="J33" s="184"/>
+      <c r="G33" s="210"/>
+      <c r="H33" s="211"/>
+      <c r="I33" s="175"/>
+      <c r="J33" s="176"/>
       <c r="K33" s="64"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6039,10 +4571,10 @@
       <c r="D34" s="63"/>
       <c r="E34" s="25"/>
       <c r="F34" s="25"/>
-      <c r="G34" s="189"/>
-      <c r="H34" s="190"/>
-      <c r="I34" s="183"/>
-      <c r="J34" s="184"/>
+      <c r="G34" s="210"/>
+      <c r="H34" s="211"/>
+      <c r="I34" s="175"/>
+      <c r="J34" s="176"/>
       <c r="K34" s="64"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6061,10 +4593,10 @@
       <c r="D35" s="63"/>
       <c r="E35" s="25"/>
       <c r="F35" s="25"/>
-      <c r="G35" s="189"/>
-      <c r="H35" s="190"/>
-      <c r="I35" s="183"/>
-      <c r="J35" s="184"/>
+      <c r="G35" s="210"/>
+      <c r="H35" s="211"/>
+      <c r="I35" s="175"/>
+      <c r="J35" s="176"/>
       <c r="K35" s="64"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6083,10 +4615,10 @@
       <c r="D36" s="63"/>
       <c r="E36" s="25"/>
       <c r="F36" s="25"/>
-      <c r="G36" s="189"/>
-      <c r="H36" s="190"/>
-      <c r="I36" s="183"/>
-      <c r="J36" s="184"/>
+      <c r="G36" s="210"/>
+      <c r="H36" s="211"/>
+      <c r="I36" s="175"/>
+      <c r="J36" s="176"/>
       <c r="K36" s="64"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6105,10 +4637,10 @@
       <c r="D37" s="63"/>
       <c r="E37" s="25"/>
       <c r="F37" s="25"/>
-      <c r="G37" s="189"/>
-      <c r="H37" s="190"/>
-      <c r="I37" s="183"/>
-      <c r="J37" s="184"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="211"/>
+      <c r="I37" s="175"/>
+      <c r="J37" s="176"/>
       <c r="K37" s="64"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6127,10 +4659,10 @@
       <c r="D38" s="63"/>
       <c r="E38" s="25"/>
       <c r="F38" s="25"/>
-      <c r="G38" s="189"/>
-      <c r="H38" s="190"/>
-      <c r="I38" s="183"/>
-      <c r="J38" s="184"/>
+      <c r="G38" s="210"/>
+      <c r="H38" s="211"/>
+      <c r="I38" s="175"/>
+      <c r="J38" s="176"/>
       <c r="K38" s="64"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6149,10 +4681,10 @@
       <c r="D39" s="63"/>
       <c r="E39" s="25"/>
       <c r="F39" s="25"/>
-      <c r="G39" s="189"/>
-      <c r="H39" s="190"/>
-      <c r="I39" s="183"/>
-      <c r="J39" s="184"/>
+      <c r="G39" s="210"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="175"/>
+      <c r="J39" s="176"/>
       <c r="K39" s="64"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6171,18 +4703,18 @@
       <c r="D40" s="63"/>
       <c r="E40" s="25"/>
       <c r="F40" s="25"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="183"/>
-      <c r="J40" s="184"/>
+      <c r="G40" s="213"/>
+      <c r="H40" s="213"/>
+      <c r="I40" s="175"/>
+      <c r="J40" s="176"/>
       <c r="K40" s="64"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="173" t="s">
+      <c r="A41" s="216" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="174"/>
-      <c r="C41" s="174"/>
+      <c r="B41" s="217"/>
+      <c r="C41" s="217"/>
       <c r="D41" s="65" t="e">
         <f>AVERAGE(D11:D40)</f>
         <v>#DIV/0!</v>
@@ -6195,27 +4727,27 @@
         <f>AVERAGE(F11:F40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G41" s="191" t="e">
+      <c r="G41" s="214" t="e">
         <f>AVERAGE(G11:H40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H41" s="192"/>
-      <c r="I41" s="225" t="e">
+      <c r="H41" s="215"/>
+      <c r="I41" s="177" t="e">
         <f>AVERAGE(I11:J40)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J41" s="226"/>
+      <c r="J41" s="178"/>
       <c r="K41" s="37" t="e">
         <f>AVERAGE(K11:K40)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="42" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="175" t="s">
+      <c r="A42" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="B42" s="176"/>
-      <c r="C42" s="176"/>
+      <c r="B42" s="219"/>
+      <c r="C42" s="219"/>
       <c r="D42" s="66">
         <f>MIN(D11:D40)</f>
         <v>0</v>
@@ -6228,27 +4760,27 @@
         <f>MIN(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="225">
         <f>MIN(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="188"/>
-      <c r="I42" s="223">
+      <c r="H42" s="226"/>
+      <c r="I42" s="173">
         <f>MIN(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J42" s="224"/>
+      <c r="J42" s="174"/>
       <c r="K42" s="40">
         <f>MIN(K11:K40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="221" t="s">
+      <c r="A43" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="B43" s="222"/>
-      <c r="C43" s="222"/>
+      <c r="B43" s="184"/>
+      <c r="C43" s="184"/>
       <c r="D43" s="67">
         <f>MAX(D11:D40)</f>
         <v>0</v>
@@ -6261,16 +4793,16 @@
         <f>MAX(F11:F40)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="217">
+      <c r="G43" s="179">
         <f>MAX(G11:H40)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="218"/>
-      <c r="I43" s="219">
+      <c r="H43" s="180"/>
+      <c r="I43" s="181">
         <f>MAX(I11:J40)</f>
         <v>0</v>
       </c>
-      <c r="J43" s="220"/>
+      <c r="J43" s="182"/>
       <c r="K43" s="69">
         <f>MAX(K11:K40)</f>
         <v>0</v>
@@ -6280,8 +4812,8 @@
       <c r="A44" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="151"/>
       <c r="D44" s="44" t="s">
         <v>22</v>
       </c>
@@ -6298,8 +4830,8 @@
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="50"/>
-      <c r="B45" s="172"/>
-      <c r="C45" s="172"/>
+      <c r="B45" s="152"/>
+      <c r="C45" s="152"/>
       <c r="D45" s="44"/>
       <c r="F45" s="46"/>
       <c r="G45" s="47"/>
@@ -6308,11 +4840,11 @@
       <c r="J45" s="51"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="156" t="s">
+      <c r="A46" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B46" s="156"/>
-      <c r="C46" s="156"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="47" t="s">
@@ -6325,11 +4857,11 @@
       <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="156" t="s">
+      <c r="A47" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="156"/>
-      <c r="C47" s="156"/>
+      <c r="B47" s="134"/>
+      <c r="C47" s="134"/>
       <c r="D47" s="44"/>
       <c r="E47" s="44"/>
       <c r="F47" s="44"/>
@@ -6384,52 +4916,38 @@
     </row>
   </sheetData>
   <mergeCells count="94">
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A7:C10"/>
-    <mergeCell ref="G7:H10"/>
-    <mergeCell ref="K7:K10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="G39:H39"/>
@@ -6446,72 +4964,86 @@
     <mergeCell ref="G36:H36"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A7:C10"/>
+    <mergeCell ref="G7:H10"/>
+    <mergeCell ref="K7:K10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="D11:D43">
-    <cfRule type="cellIs" dxfId="35" priority="8" operator="notBetween">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="notBetween">
       <formula>700</formula>
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E43">
-    <cfRule type="cellIs" dxfId="34" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThan">
       <formula>400</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:F43">
-    <cfRule type="cellIs" dxfId="33" priority="6" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="6" operator="lessThan">
       <formula>300</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:H19 G20:G39 G40:H43">
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="notBetween">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="notBetween">
       <formula>45</formula>
       <formula>55</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I11:J43">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notBetween">
+      <formula>210</formula>
+      <formula>213</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="K11:K43">
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="notBetween">
       <formula>410</formula>
       <formula>450</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:J43">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="notBetween">
-      <formula>210</formula>
-      <formula>213</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.11811023622047245" bottom="0.11811023622047245" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6533,35 +5065,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
+      <c r="B1" s="161"/>
+      <c r="C1" s="161"/>
+      <c r="D1" s="161"/>
+      <c r="E1" s="161"/>
+      <c r="F1" s="161"/>
+      <c r="G1" s="161"/>
+      <c r="H1" s="161"/>
+      <c r="I1" s="161"/>
+      <c r="J1" s="161"/>
       <c r="K1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="161" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
       <c r="K2" s="4" t="s">
         <v>29</v>
       </c>
@@ -6582,18 +5114,18 @@
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="144" t="s">
+      <c r="A4" s="162" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="145">
+      <c r="B4" s="163">
         <f>Page1!B4:D4</f>
         <v>0</v>
       </c>
-      <c r="C4" s="177">
+      <c r="C4" s="220">
         <f>Page1!C4</f>
         <v>0</v>
       </c>
-      <c r="D4" s="178"/>
+      <c r="D4" s="209"/>
       <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
@@ -6611,25 +5143,25 @@
       <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="179">
+      <c r="J4" s="221">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
-      <c r="K4" s="180"/>
+      <c r="K4" s="222"/>
     </row>
     <row r="5" spans="1:11" s="45" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="166" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="149">
+      <c r="B5" s="167">
         <f>Page1!B5:D5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="150">
+      <c r="C5" s="168">
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="151"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
@@ -6647,11 +5179,11 @@
       <c r="I5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="195">
+      <c r="J5" s="185">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="196"/>
+      <c r="K5" s="186"/>
     </row>
     <row r="6" spans="1:11" s="45" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="230" t="s">
@@ -6660,66 +5192,66 @@
       <c r="B6" s="231"/>
       <c r="C6" s="232"/>
       <c r="D6" s="233"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="155"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="172"/>
       <c r="H6" s="71"/>
-      <c r="I6" s="197"/>
-      <c r="J6" s="198"/>
-      <c r="K6" s="204"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="188"/>
+      <c r="K6" s="195"/>
     </row>
     <row r="7" spans="1:11" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="198"/>
-      <c r="C7" s="198"/>
-      <c r="D7" s="216" t="s">
+      <c r="A7" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="188"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="208" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="234"/>
       <c r="F7" s="234"/>
-      <c r="G7" s="178"/>
+      <c r="G7" s="209"/>
       <c r="H7" s="227" t="s">
         <v>126</v>
       </c>
-      <c r="I7" s="199"/>
-      <c r="J7" s="200"/>
-      <c r="K7" s="205"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="190"/>
+      <c r="K7" s="196"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="199"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="200"/>
+      <c r="A8" s="189"/>
+      <c r="B8" s="190"/>
+      <c r="C8" s="190"/>
       <c r="D8" s="237" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="208" t="s">
+      <c r="E8" s="199" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="208" t="s">
+      <c r="F8" s="199" t="s">
         <v>131</v>
       </c>
-      <c r="G8" s="208" t="s">
+      <c r="G8" s="199" t="s">
         <v>128</v>
       </c>
       <c r="H8" s="228"/>
-      <c r="I8" s="199"/>
-      <c r="J8" s="200"/>
-      <c r="K8" s="205"/>
+      <c r="I8" s="189"/>
+      <c r="J8" s="190"/>
+      <c r="K8" s="196"/>
     </row>
     <row r="9" spans="1:11" s="5" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199"/>
-      <c r="B9" s="200"/>
-      <c r="C9" s="200"/>
+      <c r="A9" s="189"/>
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
       <c r="D9" s="238"/>
-      <c r="E9" s="153"/>
-      <c r="F9" s="153"/>
-      <c r="G9" s="153"/>
+      <c r="E9" s="171"/>
+      <c r="F9" s="171"/>
+      <c r="G9" s="171"/>
       <c r="H9" s="229"/>
-      <c r="I9" s="199"/>
-      <c r="J9" s="200"/>
-      <c r="K9" s="205"/>
+      <c r="I9" s="189"/>
+      <c r="J9" s="190"/>
+      <c r="K9" s="196"/>
     </row>
     <row r="10" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
@@ -6739,9 +5271,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="73"/>
       <c r="H10" s="74"/>
-      <c r="I10" s="199"/>
-      <c r="J10" s="200"/>
-      <c r="K10" s="205"/>
+      <c r="I10" s="189"/>
+      <c r="J10" s="190"/>
+      <c r="K10" s="196"/>
     </row>
     <row r="11" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="123">
@@ -6761,9 +5293,9 @@
       <c r="F11" s="26"/>
       <c r="G11" s="76"/>
       <c r="H11" s="77"/>
-      <c r="I11" s="199"/>
-      <c r="J11" s="200"/>
-      <c r="K11" s="205"/>
+      <c r="I11" s="189"/>
+      <c r="J11" s="190"/>
+      <c r="K11" s="196"/>
     </row>
     <row r="12" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="123">
@@ -6783,9 +5315,9 @@
       <c r="F12" s="26"/>
       <c r="G12" s="76"/>
       <c r="H12" s="77"/>
-      <c r="I12" s="199"/>
-      <c r="J12" s="200"/>
-      <c r="K12" s="205"/>
+      <c r="I12" s="189"/>
+      <c r="J12" s="190"/>
+      <c r="K12" s="196"/>
     </row>
     <row r="13" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="123">
@@ -6805,9 +5337,9 @@
       <c r="F13" s="23"/>
       <c r="G13" s="73"/>
       <c r="H13" s="77"/>
-      <c r="I13" s="199"/>
-      <c r="J13" s="200"/>
-      <c r="K13" s="205"/>
+      <c r="I13" s="189"/>
+      <c r="J13" s="190"/>
+      <c r="K13" s="196"/>
     </row>
     <row r="14" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="123">
@@ -6827,9 +5359,9 @@
       <c r="F14" s="26"/>
       <c r="G14" s="76"/>
       <c r="H14" s="77"/>
-      <c r="I14" s="199"/>
-      <c r="J14" s="200"/>
-      <c r="K14" s="205"/>
+      <c r="I14" s="189"/>
+      <c r="J14" s="190"/>
+      <c r="K14" s="196"/>
     </row>
     <row r="15" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="123">
@@ -6849,9 +5381,9 @@
       <c r="F15" s="26"/>
       <c r="G15" s="76"/>
       <c r="H15" s="77"/>
-      <c r="I15" s="199"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="205"/>
+      <c r="I15" s="189"/>
+      <c r="J15" s="190"/>
+      <c r="K15" s="196"/>
     </row>
     <row r="16" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="123">
@@ -6871,9 +5403,9 @@
       <c r="F16" s="26"/>
       <c r="G16" s="76"/>
       <c r="H16" s="77"/>
-      <c r="I16" s="199"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="205"/>
+      <c r="I16" s="189"/>
+      <c r="J16" s="190"/>
+      <c r="K16" s="196"/>
     </row>
     <row r="17" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="123">
@@ -6893,9 +5425,9 @@
       <c r="F17" s="26"/>
       <c r="G17" s="76"/>
       <c r="H17" s="77"/>
-      <c r="I17" s="199"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="205"/>
+      <c r="I17" s="189"/>
+      <c r="J17" s="190"/>
+      <c r="K17" s="196"/>
     </row>
     <row r="18" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="123">
@@ -6915,9 +5447,9 @@
       <c r="F18" s="26"/>
       <c r="G18" s="76"/>
       <c r="H18" s="77"/>
-      <c r="I18" s="199"/>
-      <c r="J18" s="200"/>
-      <c r="K18" s="205"/>
+      <c r="I18" s="189"/>
+      <c r="J18" s="190"/>
+      <c r="K18" s="196"/>
     </row>
     <row r="19" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="123">
@@ -6937,9 +5469,9 @@
       <c r="F19" s="26"/>
       <c r="G19" s="76"/>
       <c r="H19" s="77"/>
-      <c r="I19" s="199"/>
-      <c r="J19" s="200"/>
-      <c r="K19" s="205"/>
+      <c r="I19" s="189"/>
+      <c r="J19" s="190"/>
+      <c r="K19" s="196"/>
     </row>
     <row r="20" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="129">
@@ -6959,9 +5491,9 @@
       <c r="F20" s="26"/>
       <c r="G20" s="76"/>
       <c r="H20" s="77"/>
-      <c r="I20" s="199"/>
-      <c r="J20" s="200"/>
-      <c r="K20" s="205"/>
+      <c r="I20" s="189"/>
+      <c r="J20" s="190"/>
+      <c r="K20" s="196"/>
     </row>
     <row r="21" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="123">
@@ -6981,9 +5513,9 @@
       <c r="F21" s="26"/>
       <c r="G21" s="76"/>
       <c r="H21" s="77"/>
-      <c r="I21" s="199"/>
-      <c r="J21" s="200"/>
-      <c r="K21" s="205"/>
+      <c r="I21" s="189"/>
+      <c r="J21" s="190"/>
+      <c r="K21" s="196"/>
     </row>
     <row r="22" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="123">
@@ -7003,9 +5535,9 @@
       <c r="F22" s="26"/>
       <c r="G22" s="76"/>
       <c r="H22" s="77"/>
-      <c r="I22" s="199"/>
-      <c r="J22" s="200"/>
-      <c r="K22" s="205"/>
+      <c r="I22" s="189"/>
+      <c r="J22" s="190"/>
+      <c r="K22" s="196"/>
     </row>
     <row r="23" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="123">
@@ -7025,9 +5557,9 @@
       <c r="F23" s="26"/>
       <c r="G23" s="76"/>
       <c r="H23" s="77"/>
-      <c r="I23" s="199"/>
-      <c r="J23" s="200"/>
-      <c r="K23" s="205"/>
+      <c r="I23" s="189"/>
+      <c r="J23" s="190"/>
+      <c r="K23" s="196"/>
     </row>
     <row r="24" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="123">
@@ -7047,9 +5579,9 @@
       <c r="F24" s="26"/>
       <c r="G24" s="76"/>
       <c r="H24" s="77"/>
-      <c r="I24" s="199"/>
-      <c r="J24" s="200"/>
-      <c r="K24" s="205"/>
+      <c r="I24" s="189"/>
+      <c r="J24" s="190"/>
+      <c r="K24" s="196"/>
     </row>
     <row r="25" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123">
@@ -7069,9 +5601,9 @@
       <c r="F25" s="26"/>
       <c r="G25" s="76"/>
       <c r="H25" s="77"/>
-      <c r="I25" s="199"/>
-      <c r="J25" s="200"/>
-      <c r="K25" s="205"/>
+      <c r="I25" s="189"/>
+      <c r="J25" s="190"/>
+      <c r="K25" s="196"/>
     </row>
     <row r="26" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="123">
@@ -7091,9 +5623,9 @@
       <c r="F26" s="26"/>
       <c r="G26" s="76"/>
       <c r="H26" s="77"/>
-      <c r="I26" s="199"/>
-      <c r="J26" s="200"/>
-      <c r="K26" s="205"/>
+      <c r="I26" s="189"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="196"/>
     </row>
     <row r="27" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="123">
@@ -7113,9 +5645,9 @@
       <c r="F27" s="26"/>
       <c r="G27" s="76"/>
       <c r="H27" s="77"/>
-      <c r="I27" s="199"/>
-      <c r="J27" s="200"/>
-      <c r="K27" s="205"/>
+      <c r="I27" s="189"/>
+      <c r="J27" s="190"/>
+      <c r="K27" s="196"/>
     </row>
     <row r="28" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="123">
@@ -7135,9 +5667,9 @@
       <c r="F28" s="26"/>
       <c r="G28" s="76"/>
       <c r="H28" s="77"/>
-      <c r="I28" s="199"/>
-      <c r="J28" s="200"/>
-      <c r="K28" s="205"/>
+      <c r="I28" s="189"/>
+      <c r="J28" s="190"/>
+      <c r="K28" s="196"/>
     </row>
     <row r="29" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="123">
@@ -7157,9 +5689,9 @@
       <c r="F29" s="26"/>
       <c r="G29" s="76"/>
       <c r="H29" s="77"/>
-      <c r="I29" s="199"/>
-      <c r="J29" s="200"/>
-      <c r="K29" s="205"/>
+      <c r="I29" s="189"/>
+      <c r="J29" s="190"/>
+      <c r="K29" s="196"/>
     </row>
     <row r="30" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="129">
@@ -7179,9 +5711,9 @@
       <c r="F30" s="26"/>
       <c r="G30" s="76"/>
       <c r="H30" s="77"/>
-      <c r="I30" s="199"/>
-      <c r="J30" s="200"/>
-      <c r="K30" s="205"/>
+      <c r="I30" s="189"/>
+      <c r="J30" s="190"/>
+      <c r="K30" s="196"/>
     </row>
     <row r="31" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="123">
@@ -7201,9 +5733,9 @@
       <c r="F31" s="26"/>
       <c r="G31" s="76"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="199"/>
-      <c r="J31" s="200"/>
-      <c r="K31" s="205"/>
+      <c r="I31" s="189"/>
+      <c r="J31" s="190"/>
+      <c r="K31" s="196"/>
     </row>
     <row r="32" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="123">
@@ -7223,9 +5755,9 @@
       <c r="F32" s="26"/>
       <c r="G32" s="76"/>
       <c r="H32" s="77"/>
-      <c r="I32" s="199"/>
-      <c r="J32" s="200"/>
-      <c r="K32" s="205"/>
+      <c r="I32" s="189"/>
+      <c r="J32" s="190"/>
+      <c r="K32" s="196"/>
     </row>
     <row r="33" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="123">
@@ -7245,9 +5777,9 @@
       <c r="F33" s="26"/>
       <c r="G33" s="76"/>
       <c r="H33" s="77"/>
-      <c r="I33" s="199"/>
-      <c r="J33" s="200"/>
-      <c r="K33" s="205"/>
+      <c r="I33" s="189"/>
+      <c r="J33" s="190"/>
+      <c r="K33" s="196"/>
     </row>
     <row r="34" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="123">
@@ -7267,9 +5799,9 @@
       <c r="F34" s="26"/>
       <c r="G34" s="76"/>
       <c r="H34" s="77"/>
-      <c r="I34" s="199"/>
-      <c r="J34" s="200"/>
-      <c r="K34" s="205"/>
+      <c r="I34" s="189"/>
+      <c r="J34" s="190"/>
+      <c r="K34" s="196"/>
     </row>
     <row r="35" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="123">
@@ -7289,9 +5821,9 @@
       <c r="F35" s="26"/>
       <c r="G35" s="76"/>
       <c r="H35" s="77"/>
-      <c r="I35" s="199"/>
-      <c r="J35" s="200"/>
-      <c r="K35" s="205"/>
+      <c r="I35" s="189"/>
+      <c r="J35" s="190"/>
+      <c r="K35" s="196"/>
     </row>
     <row r="36" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="123">
@@ -7311,9 +5843,9 @@
       <c r="F36" s="26"/>
       <c r="G36" s="76"/>
       <c r="H36" s="77"/>
-      <c r="I36" s="199"/>
-      <c r="J36" s="200"/>
-      <c r="K36" s="205"/>
+      <c r="I36" s="189"/>
+      <c r="J36" s="190"/>
+      <c r="K36" s="196"/>
     </row>
     <row r="37" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="123">
@@ -7333,9 +5865,9 @@
       <c r="F37" s="26"/>
       <c r="G37" s="76"/>
       <c r="H37" s="77"/>
-      <c r="I37" s="199"/>
-      <c r="J37" s="200"/>
-      <c r="K37" s="205"/>
+      <c r="I37" s="189"/>
+      <c r="J37" s="190"/>
+      <c r="K37" s="196"/>
     </row>
     <row r="38" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="123">
@@ -7355,9 +5887,9 @@
       <c r="F38" s="26"/>
       <c r="G38" s="76"/>
       <c r="H38" s="77"/>
-      <c r="I38" s="199"/>
-      <c r="J38" s="200"/>
-      <c r="K38" s="205"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="190"/>
+      <c r="K38" s="196"/>
     </row>
     <row r="39" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="130">
@@ -7377,9 +5909,9 @@
       <c r="F39" s="26"/>
       <c r="G39" s="76"/>
       <c r="H39" s="77"/>
-      <c r="I39" s="199"/>
-      <c r="J39" s="200"/>
-      <c r="K39" s="205"/>
+      <c r="I39" s="189"/>
+      <c r="J39" s="190"/>
+      <c r="K39" s="196"/>
     </row>
     <row r="40" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="235" t="s">
@@ -7407,16 +5939,16 @@
         <f>AVERAGE(H10:H39)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I40" s="200"/>
-      <c r="J40" s="200"/>
-      <c r="K40" s="205"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="190"/>
+      <c r="K40" s="196"/>
     </row>
     <row r="41" spans="1:11" s="45" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="175" t="s">
+      <c r="A41" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="176"/>
-      <c r="C41" s="176"/>
+      <c r="B41" s="219"/>
+      <c r="C41" s="219"/>
       <c r="D41" s="80">
         <f>MIN(D10:D39)</f>
         <v>0</v>
@@ -7437,16 +5969,16 @@
         <f>MIN(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I41" s="200"/>
-      <c r="J41" s="200"/>
-      <c r="K41" s="205"/>
+      <c r="I41" s="190"/>
+      <c r="J41" s="190"/>
+      <c r="K41" s="196"/>
     </row>
     <row r="42" spans="1:11" s="5" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="221" t="s">
+      <c r="A42" s="183" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="222"/>
-      <c r="C42" s="222"/>
+      <c r="B42" s="184"/>
+      <c r="C42" s="184"/>
       <c r="D42" s="82">
         <f>MAX(D10:D39)</f>
         <v>0</v>
@@ -7467,16 +5999,16 @@
         <f>MAX(H10:H39)</f>
         <v>0</v>
       </c>
-      <c r="I42" s="203"/>
-      <c r="J42" s="203"/>
-      <c r="K42" s="206"/>
+      <c r="I42" s="194"/>
+      <c r="J42" s="194"/>
+      <c r="K42" s="197"/>
     </row>
     <row r="43" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="B43" s="171"/>
-      <c r="C43" s="171"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="151"/>
       <c r="D43" s="44" t="s">
         <v>22</v>
       </c>
@@ -7493,8 +6025,8 @@
     </row>
     <row r="44" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="50"/>
-      <c r="B44" s="172"/>
-      <c r="C44" s="172"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="152"/>
       <c r="D44" s="44"/>
       <c r="F44" s="46"/>
       <c r="G44" s="47"/>
@@ -7503,11 +6035,11 @@
       <c r="J44" s="51"/>
     </row>
     <row r="45" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="156"/>
-      <c r="C45" s="156"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="134"/>
       <c r="D45" s="44"/>
       <c r="E45" s="44"/>
       <c r="F45" s="47" t="s">
@@ -7520,11 +6052,11 @@
       <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:11" s="45" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="156" t="s">
+      <c r="A46" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="B46" s="156"/>
-      <c r="C46" s="156"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
       <c r="D46" s="44"/>
       <c r="E46" s="44"/>
       <c r="F46" s="44"/>
@@ -7549,6 +6081,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="I6:K42"/>
     <mergeCell ref="H7:H9"/>
@@ -7565,36 +6106,27 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <conditionalFormatting sqref="D10:D42">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="notBetween">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="notBetween">
       <formula>55</formula>
       <formula>65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10:E42">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="notBetween">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="notBetween">
       <formula>45</formula>
       <formula>55</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F42">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="notBetween">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="notBetween">
       <formula>-16</formula>
       <formula>-6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G10:H42">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="notBetween">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
       <formula>0</formula>
       <formula>4</formula>
     </cfRule>
@@ -7620,15 +6152,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="289" t="s">
+      <c r="A1" s="240" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="290"/>
-      <c r="C1" s="290"/>
-      <c r="D1" s="290"/>
-      <c r="E1" s="290"/>
-      <c r="F1" s="290"/>
-      <c r="G1" s="291"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="242"/>
     </row>
     <row r="2" spans="1:7" s="86" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="87"/>
@@ -7642,37 +6174,37 @@
       </c>
     </row>
     <row r="3" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="297" t="s">
+      <c r="A3" s="251" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="298"/>
-      <c r="C3" s="298"/>
-      <c r="D3" s="298"/>
-      <c r="E3" s="298"/>
-      <c r="F3" s="298"/>
-      <c r="G3" s="299"/>
+      <c r="B3" s="252"/>
+      <c r="C3" s="252"/>
+      <c r="D3" s="252"/>
+      <c r="E3" s="252"/>
+      <c r="F3" s="252"/>
+      <c r="G3" s="253"/>
     </row>
     <row r="4" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="199" t="s">
+      <c r="A4" s="189" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
-      <c r="F4" s="200"/>
-      <c r="G4" s="205"/>
+      <c r="B4" s="190"/>
+      <c r="C4" s="190"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="196"/>
     </row>
     <row r="5" spans="1:7" s="86" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="292" t="s">
+      <c r="A5" s="243" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="293"/>
-      <c r="C5" s="293"/>
-      <c r="D5" s="293"/>
-      <c r="E5" s="293"/>
-      <c r="F5" s="293"/>
-      <c r="G5" s="294"/>
+      <c r="B5" s="244"/>
+      <c r="C5" s="244"/>
+      <c r="D5" s="244"/>
+      <c r="E5" s="244"/>
+      <c r="F5" s="244"/>
+      <c r="G5" s="245"/>
     </row>
     <row r="6" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="90" t="s">
@@ -7684,14 +6216,15 @@
       <c r="C6" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="257" t="s">
-        <v>141</v>
-      </c>
-      <c r="E6" s="259"/>
-      <c r="F6" s="295" t="s">
+      <c r="D6" s="246">
+        <f>Page1!H4</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="247"/>
+      <c r="F6" s="248" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="280">
+      <c r="G6" s="249">
         <f>Page1!J4</f>
         <v>0</v>
       </c>
@@ -7704,13 +6237,13 @@
       <c r="C7" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="257">
+      <c r="D7" s="246">
         <f>Page1!F5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="259"/>
-      <c r="F7" s="295"/>
-      <c r="G7" s="296"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="248"/>
+      <c r="G7" s="250"/>
     </row>
     <row r="8" spans="1:7" s="86" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
@@ -7723,15 +6256,15 @@
       <c r="C8" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="295">
+      <c r="D8" s="248">
         <f>Page1!H5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="295"/>
-      <c r="F8" s="277" t="s">
+      <c r="E8" s="248"/>
+      <c r="F8" s="263" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="280">
+      <c r="G8" s="249">
         <f>Page1!J5</f>
         <v>0</v>
       </c>
@@ -7744,15 +6277,15 @@
         <f>Page1!G44</f>
         <v>461359700</v>
       </c>
-      <c r="C9" s="277" t="s">
+      <c r="C9" s="263" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="283" t="s">
+      <c r="D9" s="268" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="284"/>
-      <c r="F9" s="278"/>
-      <c r="G9" s="281"/>
+      <c r="E9" s="269"/>
+      <c r="F9" s="264"/>
+      <c r="G9" s="266"/>
     </row>
     <row r="10" spans="1:7" s="86" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="97" t="s">
@@ -7762,34 +6295,34 @@
         <f>Page1!C5</f>
         <v>0</v>
       </c>
-      <c r="C10" s="279"/>
-      <c r="D10" s="285"/>
-      <c r="E10" s="286"/>
-      <c r="F10" s="279"/>
-      <c r="G10" s="282"/>
+      <c r="C10" s="265"/>
+      <c r="D10" s="270"/>
+      <c r="E10" s="271"/>
+      <c r="F10" s="265"/>
+      <c r="G10" s="267"/>
     </row>
     <row r="11" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="300" t="s">
+      <c r="A11" s="254" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="302" t="s">
+      <c r="B11" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="304" t="s">
+      <c r="C11" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="305"/>
-      <c r="E11" s="306"/>
-      <c r="F11" s="302" t="s">
+      <c r="D11" s="259"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="307" t="s">
+      <c r="G11" s="261" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="301"/>
-      <c r="B12" s="303"/>
+      <c r="A12" s="255"/>
+      <c r="B12" s="257"/>
       <c r="C12" s="99" t="s">
         <v>60</v>
       </c>
@@ -7799,8 +6332,8 @@
       <c r="E12" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="303"/>
-      <c r="G12" s="308"/>
+      <c r="F12" s="257"/>
+      <c r="G12" s="262"/>
     </row>
     <row r="13" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="100" t="s">
@@ -7870,7 +6403,7 @@
         <f>Page1!K39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G15" s="287" t="s">
+      <c r="G15" s="272" t="s">
         <v>71</v>
       </c>
     </row>
@@ -8026,7 +6559,7 @@
         <f>Page1!H39</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G22" s="138"/>
+      <c r="G22" s="156"/>
     </row>
     <row r="23" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -8126,26 +6659,26 @@
       </c>
     </row>
     <row r="27" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="271" t="s">
+      <c r="A27" s="273" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="272"/>
-      <c r="C27" s="272"/>
-      <c r="D27" s="272"/>
-      <c r="E27" s="272"/>
-      <c r="F27" s="272"/>
-      <c r="G27" s="273"/>
+      <c r="B27" s="274"/>
+      <c r="C27" s="274"/>
+      <c r="D27" s="274"/>
+      <c r="E27" s="274"/>
+      <c r="F27" s="274"/>
+      <c r="G27" s="275"/>
     </row>
     <row r="28" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="255" t="s">
+      <c r="A28" s="276" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="256"/>
-      <c r="C28" s="274" t="s">
+      <c r="B28" s="277"/>
+      <c r="C28" s="278" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="275"/>
-      <c r="E28" s="276"/>
+      <c r="D28" s="279"/>
+      <c r="E28" s="280"/>
       <c r="F28" s="113" t="s">
         <v>92</v>
       </c>
@@ -8154,15 +6687,15 @@
       </c>
     </row>
     <row r="29" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="260" t="s">
+      <c r="A29" s="281" t="s">
         <v>94</v>
       </c>
-      <c r="B29" s="259"/>
-      <c r="C29" s="265" t="s">
+      <c r="B29" s="247"/>
+      <c r="C29" s="282" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="266"/>
-      <c r="E29" s="267"/>
+      <c r="D29" s="283"/>
+      <c r="E29" s="284"/>
       <c r="F29" s="66" t="s">
         <v>92</v>
       </c>
@@ -8171,15 +6704,15 @@
       </c>
     </row>
     <row r="30" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="260" t="s">
+      <c r="A30" s="281" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="259"/>
-      <c r="C30" s="265" t="s">
+      <c r="B30" s="247"/>
+      <c r="C30" s="282" t="s">
         <v>97</v>
       </c>
-      <c r="D30" s="266"/>
-      <c r="E30" s="267"/>
+      <c r="D30" s="283"/>
+      <c r="E30" s="284"/>
       <c r="F30" s="66" t="s">
         <v>92</v>
       </c>
@@ -8188,15 +6721,15 @@
       </c>
     </row>
     <row r="31" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="260" t="s">
+      <c r="A31" s="281" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="259"/>
-      <c r="C31" s="265" t="s">
+      <c r="B31" s="247"/>
+      <c r="C31" s="282" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="266"/>
-      <c r="E31" s="267"/>
+      <c r="D31" s="283"/>
+      <c r="E31" s="284"/>
       <c r="F31" s="66" t="s">
         <v>92</v>
       </c>
@@ -8205,15 +6738,15 @@
       </c>
     </row>
     <row r="32" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="260" t="s">
+      <c r="A32" s="281" t="s">
         <v>101</v>
       </c>
-      <c r="B32" s="259"/>
-      <c r="C32" s="265" t="s">
+      <c r="B32" s="247"/>
+      <c r="C32" s="282" t="s">
         <v>102</v>
       </c>
-      <c r="D32" s="266"/>
-      <c r="E32" s="267"/>
+      <c r="D32" s="283"/>
+      <c r="E32" s="284"/>
       <c r="F32" s="66" t="s">
         <v>92</v>
       </c>
@@ -8222,15 +6755,15 @@
       </c>
     </row>
     <row r="33" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="260" t="s">
+      <c r="A33" s="281" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="259"/>
-      <c r="C33" s="265" t="s">
+      <c r="B33" s="247"/>
+      <c r="C33" s="282" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="266"/>
-      <c r="E33" s="267"/>
+      <c r="D33" s="283"/>
+      <c r="E33" s="284"/>
       <c r="F33" s="66" t="s">
         <v>92</v>
       </c>
@@ -8239,15 +6772,15 @@
       </c>
     </row>
     <row r="34" spans="1:7" s="86" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="166" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="149"/>
-      <c r="C34" s="268" t="s">
+      <c r="B34" s="167"/>
+      <c r="C34" s="287" t="s">
         <v>106</v>
       </c>
-      <c r="D34" s="269"/>
-      <c r="E34" s="270"/>
+      <c r="D34" s="288"/>
+      <c r="E34" s="289"/>
       <c r="F34" s="114" t="s">
         <v>92</v>
       </c>
@@ -8256,26 +6789,26 @@
       </c>
     </row>
     <row r="35" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="271" t="s">
+      <c r="A35" s="273" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="272"/>
-      <c r="C35" s="272"/>
-      <c r="D35" s="272"/>
-      <c r="E35" s="272"/>
-      <c r="F35" s="272"/>
-      <c r="G35" s="273"/>
+      <c r="B35" s="274"/>
+      <c r="C35" s="274"/>
+      <c r="D35" s="274"/>
+      <c r="E35" s="274"/>
+      <c r="F35" s="274"/>
+      <c r="G35" s="275"/>
     </row>
     <row r="36" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="144" t="s">
+      <c r="A36" s="162" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="145"/>
-      <c r="C36" s="263" t="s">
+      <c r="B36" s="163"/>
+      <c r="C36" s="285" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="264"/>
-      <c r="E36" s="145"/>
+      <c r="D36" s="286"/>
+      <c r="E36" s="163"/>
       <c r="F36" s="10" t="s">
         <v>92</v>
       </c>
@@ -8284,15 +6817,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="255" t="s">
+      <c r="A37" s="276" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="256"/>
-      <c r="C37" s="257" t="s">
+      <c r="B37" s="277"/>
+      <c r="C37" s="246" t="s">
         <v>110</v>
       </c>
-      <c r="D37" s="258"/>
-      <c r="E37" s="259"/>
+      <c r="D37" s="290"/>
+      <c r="E37" s="247"/>
       <c r="F37" s="106" t="s">
         <v>92</v>
       </c>
@@ -8301,15 +6834,15 @@
       </c>
     </row>
     <row r="38" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="260" t="s">
+      <c r="A38" s="281" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="259"/>
-      <c r="C38" s="257" t="s">
+      <c r="B38" s="247"/>
+      <c r="C38" s="246" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="258"/>
-      <c r="E38" s="259"/>
+      <c r="D38" s="290"/>
+      <c r="E38" s="247"/>
       <c r="F38" s="106" t="s">
         <v>92</v>
       </c>
@@ -8318,15 +6851,15 @@
       </c>
     </row>
     <row r="39" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="148" t="s">
+      <c r="A39" s="166" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="149"/>
-      <c r="C39" s="261" t="s">
+      <c r="B39" s="167"/>
+      <c r="C39" s="291" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="262"/>
-      <c r="E39" s="149"/>
+      <c r="D39" s="292"/>
+      <c r="E39" s="167"/>
       <c r="F39" s="1" t="s">
         <v>92</v>
       </c>
@@ -8335,50 +6868,50 @@
       </c>
     </row>
     <row r="40" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="241" t="s">
+      <c r="A40" s="295" t="s">
         <v>115</v>
       </c>
-      <c r="B40" s="242"/>
-      <c r="C40" s="243" t="s">
+      <c r="B40" s="296"/>
+      <c r="C40" s="297" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="245"/>
-      <c r="F40" s="243" t="s">
+      <c r="D40" s="298"/>
+      <c r="E40" s="299"/>
+      <c r="F40" s="297" t="s">
         <v>138</v>
       </c>
-      <c r="G40" s="245"/>
+      <c r="G40" s="299"/>
     </row>
     <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="246"/>
-      <c r="B41" s="247"/>
-      <c r="C41" s="199"/>
-      <c r="D41" s="200"/>
-      <c r="E41" s="205"/>
-      <c r="F41" s="250"/>
-      <c r="G41" s="251"/>
+      <c r="A41" s="300"/>
+      <c r="B41" s="301"/>
+      <c r="C41" s="189"/>
+      <c r="D41" s="190"/>
+      <c r="E41" s="196"/>
+      <c r="F41" s="304"/>
+      <c r="G41" s="305"/>
     </row>
     <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="248"/>
-      <c r="B42" s="249"/>
-      <c r="C42" s="252" t="s">
+      <c r="A42" s="302"/>
+      <c r="B42" s="303"/>
+      <c r="C42" s="306" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="253"/>
-      <c r="E42" s="254"/>
-      <c r="F42" s="252" t="s">
+      <c r="D42" s="307"/>
+      <c r="E42" s="308"/>
+      <c r="F42" s="306" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="254"/>
+      <c r="G42" s="308"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
       <c r="B43" s="115"/>
       <c r="C43" s="115"/>
       <c r="D43" s="115"/>
-      <c r="E43" s="239"/>
-      <c r="F43" s="239"/>
-      <c r="G43" s="239"/>
+      <c r="E43" s="293"/>
+      <c r="F43" s="293"/>
+      <c r="G43" s="293"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="46" t="s">
@@ -8387,24 +6920,63 @@
       <c r="B44" s="116"/>
       <c r="C44" s="118"/>
       <c r="D44" s="115"/>
-      <c r="E44" s="240"/>
-      <c r="F44" s="240"/>
-      <c r="G44" s="240"/>
+      <c r="E44" s="294"/>
+      <c r="F44" s="294"/>
+      <c r="G44" s="294"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="288" t="s">
+      <c r="A46" s="239" t="s">
         <v>117</v>
       </c>
-      <c r="B46" s="288"/>
+      <c r="B46" s="239"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="288" t="s">
+      <c r="A47" s="239" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="288"/>
+      <c r="B47" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A41:B42"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="G15:G22"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:G1"/>
@@ -8421,45 +6993,6 @@
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="G15:G22"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="F42:G42"/>
   </mergeCells>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.78740157480314965" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/UC-18gsm-210W-BFQR.xlsx
+++ b/backend/templates/UC-18gsm-210W-BFQR.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00DB193-E85B-44C3-AA1A-52AC6DB8DE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2717A4-72D6-43AB-B9E9-95C05548D9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1443,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="309">
+  <cellXfs count="310">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2393,20 +2393,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6882,27 +6885,27 @@
       </c>
       <c r="G40" s="299"/>
     </row>
-    <row r="41" spans="1:7" s="86" customFormat="1" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" s="86" customFormat="1" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="300"/>
       <c r="B41" s="301"/>
-      <c r="C41" s="189"/>
-      <c r="D41" s="190"/>
-      <c r="E41" s="196"/>
+      <c r="C41" s="304"/>
+      <c r="D41" s="305"/>
+      <c r="E41" s="306"/>
       <c r="F41" s="304"/>
-      <c r="G41" s="305"/>
-    </row>
-    <row r="42" spans="1:7" s="86" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G41" s="306"/>
+    </row>
+    <row r="42" spans="1:7" s="86" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="302"/>
       <c r="B42" s="303"/>
-      <c r="C42" s="306" t="s">
+      <c r="C42" s="307" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="307"/>
-      <c r="E42" s="308"/>
-      <c r="F42" s="306" t="s">
+      <c r="D42" s="308"/>
+      <c r="E42" s="309"/>
+      <c r="F42" s="307" t="s">
         <v>139</v>
       </c>
-      <c r="G42" s="308"/>
+      <c r="G42" s="309"/>
     </row>
     <row r="43" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="115"/>
